--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -8,17 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R Projects\github\statistics-for-psychology\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D840DD-B398-465B-A808-1F963C7440F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89080D38-2B40-4857-99ED-205BB6C0E2DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Model" sheetId="1" r:id="rId1"/>
-    <sheet name="QQ" sheetId="2" r:id="rId2"/>
+    <sheet name="Prehled" sheetId="1" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="QQ" sheetId="3" r:id="rId3"/>
+    <sheet name="Z_skory" sheetId="4" r:id="rId4"/>
+    <sheet name="Standardizace" sheetId="5" r:id="rId5"/>
+    <sheet name="Modely" sheetId="6" r:id="rId6"/>
+    <sheet name="Skaly" sheetId="7" r:id="rId7"/>
+    <sheet name="U01_reference" sheetId="8" r:id="rId8"/>
+    <sheet name="U02_standardizace" sheetId="9" r:id="rId9"/>
+    <sheet name="U03_model" sheetId="10" r:id="rId10"/>
+    <sheet name="U04_plochy" sheetId="11" r:id="rId11"/>
+    <sheet name="U05_percentily" sheetId="12" r:id="rId12"/>
+    <sheet name="U06_zaokrouhleni" sheetId="13" r:id="rId13"/>
+    <sheet name="U07_prevody" sheetId="14" r:id="rId14"/>
+    <sheet name="U08_pasmo" sheetId="15" r:id="rId15"/>
+    <sheet name="QQ_data" sheetId="16" r:id="rId16"/>
+    <sheet name="Sim_normalni" sheetId="17" r:id="rId17"/>
+    <sheet name="Sim_sikme" sheetId="18" r:id="rId18"/>
+    <sheet name="Sim_chvosty" sheetId="19" r:id="rId19"/>
+    <sheet name="Sim_smes" sheetId="20" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Model!$A$1:$D$25</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">QQ!$A$1:$N$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Model!$A$1:$D$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">QQ!$A$1:$N$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +56,178 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="128">
+  <si>
+    <t>Data ke kapitole 4</t>
+  </si>
+  <si>
+    <t>Začněte vstupy. Žluté buňky obsahují data; modré buňky na výpočtových listech vzorce.</t>
+  </si>
+  <si>
+    <t>Zadání a vysvětlení jsou v kapitole. Řešení otevírejte až po vlastním pokusu.</t>
+  </si>
+  <si>
+    <t>Slovní úlohy bez konkrétních pozorování nevyžadují vlastní datový list.</t>
+  </si>
+  <si>
+    <t>Hladké modelové křivky jsou modely, nikoli další soubory naměřených hodnot.</t>
+  </si>
+  <si>
+    <t>List</t>
+  </si>
+  <si>
+    <t>Oblast vstupů / tabulky</t>
+  </si>
+  <si>
+    <t>Příklad nebo cvičení</t>
+  </si>
+  <si>
+    <t>Z_skory</t>
+  </si>
+  <si>
+    <t>A2:D3</t>
+  </si>
+  <si>
+    <t>Výklad: dvě různé referenční skupiny</t>
+  </si>
+  <si>
+    <t>Standardizace</t>
+  </si>
+  <si>
+    <t>A2:A6</t>
+  </si>
+  <si>
+    <t>Výklad: standardizace pěti časů</t>
+  </si>
+  <si>
+    <t>Modely</t>
+  </si>
+  <si>
+    <t>A2:C4</t>
+  </si>
+  <si>
+    <t>Výklad: poloha a šířka normálního modelu</t>
+  </si>
+  <si>
+    <t>Skaly</t>
+  </si>
+  <si>
+    <t>A2:C5</t>
+  </si>
+  <si>
+    <t>Výklad a cvičení 7: lineární převody</t>
+  </si>
+  <si>
+    <t>U01_reference</t>
+  </si>
+  <si>
+    <t>A2:E3</t>
+  </si>
+  <si>
+    <t>Cvičení 1</t>
+  </si>
+  <si>
+    <t>U02_standardizace</t>
+  </si>
+  <si>
+    <t>Cvičení 2</t>
+  </si>
+  <si>
+    <t>U03_model</t>
+  </si>
+  <si>
+    <t>A2:B6</t>
+  </si>
+  <si>
+    <t>Cvičení 3</t>
+  </si>
+  <si>
+    <t>U04_plochy</t>
+  </si>
+  <si>
+    <t>A2:B7</t>
+  </si>
+  <si>
+    <t>Cvičení 4</t>
+  </si>
+  <si>
+    <t>U05_percentily</t>
+  </si>
+  <si>
+    <t>Cvičení 5</t>
+  </si>
+  <si>
+    <t>U06_zaokrouhleni</t>
+  </si>
+  <si>
+    <t>A2:B5</t>
+  </si>
+  <si>
+    <t>Cvičení 6</t>
+  </si>
+  <si>
+    <t>U07_prevody</t>
+  </si>
+  <si>
+    <t>A2:A5</t>
+  </si>
+  <si>
+    <t>Cvičení 7</t>
+  </si>
+  <si>
+    <t>U08_pasmo</t>
+  </si>
+  <si>
+    <t>A2:A4</t>
+  </si>
+  <si>
+    <t>Cvičení 8</t>
+  </si>
+  <si>
+    <t>QQ_data</t>
+  </si>
+  <si>
+    <t>A2:A13</t>
+  </si>
+  <si>
+    <t>Výklad Q–Q; cvičení 9</t>
+  </si>
+  <si>
+    <t>Sim_normalni</t>
+  </si>
+  <si>
+    <t>A2:A201</t>
+  </si>
+  <si>
+    <t>Obrázky histogramů a Q–Q grafů</t>
+  </si>
+  <si>
+    <t>Sim_sikme</t>
+  </si>
+  <si>
+    <t>Sim_chvosty</t>
+  </si>
+  <si>
+    <t>Sim_smes</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>A1:D25</t>
+  </si>
+  <si>
+    <t>Hotové převody modelu N(50, 10)</t>
+  </si>
+  <si>
+    <t>QQ</t>
+  </si>
+  <si>
+    <t>A1:N24</t>
+  </si>
+  <si>
+    <t>Hotový Q–Q graf a mezivýpočty</t>
+  </si>
   <si>
     <t>Normální model</t>
   </si>
@@ -161,6 +350,96 @@
   </si>
   <si>
     <t>Graf a vzorce se přepočítají. Data nemají být prázdná.</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Použití a původ</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Autorské ilustrační údaje. Nejde o skutečný výzkum.</t>
+  </si>
+  <si>
+    <t>Doba (min)</t>
+  </si>
+  <si>
+    <t>Základní</t>
+  </si>
+  <si>
+    <t>Posunutý</t>
+  </si>
+  <si>
+    <t>Širší</t>
+  </si>
+  <si>
+    <t>Škála</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>IQ</t>
+  </si>
+  <si>
+    <t>Subtest</t>
+  </si>
+  <si>
+    <t>Skupina</t>
+  </si>
+  <si>
+    <t>Z pro zpětný převod</t>
+  </si>
+  <si>
+    <t>Vstup</t>
+  </si>
+  <si>
+    <t>Posuzovaná hustota (na bod)</t>
+  </si>
+  <si>
+    <t>Druhý údaj v alternativním zápisu</t>
+  </si>
+  <si>
+    <t>Počet lidí ve skutečné skupině</t>
+  </si>
+  <si>
+    <t>Nejvýše 45 bodů ve skutečné skupině</t>
+  </si>
+  <si>
+    <t>Podíl vpravo</t>
+  </si>
+  <si>
+    <t>Zaznamenaný skór (body)</t>
+  </si>
+  <si>
+    <t>Krok zaokrouhlení (body)</t>
+  </si>
+  <si>
+    <t>T-skór</t>
+  </si>
+  <si>
+    <t>První skór slouží k lineárnímu převodu; ostatní tři k porovnání modelových percentilových pořadí. Parametry škál jsou na listu Skaly.</t>
+  </si>
+  <si>
+    <t>Z-skór</t>
+  </si>
+  <si>
+    <t>Seřazené autorské skóry. Sestavte vlastní graf; hotová kontrola je na listu QQ. V úloze 9 změňte 65 na 90 a poté obnovte 65.</t>
+  </si>
+  <si>
+    <t>Simulovaný skór (body)</t>
+  </si>
+  <si>
+    <t>Simulovaná data z obrázků kapitoly, 200 hodnot. Nejde o skutečný test ani o nezadaná individuální data cvičení 10.</t>
   </si>
 </sst>
 </file>
@@ -172,7 +451,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -186,6 +465,17 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF526775"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF223744"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -227,11 +517,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -263,6 +556,24 @@
     </xf>
     <xf numFmtId="166" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -316,7 +627,7 @@
             <c:v>Pozorované skóry</c:v>
           </c:tx>
           <c:spPr>
-            <a:ln w="25400">
+            <a:ln w="38100">
               <a:noFill/>
             </a:ln>
           </c:spPr>
@@ -428,7 +739,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D23E-4B54-8FAC-CBB12EC69DA9}"/>
+              <c16:uniqueId val="{00000000-E672-4E0F-8405-FFFD0FA5E6B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -542,7 +853,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D23E-4B54-8FAC-CBB12EC69DA9}"/>
+              <c16:uniqueId val="{00000001-E672-4E0F-8405-FFFD0FA5E6B0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -679,7 +990,7 @@
         <xdr:cNvPr id="2" name="Chart">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -895,6 +1206,3951 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="2" width="25" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+    </row>
+    <row r="3" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+    </row>
+    <row r="4" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A4" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A6" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" ht="30.1" customHeight="1">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="13">
+        <v>80</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13">
+        <v>5</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0.08</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" s="13">
+        <v>85</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="25" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="13">
+        <v>25</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="13">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13">
+        <v>10</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="13">
+        <v>45</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="13">
+        <v>65</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="25" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="13">
+        <v>20</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4" ht="25" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B7" s="13">
+        <v>8</v>
+      </c>
+      <c r="D7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="13">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13">
+        <v>10</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" s="13">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4" ht="25" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="13">
+        <v>0.9</v>
+      </c>
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="4" max="4" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="13">
+        <v>50</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="13">
+        <v>10</v>
+      </c>
+      <c r="D3" s="18"/>
+    </row>
+    <row r="4" spans="1:4" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="13">
+        <v>50</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="13">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="D7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="D4:D7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="13">
+        <v>38</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="13">
+        <v>50</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="13">
+        <v>60</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="13">
+        <v>70</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="C7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="13">
+        <v>1.2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="13">
+        <v>-0.6</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="13">
+        <v>0</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="C7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="13">
+        <v>35</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="13">
+        <v>39</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="13">
+        <v>42</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="13">
+        <v>45</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="13">
+        <v>47</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="13">
+        <v>49</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="13">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="13">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="13">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="13">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="13">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="13">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="15">
+        <v>48.85602655957382</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="15">
+        <v>46.839364304880455</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="15">
+        <v>29.327651524791108</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="15">
+        <v>52.872228445571935</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="15">
+        <v>43.66797230215824</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="15">
+        <v>34.485641358295069</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="15">
+        <v>45.335951801294073</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="15">
+        <v>57.931231438988789</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="15">
+        <v>73.645815079847083</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="15">
+        <v>36.790659198448253</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="15">
+        <v>60.633297746065026</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="15">
+        <v>49.953139935765826</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1">
+      <c r="A14" s="15">
+        <v>50.779485996595696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1">
+      <c r="A15" s="15">
+        <v>65.530800942829472</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1">
+      <c r="A16" s="15">
+        <v>60.164918633653301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1">
+      <c r="A17" s="15">
+        <v>61.754371173718198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1">
+      <c r="A18" s="15">
+        <v>44.577442485984605</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1">
+      <c r="A19" s="15">
+        <v>49.551019429591818</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1">
+      <c r="A20" s="15">
+        <v>41.993588583607043</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1">
+      <c r="A21" s="15">
+        <v>63.984391016308365</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1">
+      <c r="A22" s="15">
+        <v>48.310311875182087</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1">
+      <c r="A23" s="15">
+        <v>44.527688866082066</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1">
+      <c r="A24" s="15">
+        <v>59.414935702480037</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1">
+      <c r="A25" s="15">
+        <v>49.802831212210222</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1">
+      <c r="A26" s="15">
+        <v>33.994100406532567</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1">
+      <c r="A27" s="15">
+        <v>40.032562575854747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1">
+      <c r="A28" s="15">
+        <v>33.390443124033801</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1">
+      <c r="A29" s="15">
+        <v>57.714430934046831</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1">
+      <c r="A30" s="15">
+        <v>42.293809875655597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1">
+      <c r="A31" s="15">
+        <v>48.141142649359402</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1">
+      <c r="A32" s="15">
+        <v>50.142776474036509</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1">
+      <c r="A33" s="15">
+        <v>39.878822474858119</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1">
+      <c r="A34" s="15">
+        <v>58.482898079282862</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1">
+      <c r="A35" s="15">
+        <v>60.462869251118072</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1">
+      <c r="A36" s="15">
+        <v>42.867747678169067</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1">
+      <c r="A37" s="15">
+        <v>59.300964609143207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1">
+      <c r="A38" s="15">
+        <v>41.662759212547883</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1">
+      <c r="A39" s="15">
+        <v>59.760074882925849</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1">
+      <c r="A40" s="15">
+        <v>59.574101755909574</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1">
+      <c r="A41" s="15">
+        <v>49.523339023247992</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1">
+      <c r="A42" s="15">
+        <v>37.834035236208052</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1">
+      <c r="A43" s="15">
+        <v>46.41771648534035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1">
+      <c r="A44" s="15">
+        <v>36.983072480767042</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1">
+      <c r="A45" s="15">
+        <v>54.280198905821017</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1">
+      <c r="A46" s="15">
+        <v>37.035225004798946</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1">
+      <c r="A47" s="15">
+        <v>52.737564164618441</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1">
+      <c r="A48" s="15">
+        <v>46.950070180219853</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1">
+      <c r="A49" s="15">
+        <v>69.081091085624621</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1">
+      <c r="A50" s="15">
+        <v>46.412740836321916</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1">
+      <c r="A51" s="15">
+        <v>49.393557819346448</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1">
+      <c r="A52" s="15">
+        <v>55.395990431852944</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1">
+      <c r="A53" s="15">
+        <v>53.654328011244573</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1">
+      <c r="A54" s="15">
+        <v>46.816634564924215</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1">
+      <c r="A55" s="15">
+        <v>43.709912914779316</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1">
+      <c r="A56" s="15">
+        <v>43.000627703259845</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1">
+      <c r="A57" s="15">
+        <v>38.539160700178265</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1">
+      <c r="A58" s="15">
+        <v>51.752856677065076</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1">
+      <c r="A59" s="15">
+        <v>54.508636923006378</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1">
+      <c r="A60" s="15">
+        <v>40.192091375420389</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1">
+      <c r="A61" s="15">
+        <v>39.485906461018516</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1">
+      <c r="A62" s="15">
+        <v>56.937369572097801</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1">
+      <c r="A63" s="15">
+        <v>49.233452734569866</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1">
+      <c r="A64" s="15">
+        <v>37.369901795678075</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1">
+      <c r="A65" s="15">
+        <v>37.215620558245739</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1">
+      <c r="A66" s="15">
+        <v>56.194832296275479</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1">
+      <c r="A67" s="15">
+        <v>45.930398057771058</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1">
+      <c r="A68" s="15">
+        <v>34.804617767642014</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1">
+      <c r="A69" s="15">
+        <v>46.152415724374336</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1">
+      <c r="A70" s="15">
+        <v>46.591154083937894</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1">
+      <c r="A71" s="15">
+        <v>61.859591041516673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1">
+      <c r="A72" s="15">
+        <v>61.246918279723097</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1">
+      <c r="A73" s="15">
+        <v>43.323629776335913</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1">
+      <c r="A74" s="15">
+        <v>59.744644956386963</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1">
+      <c r="A75" s="15">
+        <v>65.23826650763894</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1">
+      <c r="A76" s="15">
+        <v>34.604384632836016</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1">
+      <c r="A77" s="15">
+        <v>40.947603679490442</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1">
+      <c r="A78" s="15">
+        <v>45.304021468750101</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1">
+      <c r="A79" s="15">
+        <v>53.843439944508297</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1">
+      <c r="A80" s="15">
+        <v>52.740879757534955</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1">
+      <c r="A81" s="15">
+        <v>28.105265642590773</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1">
+      <c r="A82" s="15">
+        <v>45.571114810569938</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1">
+      <c r="A83" s="15">
+        <v>53.203616542744832</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1">
+      <c r="A84" s="15">
+        <v>60.593909023906214</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1">
+      <c r="A85" s="15">
+        <v>57.60119104117085</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1">
+      <c r="A86" s="15">
+        <v>44.13690372359622</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1">
+      <c r="A87" s="15">
+        <v>36.788768113119204</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1">
+      <c r="A88" s="15">
+        <v>61.783788225442834</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1">
+      <c r="A89" s="15">
+        <v>39.29506336887534</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1">
+      <c r="A90" s="15">
+        <v>45.66521280676416</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1">
+      <c r="A91" s="15">
+        <v>45.957749168843776</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1">
+      <c r="A92" s="15">
+        <v>45.699709604273082</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1">
+      <c r="A93" s="15">
+        <v>43.497934881124671</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1">
+      <c r="A94" s="15">
+        <v>53.332077289124832</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1">
+      <c r="A95" s="15">
+        <v>67.28988187628606</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1">
+      <c r="A96" s="15">
+        <v>45.456010305269949</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1">
+      <c r="A97" s="15">
+        <v>49.534855487471489</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1">
+      <c r="A98" s="15">
+        <v>52.059508780425801</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1">
+      <c r="A99" s="15">
+        <v>48.068737172084461</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1">
+      <c r="A100" s="15">
+        <v>64.725972215108769</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1">
+      <c r="A101" s="15">
+        <v>61.560182292331547</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1">
+      <c r="A102" s="15">
+        <v>50.229310447645041</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1">
+      <c r="A103" s="15">
+        <v>25.430709780447994</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1">
+      <c r="A104" s="15">
+        <v>63.388687440098884</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1">
+      <c r="A105" s="15">
+        <v>46.780270853362268</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1">
+      <c r="A106" s="15">
+        <v>36.534135800854969</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1">
+      <c r="A107" s="15">
+        <v>42.238045619455782</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1">
+      <c r="A108" s="15">
+        <v>49.413626080812918</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1">
+      <c r="A109" s="15">
+        <v>48.771498146772707</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1">
+      <c r="A110" s="15">
+        <v>51.397818335362309</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1">
+      <c r="A111" s="15">
+        <v>60.361029134649513</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1">
+      <c r="A112" s="15">
+        <v>60.316299946003681</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1">
+      <c r="A113" s="15">
+        <v>53.128705788464941</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1">
+      <c r="A114" s="15">
+        <v>64.946012690105391</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1">
+      <c r="A115" s="15">
+        <v>65.570472734143124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1">
+      <c r="A116" s="15">
+        <v>60.988139986738474</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1">
+      <c r="A117" s="15">
+        <v>65.386298755475039</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1">
+      <c r="A118" s="15">
+        <v>51.986848954165737</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1">
+      <c r="A119" s="15">
+        <v>49.0209671102984</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1">
+      <c r="A120" s="15">
+        <v>60.864267940241319</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1">
+      <c r="A121" s="15">
+        <v>40.421905271601595</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1">
+      <c r="A122" s="15">
+        <v>32.302503424262298</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1">
+      <c r="A123" s="15">
+        <v>31.264923499048002</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1">
+      <c r="A124" s="15">
+        <v>74.569808674876398</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1">
+      <c r="A125" s="15">
+        <v>37.007746347085316</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1">
+      <c r="A126" s="15">
+        <v>48.342581739261632</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1">
+      <c r="A127" s="15">
+        <v>36.704860301550589</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1">
+      <c r="A128" s="15">
+        <v>64.005227930034394</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1">
+      <c r="A129" s="15">
+        <v>51.115247787119728</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1">
+      <c r="A130" s="15">
+        <v>66.977173845334235</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1">
+      <c r="A131" s="15">
+        <v>59.204872664136033</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1">
+      <c r="A132" s="15">
+        <v>45.847192248604749</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1">
+      <c r="A133" s="15">
+        <v>39.206399006598417</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1">
+      <c r="A134" s="15">
+        <v>38.80995021909321</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1">
+      <c r="A135" s="15">
+        <v>45.361422367684931</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1">
+      <c r="A136" s="15">
+        <v>42.219853681397353</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1">
+      <c r="A137" s="15">
+        <v>51.354421515370717</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1">
+      <c r="A138" s="15">
+        <v>57.526566372503332</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1">
+      <c r="A139" s="15">
+        <v>39.570231804106143</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1">
+      <c r="A140" s="15">
+        <v>56.324175281924994</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1">
+      <c r="A141" s="15">
+        <v>74.243524608603622</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1">
+      <c r="A142" s="15">
+        <v>51.118783278780072</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1">
+      <c r="A143" s="15">
+        <v>44.592454438244189</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1">
+      <c r="A144" s="15">
+        <v>50.68033529070587</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1">
+      <c r="A145" s="15">
+        <v>40.548883654616702</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1">
+      <c r="A146" s="15">
+        <v>57.476971275714739</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1">
+      <c r="A147" s="15">
+        <v>59.646654826703212</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1">
+      <c r="A148" s="15">
+        <v>39.385049402123293</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1">
+      <c r="A149" s="15">
+        <v>40.266263696649418</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1">
+      <c r="A150" s="15">
+        <v>34.153591938930738</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1">
+      <c r="A151" s="15">
+        <v>42.960134885386921</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1">
+      <c r="A152" s="15">
+        <v>49.190582206830676</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1">
+      <c r="A153" s="15">
+        <v>44.393858749102854</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1">
+      <c r="A154" s="15">
+        <v>40.822207618158913</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1">
+      <c r="A155" s="15">
+        <v>58.387185978863286</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1">
+      <c r="A156" s="15">
+        <v>43.940164537228007</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1">
+      <c r="A157" s="15">
+        <v>45.13621953383872</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1">
+      <c r="A158" s="15">
+        <v>44.160885732541971</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1">
+      <c r="A159" s="15">
+        <v>60.338816362286423</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1">
+      <c r="A160" s="15">
+        <v>38.336269962468833</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1">
+      <c r="A161" s="15">
+        <v>44.699578744420954</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1">
+      <c r="A162" s="15">
+        <v>60.750841970820169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1">
+      <c r="A163" s="15">
+        <v>42.217990251135319</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1">
+      <c r="A164" s="15">
+        <v>49.464529408381253</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1">
+      <c r="A165" s="15">
+        <v>26.326737268137702</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1">
+      <c r="A166" s="15">
+        <v>73.77697973777353</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1">
+      <c r="A167" s="15">
+        <v>56.985227664501572</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1">
+      <c r="A168" s="15">
+        <v>47.037125543672232</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1">
+      <c r="A169" s="15">
+        <v>47.932432716228782</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1">
+      <c r="A170" s="15">
+        <v>52.15744464937837</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1">
+      <c r="A171" s="15">
+        <v>41.820146217412486</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1">
+      <c r="A172" s="15">
+        <v>55.253686322740066</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1">
+      <c r="A173" s="15">
+        <v>37.827325971507683</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1">
+      <c r="A174" s="15">
+        <v>53.738822247743855</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1">
+      <c r="A175" s="15">
+        <v>38.077037991019182</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1">
+      <c r="A176" s="15">
+        <v>44.864807447460798</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1">
+      <c r="A177" s="15">
+        <v>31.838565931149642</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1">
+      <c r="A178" s="15">
+        <v>58.7185829174284</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1">
+      <c r="A179" s="15">
+        <v>63.885943414368768</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1">
+      <c r="A180" s="15">
+        <v>61.791327667336972</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1">
+      <c r="A181" s="15">
+        <v>47.525722878995069</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1">
+      <c r="A182" s="15">
+        <v>55.082461309605769</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1">
+      <c r="A183" s="15">
+        <v>46.218250574281711</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1">
+      <c r="A184" s="15">
+        <v>62.506367232129122</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1">
+      <c r="A185" s="15">
+        <v>55.902376601600771</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1">
+      <c r="A186" s="15">
+        <v>47.865588238340798</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1">
+      <c r="A187" s="15">
+        <v>62.486024787688606</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1">
+      <c r="A188" s="15">
+        <v>52.982428252352712</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1">
+      <c r="A189" s="15">
+        <v>56.184283627515811</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1">
+      <c r="A190" s="15">
+        <v>42.664715090276019</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1">
+      <c r="A191" s="15">
+        <v>43.631634432761146</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1">
+      <c r="A192" s="15">
+        <v>44.453961848924564</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1">
+      <c r="A193" s="15">
+        <v>53.766982817623031</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1">
+      <c r="A194" s="15">
+        <v>64.466716918938147</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1">
+      <c r="A195" s="15">
+        <v>68.023243003280058</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1">
+      <c r="A196" s="15">
+        <v>47.725956201885985</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1">
+      <c r="A197" s="15">
+        <v>41.133352827241282</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1">
+      <c r="A198" s="15">
+        <v>45.149796321819835</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1">
+      <c r="A199" s="15">
+        <v>54.39814422263963</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1">
+      <c r="A200" s="15">
+        <v>38.820045797836187</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1">
+      <c r="A201" s="15">
+        <v>55.337898635839188</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="15">
+        <v>66.073597304495223</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="15">
+        <v>38.89004377881065</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="15">
+        <v>80.020527650875579</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="15">
+        <v>31.090159951709211</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="15">
+        <v>47.040123384529956</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="15">
+        <v>30.605094073243531</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="15">
+        <v>32.889411058599826</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="15">
+        <v>49.270290531519237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="15">
+        <v>60.680770826197033</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="15">
+        <v>40.189021148253232</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="15">
+        <v>53.771901529422323</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="15">
+        <v>52.836964898001504</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1">
+      <c r="A14" s="15">
+        <v>59.209591447046762</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1">
+      <c r="A15" s="15">
+        <v>127.78312543566943</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1">
+      <c r="A16" s="15">
+        <v>34.183519198559225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1">
+      <c r="A17" s="15">
+        <v>41.18274655595738</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1">
+      <c r="A18" s="15">
+        <v>37.030579636339098</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1">
+      <c r="A19" s="15">
+        <v>69.599282320561059</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1">
+      <c r="A20" s="15">
+        <v>40.128409448079765</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1">
+      <c r="A21" s="15">
+        <v>40.909797646406474</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1">
+      <c r="A22" s="15">
+        <v>41.117681948769274</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1">
+      <c r="A23" s="15">
+        <v>33.679715639445931</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1">
+      <c r="A24" s="15">
+        <v>34.593579797074199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1">
+      <c r="A25" s="15">
+        <v>31.68787092436105</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1">
+      <c r="A26" s="15">
+        <v>32.181566556702968</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1">
+      <c r="A27" s="15">
+        <v>40.80281381453289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1">
+      <c r="A28" s="15">
+        <v>110.54126476476218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1">
+      <c r="A29" s="15">
+        <v>42.219834222986748</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1">
+      <c r="A30" s="15">
+        <v>49.51755097538549</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1">
+      <c r="A31" s="15">
+        <v>65.963283355365633</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1">
+      <c r="A32" s="15">
+        <v>50.119942095431867</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1">
+      <c r="A33" s="15">
+        <v>53.309910864240294</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1">
+      <c r="A34" s="15">
+        <v>34.308579972581441</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1">
+      <c r="A35" s="15">
+        <v>32.985101421363652</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1">
+      <c r="A36" s="15">
+        <v>64.227802537353881</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1">
+      <c r="A37" s="15">
+        <v>67.28401564803923</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1">
+      <c r="A38" s="15">
+        <v>56.376573777428632</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1">
+      <c r="A39" s="15">
+        <v>30.611158109861105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1">
+      <c r="A40" s="15">
+        <v>49.650231808725181</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1">
+      <c r="A41" s="15">
+        <v>30.256860530935228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1">
+      <c r="A42" s="15">
+        <v>47.465419680181327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1">
+      <c r="A43" s="15">
+        <v>41.842515067522939</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1">
+      <c r="A44" s="15">
+        <v>40.54850793527028</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1">
+      <c r="A45" s="15">
+        <v>50.481946504976037</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1">
+      <c r="A46" s="15">
+        <v>42.879178434911552</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1">
+      <c r="A47" s="15">
+        <v>31.99466759338975</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1">
+      <c r="A48" s="15">
+        <v>41.608413615565183</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1">
+      <c r="A49" s="15">
+        <v>35.372470412403345</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1">
+      <c r="A50" s="15">
+        <v>50.227781583116069</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1">
+      <c r="A51" s="15">
+        <v>33.258706101258475</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1">
+      <c r="A52" s="15">
+        <v>36.146681063355153</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1">
+      <c r="A53" s="15">
+        <v>41.541649535599532</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1">
+      <c r="A54" s="15">
+        <v>33.454991129692644</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1">
+      <c r="A55" s="15">
+        <v>33.187484617810696</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1">
+      <c r="A56" s="15">
+        <v>31.684710506815463</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1">
+      <c r="A57" s="15">
+        <v>54.368565714589124</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1">
+      <c r="A58" s="15">
+        <v>53.078939699238902</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1">
+      <c r="A59" s="15">
+        <v>57.385759221992259</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1">
+      <c r="A60" s="15">
+        <v>36.932783669326454</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1">
+      <c r="A61" s="15">
+        <v>44.711488661657455</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1">
+      <c r="A62" s="15">
+        <v>51.219978988002737</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1">
+      <c r="A63" s="15">
+        <v>34.738380846091424</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1">
+      <c r="A64" s="15">
+        <v>30.929745727242917</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1">
+      <c r="A65" s="15">
+        <v>30.328833469410338</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1">
+      <c r="A66" s="15">
+        <v>36.456756089111629</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1">
+      <c r="A67" s="15">
+        <v>37.117371812928468</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1">
+      <c r="A68" s="15">
+        <v>53.150044412859224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1">
+      <c r="A69" s="15">
+        <v>32.838772782124579</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1">
+      <c r="A70" s="15">
+        <v>33.988396197091788</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1">
+      <c r="A71" s="15">
+        <v>31.164749417428595</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1">
+      <c r="A72" s="15">
+        <v>60.104070127612715</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1">
+      <c r="A73" s="15">
+        <v>54.271881431332069</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1">
+      <c r="A74" s="15">
+        <v>30.121303503401577</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1">
+      <c r="A75" s="15">
+        <v>66.225175337213187</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1">
+      <c r="A76" s="15">
+        <v>40.822088484085434</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1">
+      <c r="A77" s="15">
+        <v>50.794695735580092</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1">
+      <c r="A78" s="15">
+        <v>31.005436310078949</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1">
+      <c r="A79" s="15">
+        <v>39.967539429198951</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1">
+      <c r="A80" s="15">
+        <v>52.430345461374884</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1">
+      <c r="A81" s="15">
+        <v>55.719065134084587</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1">
+      <c r="A82" s="15">
+        <v>69.307078279527076</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1">
+      <c r="A83" s="15">
+        <v>37.682667633052915</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1">
+      <c r="A84" s="15">
+        <v>32.345481631346047</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1">
+      <c r="A85" s="15">
+        <v>58.076325588530665</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1">
+      <c r="A86" s="15">
+        <v>70.60914669782133</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1">
+      <c r="A87" s="15">
+        <v>54.769155363223319</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1">
+      <c r="A88" s="15">
+        <v>37.746288275811821</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1">
+      <c r="A89" s="15">
+        <v>64.19509685089065</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1">
+      <c r="A90" s="15">
+        <v>67.746267547232719</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1">
+      <c r="A91" s="15">
+        <v>35.118766218344049</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1">
+      <c r="A92" s="15">
+        <v>43.427614587660315</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1">
+      <c r="A93" s="15">
+        <v>43.050719894769969</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1">
+      <c r="A94" s="15">
+        <v>34.890101321507245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1">
+      <c r="A95" s="15">
+        <v>37.646529239136726</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1">
+      <c r="A96" s="15">
+        <v>36.512210180517286</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1">
+      <c r="A97" s="15">
+        <v>44.99191072240788</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1">
+      <c r="A98" s="15">
+        <v>40.478340214419546</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1">
+      <c r="A99" s="15">
+        <v>52.912835216752057</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1">
+      <c r="A100" s="15">
+        <v>32.852263803918561</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1">
+      <c r="A101" s="15">
+        <v>42.150519377853158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1">
+      <c r="A102" s="15">
+        <v>34.615299509419771</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1">
+      <c r="A103" s="15">
+        <v>36.867444069527146</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1">
+      <c r="A104" s="15">
+        <v>57.641927952549224</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1">
+      <c r="A105" s="15">
+        <v>49.332261517945113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1">
+      <c r="A106" s="15">
+        <v>38.767668509390205</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1">
+      <c r="A107" s="15">
+        <v>34.39139593849702</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1">
+      <c r="A108" s="15">
+        <v>38.342546371277422</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1">
+      <c r="A109" s="15">
+        <v>37.086550329863663</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1">
+      <c r="A110" s="15">
+        <v>61.755756277563222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1">
+      <c r="A111" s="15">
+        <v>33.55604701442644</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1">
+      <c r="A112" s="15">
+        <v>49.528933362405184</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1">
+      <c r="A113" s="15">
+        <v>53.53956713215149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1">
+      <c r="A114" s="15">
+        <v>54.111682287088399</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1">
+      <c r="A115" s="15">
+        <v>45.94257321611363</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1">
+      <c r="A116" s="15">
+        <v>65.763890061499723</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1">
+      <c r="A117" s="15">
+        <v>40.325761288404465</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1">
+      <c r="A118" s="15">
+        <v>31.281466302461922</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1">
+      <c r="A119" s="15">
+        <v>38.169489009305835</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1">
+      <c r="A120" s="15">
+        <v>37.51286887563765</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1">
+      <c r="A121" s="15">
+        <v>52.210685516361863</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1">
+      <c r="A122" s="15">
+        <v>32.152299138249312</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1">
+      <c r="A123" s="15">
+        <v>33.794799861498177</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1">
+      <c r="A124" s="15">
+        <v>32.705895078834146</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1">
+      <c r="A125" s="15">
+        <v>40.015180462505668</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1">
+      <c r="A126" s="15">
+        <v>31.645221028011292</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1">
+      <c r="A127" s="15">
+        <v>39.651232904288918</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1">
+      <c r="A128" s="15">
+        <v>38.624180280603468</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1">
+      <c r="A129" s="15">
+        <v>30.275298054726374</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1">
+      <c r="A130" s="15">
+        <v>33.485360399354249</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1">
+      <c r="A131" s="15">
+        <v>32.457574945874512</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1">
+      <c r="A132" s="15">
+        <v>43.469868907496675</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1">
+      <c r="A133" s="15">
+        <v>40.892417756210449</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1">
+      <c r="A134" s="15">
+        <v>49.959278068806412</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1">
+      <c r="A135" s="15">
+        <v>33.819442035164684</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1">
+      <c r="A136" s="15">
+        <v>37.856629632879049</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1">
+      <c r="A137" s="15">
+        <v>66.154856239566385</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1">
+      <c r="A138" s="15">
+        <v>55.816313911518563</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1">
+      <c r="A139" s="15">
+        <v>31.1981864226982</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1">
+      <c r="A140" s="15">
+        <v>39.189103175885975</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1">
+      <c r="A141" s="15">
+        <v>32.972748074680567</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1">
+      <c r="A142" s="15">
+        <v>39.807592425495386</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1">
+      <c r="A143" s="15">
+        <v>55.748269181038474</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1">
+      <c r="A144" s="15">
+        <v>42.013864893767419</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1">
+      <c r="A145" s="15">
+        <v>59.178414399406677</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1">
+      <c r="A146" s="15">
+        <v>50.12521477353144</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1">
+      <c r="A147" s="15">
+        <v>87.675613062339906</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1">
+      <c r="A148" s="15">
+        <v>30.488174340651693</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1">
+      <c r="A149" s="15">
+        <v>31.602561503361489</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1">
+      <c r="A150" s="15">
+        <v>55.443514394930453</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1">
+      <c r="A151" s="15">
+        <v>56.192054086035853</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1">
+      <c r="A152" s="15">
+        <v>56.150123476433663</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1">
+      <c r="A153" s="15">
+        <v>55.68656232081986</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1">
+      <c r="A154" s="15">
+        <v>52.108126048601036</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1">
+      <c r="A155" s="15">
+        <v>61.11078056380785</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1">
+      <c r="A156" s="15">
+        <v>49.010764178189817</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1">
+      <c r="A157" s="15">
+        <v>39.469132425729185</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1">
+      <c r="A158" s="15">
+        <v>34.490346286911517</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1">
+      <c r="A159" s="15">
+        <v>61.676710013272412</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1">
+      <c r="A160" s="15">
+        <v>40.178170586004853</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1">
+      <c r="A161" s="15">
+        <v>47.584741701673153</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1">
+      <c r="A162" s="15">
+        <v>45.731316119888731</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1">
+      <c r="A163" s="15">
+        <v>55.215121841660505</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1">
+      <c r="A164" s="15">
+        <v>32.609912313574071</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1">
+      <c r="A165" s="15">
+        <v>68.509276777478107</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1">
+      <c r="A166" s="15">
+        <v>41.674246587085797</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1">
+      <c r="A167" s="15">
+        <v>72.258166835091544</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1">
+      <c r="A168" s="15">
+        <v>33.935264372921168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1">
+      <c r="A169" s="15">
+        <v>62.180283317410215</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1">
+      <c r="A170" s="15">
+        <v>45.977431022863271</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1">
+      <c r="A171" s="15">
+        <v>47.563953981104675</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1">
+      <c r="A172" s="15">
+        <v>46.289589497561934</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1">
+      <c r="A173" s="15">
+        <v>35.568672852011275</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1">
+      <c r="A174" s="15">
+        <v>52.65075185210145</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1">
+      <c r="A175" s="15">
+        <v>41.391437099616411</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1">
+      <c r="A176" s="15">
+        <v>31.535752152121631</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1">
+      <c r="A177" s="15">
+        <v>35.991911246117787</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1">
+      <c r="A178" s="15">
+        <v>37.004774257075042</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1">
+      <c r="A179" s="15">
+        <v>36.426826003007591</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1">
+      <c r="A180" s="15">
+        <v>36.473699386697263</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1">
+      <c r="A181" s="15">
+        <v>47.995016471783998</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1">
+      <c r="A182" s="15">
+        <v>38.942083126911427</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1">
+      <c r="A183" s="15">
+        <v>38.489750877488405</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1">
+      <c r="A184" s="15">
+        <v>37.104922577273101</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1">
+      <c r="A185" s="15">
+        <v>66.423356354208835</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1">
+      <c r="A186" s="15">
+        <v>33.493768929038197</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1">
+      <c r="A187" s="15">
+        <v>35.440031850019146</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1">
+      <c r="A188" s="15">
+        <v>45.77485809505302</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1">
+      <c r="A189" s="15">
+        <v>32.561445453993244</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1">
+      <c r="A190" s="15">
+        <v>58.733083101591831</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1">
+      <c r="A191" s="15">
+        <v>54.14418962658084</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1">
+      <c r="A192" s="15">
+        <v>30.812619506228234</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1">
+      <c r="A193" s="15">
+        <v>92.304656660758866</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1">
+      <c r="A194" s="15">
+        <v>39.329092456027865</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1">
+      <c r="A195" s="15">
+        <v>50.524832247126284</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1">
+      <c r="A196" s="15">
+        <v>31.928302756713844</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1">
+      <c r="A197" s="15">
+        <v>37.989236824214458</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1">
+      <c r="A198" s="15">
+        <v>46.942548611502531</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1">
+      <c r="A199" s="15">
+        <v>44.546492085161987</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1">
+      <c r="A200" s="15">
+        <v>34.785326840355992</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1">
+      <c r="A201" s="15">
+        <v>55.360773726037507</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="15">
+        <v>44.583323970004095</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="15">
+        <v>51.334447207766225</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="15">
+        <v>22.049299769270558</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="15">
+        <v>67.12353898825269</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="15">
+        <v>51.43348741741498</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="15">
+        <v>51.851061941192299</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="15">
+        <v>61.899850011110217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="15">
+        <v>45.089113454926675</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="15">
+        <v>58.022351957847448</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="15">
+        <v>27.918169643776512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="15">
+        <v>48.252400632490939</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="15">
+        <v>50.504048652608617</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1">
+      <c r="A14" s="15">
+        <v>46.940464063830234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1">
+      <c r="A15" s="15">
+        <v>32.477745204184998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1">
+      <c r="A16" s="15">
+        <v>47.776046232762582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1">
+      <c r="A17" s="15">
+        <v>52.364536146374576</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1">
+      <c r="A18" s="15">
+        <v>45.500856174103568</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1">
+      <c r="A19" s="15">
+        <v>55.052096044162909</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1">
+      <c r="A20" s="15">
+        <v>50.685613161086344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1">
+      <c r="A21" s="15">
+        <v>49.66952996775624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1">
+      <c r="A22" s="15">
+        <v>104.0837872400076</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1">
+      <c r="A23" s="15">
+        <v>48.138533562033437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1">
+      <c r="A24" s="15">
+        <v>51.306818862784155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1">
+      <c r="A25" s="15">
+        <v>50.20944889961028</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1">
+      <c r="A26" s="15">
+        <v>75.063939489551288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1">
+      <c r="A27" s="15">
+        <v>45.850919890213376</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1">
+      <c r="A28" s="15">
+        <v>61.182874319803965</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1">
+      <c r="A29" s="15">
+        <v>53.242645886564432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1">
+      <c r="A30" s="15">
+        <v>48.457622052033251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1">
+      <c r="A31" s="15">
+        <v>50.141780231489143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1">
+      <c r="A32" s="15">
+        <v>54.727203415741691</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1">
+      <c r="A33" s="15">
+        <v>41.170085502511725</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1">
+      <c r="A34" s="15">
+        <v>45.643499747389342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1">
+      <c r="A35" s="15">
+        <v>49.679103878592088</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1">
+      <c r="A36" s="15">
+        <v>48.057261654852617</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1">
+      <c r="A37" s="15">
+        <v>69.936980427049335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1">
+      <c r="A38" s="15">
+        <v>49.69352250939118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1">
+      <c r="A39" s="15">
+        <v>68.62388039969656</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1">
+      <c r="A40" s="15">
+        <v>49.630861611768701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1">
+      <c r="A41" s="15">
+        <v>46.252110620339266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1">
+      <c r="A42" s="15">
+        <v>33.849920369473907</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1">
+      <c r="A43" s="15">
+        <v>61.040272273906567</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1">
+      <c r="A44" s="15">
+        <v>51.026349773822112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1">
+      <c r="A45" s="15">
+        <v>25.437813575006874</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1">
+      <c r="A46" s="15">
+        <v>42.412842605243902</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1">
+      <c r="A47" s="15">
+        <v>62.686303636400751</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1">
+      <c r="A48" s="15">
+        <v>42.704975764122004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1">
+      <c r="A49" s="15">
+        <v>49.587829692225341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1">
+      <c r="A50" s="15">
+        <v>40.78205054740252</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1">
+      <c r="A51" s="15">
+        <v>41.946539670316461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1">
+      <c r="A52" s="15">
+        <v>45.353919743322727</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1">
+      <c r="A53" s="15">
+        <v>51.583911931211553</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1">
+      <c r="A54" s="15">
+        <v>43.714457679757274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1">
+      <c r="A55" s="15">
+        <v>52.37259939470421</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1">
+      <c r="A56" s="15">
+        <v>36.057837306818556</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1">
+      <c r="A57" s="15">
+        <v>52.312866521311008</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1">
+      <c r="A58" s="15">
+        <v>50.898708249164237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1">
+      <c r="A59" s="15">
+        <v>41.696665737883528</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1">
+      <c r="A60" s="15">
+        <v>44.350601057959913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1">
+      <c r="A61" s="15">
+        <v>58.236466252153789</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1">
+      <c r="A62" s="15">
+        <v>19.574030505252157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1">
+      <c r="A63" s="15">
+        <v>56.080188977948879</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1">
+      <c r="A64" s="15">
+        <v>30.680745556369434</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1">
+      <c r="A65" s="15">
+        <v>-12.204560354287352</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1">
+      <c r="A66" s="15">
+        <v>45.220203620598937</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1">
+      <c r="A67" s="15">
+        <v>17.633038518680848</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1">
+      <c r="A68" s="15">
+        <v>52.558418096840398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1">
+      <c r="A69" s="15">
+        <v>53.918768547743881</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1">
+      <c r="A70" s="15">
+        <v>56.972852118665365</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1">
+      <c r="A71" s="15">
+        <v>58.026408528720026</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1">
+      <c r="A72" s="15">
+        <v>42.542720247102906</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1">
+      <c r="A73" s="15">
+        <v>48.323793455863751</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1">
+      <c r="A74" s="15">
+        <v>50.092658671687573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1">
+      <c r="A75" s="15">
+        <v>45.229895119984732</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1">
+      <c r="A76" s="15">
+        <v>52.728573385504006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1">
+      <c r="A77" s="15">
+        <v>71.899363117058016</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1">
+      <c r="A78" s="15">
+        <v>44.513348927234212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1">
+      <c r="A79" s="15">
+        <v>63.77864435299476</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1">
+      <c r="A80" s="15">
+        <v>46.436575656511899</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1">
+      <c r="A81" s="15">
+        <v>34.887998227138411</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1">
+      <c r="A82" s="15">
+        <v>58.462021678261699</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1">
+      <c r="A83" s="15">
+        <v>88.463061624052457</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1">
+      <c r="A84" s="15">
+        <v>67.934703645557789</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1">
+      <c r="A85" s="15">
+        <v>42.4628425000082</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1">
+      <c r="A86" s="15">
+        <v>61.204939847809861</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1">
+      <c r="A87" s="15">
+        <v>30.712805609794106</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1">
+      <c r="A88" s="15">
+        <v>51.861494525023879</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1">
+      <c r="A89" s="15">
+        <v>54.918184385449301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1">
+      <c r="A90" s="15">
+        <v>32.623603626472288</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1">
+      <c r="A91" s="15">
+        <v>45.728197050296096</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1">
+      <c r="A92" s="15">
+        <v>43.597926883139415</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1">
+      <c r="A93" s="15">
+        <v>23.030243265509874</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1">
+      <c r="A94" s="15">
+        <v>56.656211338615392</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1">
+      <c r="A95" s="15">
+        <v>58.795607188661208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1">
+      <c r="A96" s="15">
+        <v>45.169194495007787</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1">
+      <c r="A97" s="15">
+        <v>58.697729354499721</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1">
+      <c r="A98" s="15">
+        <v>36.002693637123954</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1">
+      <c r="A99" s="15">
+        <v>48.499856032151719</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1">
+      <c r="A100" s="15">
+        <v>55.574792339894898</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1">
+      <c r="A101" s="15">
+        <v>46.620051006744809</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1">
+      <c r="A102" s="15">
+        <v>35.192832980731971</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1">
+      <c r="A103" s="15">
+        <v>45.186132660524521</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1">
+      <c r="A104" s="15">
+        <v>41.440002205863252</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1">
+      <c r="A105" s="15">
+        <v>56.867720158468678</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1">
+      <c r="A106" s="15">
+        <v>53.295696930395053</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1">
+      <c r="A107" s="15">
+        <v>64.889311035448912</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1">
+      <c r="A108" s="15">
+        <v>54.26200612782938</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1">
+      <c r="A109" s="15">
+        <v>52.544742047961151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1">
+      <c r="A110" s="15">
+        <v>40.523359873000345</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1">
+      <c r="A111" s="15">
+        <v>46.446031997827333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1">
+      <c r="A112" s="15">
+        <v>51.779561027162579</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1">
+      <c r="A113" s="15">
+        <v>49.014194362670722</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1">
+      <c r="A114" s="15">
+        <v>61.819034752771493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1">
+      <c r="A115" s="15">
+        <v>29.985690829060811</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1">
+      <c r="A116" s="15">
+        <v>53.876783794405526</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1">
+      <c r="A117" s="15">
+        <v>61.539812338110224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1">
+      <c r="A118" s="15">
+        <v>43.974827192966821</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1">
+      <c r="A119" s="15">
+        <v>45.551346114953439</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1">
+      <c r="A120" s="15">
+        <v>50.084261318972246</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1">
+      <c r="A121" s="15">
+        <v>62.01638668237868</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1">
+      <c r="A122" s="15">
+        <v>56.175165413494142</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1">
+      <c r="A123" s="15">
+        <v>47.456388751873405</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1">
+      <c r="A124" s="15">
+        <v>23.038518892969723</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1">
+      <c r="A125" s="15">
+        <v>51.998571819711955</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1">
+      <c r="A126" s="15">
+        <v>44.601782349880828</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1">
+      <c r="A127" s="15">
+        <v>62.587679284555179</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1">
+      <c r="A128" s="15">
+        <v>47.981402959431179</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1">
+      <c r="A129" s="15">
+        <v>57.746497474145698</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1">
+      <c r="A130" s="15">
+        <v>39.268318019440855</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1">
+      <c r="A131" s="15">
+        <v>40.593793682408517</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1">
+      <c r="A132" s="15">
+        <v>68.981146636466704</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1">
+      <c r="A133" s="15">
+        <v>52.193130853285872</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1">
+      <c r="A134" s="15">
+        <v>33.76091170487512</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1">
+      <c r="A135" s="15">
+        <v>50.171022483272182</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1">
+      <c r="A136" s="15">
+        <v>60.620977113570738</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1">
+      <c r="A137" s="15">
+        <v>39.784466650531179</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1">
+      <c r="A138" s="15">
+        <v>63.595008502574217</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1">
+      <c r="A139" s="15">
+        <v>50.529974380471813</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1">
+      <c r="A140" s="15">
+        <v>44.190483929113618</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1">
+      <c r="A141" s="15">
+        <v>53.542574514794453</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1">
+      <c r="A142" s="15">
+        <v>39.477142117733074</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1">
+      <c r="A143" s="15">
+        <v>43.732251991134852</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1">
+      <c r="A144" s="15">
+        <v>41.959239458331346</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1">
+      <c r="A145" s="15">
+        <v>38.792495139376115</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1">
+      <c r="A146" s="15">
+        <v>45.854655573468918</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1">
+      <c r="A147" s="15">
+        <v>60.354771536885288</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1">
+      <c r="A148" s="15">
+        <v>62.219049231687123</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1">
+      <c r="A149" s="15">
+        <v>45.52130275469495</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1">
+      <c r="A150" s="15">
+        <v>49.924428774898615</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1">
+      <c r="A151" s="15">
+        <v>37.764960053846963</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1">
+      <c r="A152" s="15">
+        <v>51.658304855015182</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1">
+      <c r="A153" s="15">
+        <v>29.707599198619082</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1">
+      <c r="A154" s="15">
+        <v>46.231772923103257</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1">
+      <c r="A155" s="15">
+        <v>55.298751839191588</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1">
+      <c r="A156" s="15">
+        <v>41.922572445910873</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1">
+      <c r="A157" s="15">
+        <v>48.262933858575977</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1">
+      <c r="A158" s="15">
+        <v>44.476607929252594</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1">
+      <c r="A159" s="15">
+        <v>48.533536089568322</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1">
+      <c r="A160" s="15">
+        <v>50.891699221834102</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1">
+      <c r="A161" s="15">
+        <v>55.942113835665133</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1">
+      <c r="A162" s="15">
+        <v>46.056943456482507</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1">
+      <c r="A163" s="15">
+        <v>58.216244888538114</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1">
+      <c r="A164" s="15">
+        <v>52.217003100011731</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1">
+      <c r="A165" s="15">
+        <v>48.210090208151811</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1">
+      <c r="A166" s="15">
+        <v>62.0879827797365</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1">
+      <c r="A167" s="15">
+        <v>64.228945367396022</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1">
+      <c r="A168" s="15">
+        <v>20.131492243533419</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1">
+      <c r="A169" s="15">
+        <v>110.64886999472245</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1">
+      <c r="A170" s="15">
+        <v>32.941935085315933</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1">
+      <c r="A171" s="15">
+        <v>38.163113947951629</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1">
+      <c r="A172" s="15">
+        <v>28.014152026886876</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1">
+      <c r="A173" s="15">
+        <v>37.31657769048735</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1">
+      <c r="A174" s="15">
+        <v>62.196798206891565</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1">
+      <c r="A175" s="15">
+        <v>71.437812193563587</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1">
+      <c r="A176" s="15">
+        <v>60.833312973349301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1">
+      <c r="A177" s="15">
+        <v>47.624045845330549</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1">
+      <c r="A178" s="15">
+        <v>47.969146974682602</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1">
+      <c r="A179" s="15">
+        <v>41.411513183912675</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1">
+      <c r="A180" s="15">
+        <v>40.775685771027305</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1">
+      <c r="A181" s="15">
+        <v>37.87482306899652</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1">
+      <c r="A182" s="15">
+        <v>36.109009913511997</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1">
+      <c r="A183" s="15">
+        <v>58.135307145492682</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1">
+      <c r="A184" s="15">
+        <v>66.807164265069304</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1">
+      <c r="A185" s="15">
+        <v>53.720121887290681</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1">
+      <c r="A186" s="15">
+        <v>62.774840258291775</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1">
+      <c r="A187" s="15">
+        <v>47.137994499823385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1">
+      <c r="A188" s="15">
+        <v>42.151912174740652</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1">
+      <c r="A189" s="15">
+        <v>51.059677931739131</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1">
+      <c r="A190" s="15">
+        <v>28.741581848902058</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1">
+      <c r="A191" s="15">
+        <v>41.54036883231511</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1">
+      <c r="A192" s="15">
+        <v>40.373172130813913</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1">
+      <c r="A193" s="15">
+        <v>55.702822738870395</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1">
+      <c r="A194" s="15">
+        <v>11.42434803408441</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1">
+      <c r="A195" s="15">
+        <v>49.053571153044992</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1">
+      <c r="A196" s="15">
+        <v>45.577680998383187</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1">
+      <c r="A197" s="15">
+        <v>39.826789789901085</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1">
+      <c r="A198" s="15">
+        <v>38.979676161116856</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1">
+      <c r="A199" s="15">
+        <v>51.981276736960531</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1">
+      <c r="A200" s="15">
+        <v>20.98298801463104</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1">
+      <c r="A201" s="15">
+        <v>46.144000858098984</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -909,11 +5165,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="44" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
+      <c r="A1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>58</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -922,37 +5178,37 @@
     </row>
     <row r="2" spans="1:6" ht="23.95" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3">
+        <v>59</v>
+      </c>
+      <c r="B2" s="4">
         <v>50</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
     </row>
     <row r="3" spans="1:6" ht="23.95" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
+        <v>61</v>
+      </c>
+      <c r="B3" s="4">
         <v>10</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" ht="23.95" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3">
+        <v>63</v>
+      </c>
+      <c r="B4" s="4">
         <v>60</v>
       </c>
       <c r="C4" s="1"/>
@@ -965,16 +5221,16 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:6" ht="23.95" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4">
+        <v>65</v>
+      </c>
+      <c r="B6" s="5">
         <f>(B4-B2)/B3</f>
         <v>1</v>
       </c>
@@ -985,39 +5241,39 @@
     </row>
     <row r="7" spans="1:6" ht="23.95" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5">
+        <v>66</v>
+      </c>
+      <c r="B7" s="6">
         <f>_xlfn.NORM.S.DIST(B6,TRUE)</f>
         <v>0.84134474606854304</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
     </row>
     <row r="8" spans="1:6" ht="23.95" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="5">
+        <v>68</v>
+      </c>
+      <c r="B8" s="6">
         <f>1-B7</f>
         <v>0.15865525393145696</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:6" ht="23.95" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="5">
+        <v>70</v>
+      </c>
+      <c r="B9" s="6">
         <f>_xlfn.NORM.DIST(B4,B2,B3,TRUE)</f>
         <v>0.84134474606854304</v>
       </c>
@@ -1031,30 +5287,30 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:6" ht="23.95" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="3">
+        <v>72</v>
+      </c>
+      <c r="B11" s="4">
         <v>60</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:6" ht="23.95" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="3">
+        <v>74</v>
+      </c>
+      <c r="B12" s="4">
         <v>70</v>
       </c>
       <c r="C12" s="1"/>
@@ -1064,9 +5320,9 @@
     </row>
     <row r="13" spans="1:6" ht="23.95" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="5">
+        <v>75</v>
+      </c>
+      <c r="B13" s="6">
         <f>_xlfn.NORM.S.DIST((B12-B2)/B3,TRUE)-_xlfn.NORM.S.DIST((B11-B2)/B3,TRUE)</f>
         <v>0.13590512198327775</v>
       </c>
@@ -1080,7 +5336,7 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -1095,9 +5351,9 @@
     </row>
     <row r="16" spans="1:6" ht="23.95" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="6">
+        <v>77</v>
+      </c>
+      <c r="B16" s="7">
         <v>0.9</v>
       </c>
       <c r="C16" s="1"/>
@@ -1107,9 +5363,9 @@
     </row>
     <row r="17" spans="1:6" ht="23.95" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="4">
+        <v>78</v>
+      </c>
+      <c r="B17" s="5">
         <f>_xlfn.NORM.S.INV(B16)</f>
         <v>1.2815515655446006</v>
       </c>
@@ -1120,9 +5376,9 @@
     </row>
     <row r="18" spans="1:6" ht="23.95" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="7">
+        <v>79</v>
+      </c>
+      <c r="B18" s="8">
         <f>B2+B3*B17</f>
         <v>62.815515655446006</v>
       </c>
@@ -1133,9 +5389,9 @@
     </row>
     <row r="19" spans="1:6" ht="23.95" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="7">
+        <v>80</v>
+      </c>
+      <c r="B19" s="8">
         <f>_xlfn.NORM.INV(B16,B2,B3)</f>
         <v>62.815515655446006</v>
       </c>
@@ -1162,9 +5418,9 @@
     </row>
     <row r="22" spans="1:6" ht="23.95" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="6">
+        <v>81</v>
+      </c>
+      <c r="B22" s="7">
         <v>0.95</v>
       </c>
       <c r="C22" s="1"/>
@@ -1174,9 +5430,9 @@
     </row>
     <row r="23" spans="1:6" ht="23.95" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="5">
+        <v>82</v>
+      </c>
+      <c r="B23" s="6">
         <f>(1-B22)/2</f>
         <v>2.5000000000000022E-2</v>
       </c>
@@ -1187,9 +5443,9 @@
     </row>
     <row r="24" spans="1:6" ht="23.95" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="7">
+        <v>83</v>
+      </c>
+      <c r="B24" s="8">
         <f>_xlfn.NORM.INV(B23,B2,B3)</f>
         <v>30.400360154599465</v>
       </c>
@@ -1200,9 +5456,9 @@
     </row>
     <row r="25" spans="1:6" ht="23.95" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="7">
+        <v>84</v>
+      </c>
+      <c r="B25" s="8">
         <f>_xlfn.NORM.INV(1-B23,B2,B3)</f>
         <v>69.599639845400532</v>
       </c>
@@ -1244,12 +5500,1048 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="15">
+        <v>36.276933564652332</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="15">
+        <v>37.212483542398708</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="15">
+        <v>35.639479476123725</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="15">
+        <v>35.015683039221358</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="15">
+        <v>38.973432309598977</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1">
+      <c r="A7" s="15">
+        <v>35.288905299842419</v>
+      </c>
+      <c r="C7" s="18"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1">
+      <c r="A8" s="15">
+        <v>43.675716818946363</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1">
+      <c r="A9" s="15">
+        <v>39.659870499249976</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1">
+      <c r="A10" s="15">
+        <v>28.705085302838512</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1">
+      <c r="A11" s="15">
+        <v>46.113870484277946</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1">
+      <c r="A12" s="15">
+        <v>32.624634396630668</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1">
+      <c r="A13" s="15">
+        <v>29.600658843246485</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1">
+      <c r="A14" s="15">
+        <v>40.036980480828731</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1">
+      <c r="A15" s="15">
+        <v>34.70426640911549</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1">
+      <c r="A16" s="15">
+        <v>37.781947730172071</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1">
+      <c r="A17" s="15">
+        <v>34.479018435346106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1">
+      <c r="A18" s="15">
+        <v>47.176194669335828</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1">
+      <c r="A19" s="15">
+        <v>41.85250135784122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1">
+      <c r="A20" s="15">
+        <v>34.338404272432449</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1">
+      <c r="A21" s="15">
+        <v>40.546205317695261</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1">
+      <c r="A22" s="15">
+        <v>41.98711328472664</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1">
+      <c r="A23" s="15">
+        <v>43.288398439143975</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1">
+      <c r="A24" s="15">
+        <v>43.454574684605518</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1">
+      <c r="A25" s="15">
+        <v>38.05419126548675</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1">
+      <c r="A26" s="15">
+        <v>43.345643923664916</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1">
+      <c r="A27" s="15">
+        <v>40.602826762940104</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1">
+      <c r="A28" s="15">
+        <v>35.449857059653674</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1">
+      <c r="A29" s="15">
+        <v>36.965660500573406</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1">
+      <c r="A30" s="15">
+        <v>38.494861421933109</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1">
+      <c r="A31" s="15">
+        <v>37.043023220290131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1">
+      <c r="A32" s="15">
+        <v>31.133231850280414</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1">
+      <c r="A33" s="15">
+        <v>26.547409544307861</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1">
+      <c r="A34" s="15">
+        <v>25.231197992869959</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1">
+      <c r="A35" s="15">
+        <v>34.240362923682653</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1">
+      <c r="A36" s="15">
+        <v>30.949089105423791</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1">
+      <c r="A37" s="15">
+        <v>37.585267238271342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1">
+      <c r="A38" s="15">
+        <v>39.673734962202417</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1">
+      <c r="A39" s="15">
+        <v>39.408101091742523</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1">
+      <c r="A40" s="15">
+        <v>33.457981885760276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1">
+      <c r="A41" s="15">
+        <v>33.556803869418218</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1">
+      <c r="A42" s="15">
+        <v>38.341489215237772</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1">
+      <c r="A43" s="15">
+        <v>43.443655483244918</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1">
+      <c r="A44" s="15">
+        <v>32.544513154120381</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1">
+      <c r="A45" s="15">
+        <v>30.836390642576227</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1">
+      <c r="A46" s="15">
+        <v>33.085893909088711</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1">
+      <c r="A47" s="15">
+        <v>34.667812451561865</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1">
+      <c r="A48" s="15">
+        <v>44.875501095715734</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1">
+      <c r="A49" s="15">
+        <v>30.921848787560336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1">
+      <c r="A50" s="15">
+        <v>49.148823252143913</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1">
+      <c r="A51" s="15">
+        <v>33.690535437127458</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1">
+      <c r="A52" s="15">
+        <v>38.056780248257553</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1">
+      <c r="A53" s="15">
+        <v>35.928017547539064</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1">
+      <c r="A54" s="15">
+        <v>27.551339436887751</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1">
+      <c r="A55" s="15">
+        <v>34.120468412276793</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1">
+      <c r="A56" s="15">
+        <v>47.383916956604878</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1">
+      <c r="A57" s="15">
+        <v>27.175412821590594</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1">
+      <c r="A58" s="15">
+        <v>36.928034334868862</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1">
+      <c r="A59" s="15">
+        <v>47.259996458911331</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1">
+      <c r="A60" s="15">
+        <v>31.621974384651867</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1">
+      <c r="A61" s="15">
+        <v>42.18066464773564</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1">
+      <c r="A62" s="15">
+        <v>37.191211497401035</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1">
+      <c r="A63" s="15">
+        <v>33.505605217495329</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1">
+      <c r="A64" s="15">
+        <v>46.342692737621832</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1">
+      <c r="A65" s="15">
+        <v>33.263402259259543</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1">
+      <c r="A66" s="15">
+        <v>25.582255920098014</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1">
+      <c r="A67" s="15">
+        <v>34.877706772836675</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1">
+      <c r="A68" s="15">
+        <v>37.296362892278651</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1">
+      <c r="A69" s="15">
+        <v>38.571324118181231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1">
+      <c r="A70" s="15">
+        <v>29.72673380533092</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1">
+      <c r="A71" s="15">
+        <v>43.765248122025461</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1">
+      <c r="A72" s="15">
+        <v>41.627080081287609</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1">
+      <c r="A73" s="15">
+        <v>32.376537350320156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1">
+      <c r="A74" s="15">
+        <v>44.047178598305841</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1">
+      <c r="A75" s="15">
+        <v>28.14708556984327</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1">
+      <c r="A76" s="15">
+        <v>31.349846283299087</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1">
+      <c r="A77" s="15">
+        <v>39.482689179392416</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1">
+      <c r="A78" s="15">
+        <v>38.779652122860952</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1">
+      <c r="A79" s="15">
+        <v>38.57886602882796</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1">
+      <c r="A80" s="15">
+        <v>33.586484329082388</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1">
+      <c r="A81" s="15">
+        <v>34.294519868213229</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1">
+      <c r="A82" s="15">
+        <v>32.41271039383404</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1">
+      <c r="A83" s="15">
+        <v>34.142570946496122</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1">
+      <c r="A84" s="15">
+        <v>42.531292622997107</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1">
+      <c r="A85" s="15">
+        <v>37.649086005167611</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1">
+      <c r="A86" s="15">
+        <v>34.941076879313279</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1">
+      <c r="A87" s="15">
+        <v>35.536828037063401</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1">
+      <c r="A88" s="15">
+        <v>37.835441078784008</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1">
+      <c r="A89" s="15">
+        <v>30.368649106778982</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1">
+      <c r="A90" s="15">
+        <v>25.014262592330276</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1">
+      <c r="A91" s="15">
+        <v>26.106646991745915</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1">
+      <c r="A92" s="15">
+        <v>34.650840260671281</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1">
+      <c r="A93" s="15">
+        <v>30.608793933373676</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1">
+      <c r="A94" s="15">
+        <v>42.318676172716906</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1">
+      <c r="A95" s="15">
+        <v>39.052077850681556</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1">
+      <c r="A96" s="15">
+        <v>36.368162231612743</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1">
+      <c r="A97" s="15">
+        <v>38.082545640745451</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1">
+      <c r="A98" s="15">
+        <v>39.05160365476636</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1">
+      <c r="A99" s="15">
+        <v>37.019542171432981</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1">
+      <c r="A100" s="15">
+        <v>43.775316458262964</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1">
+      <c r="A101" s="15">
+        <v>33.819535266324593</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1">
+      <c r="A102" s="15">
+        <v>61.464097568870351</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1">
+      <c r="A103" s="15">
+        <v>56.779055352698904</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1">
+      <c r="A104" s="15">
+        <v>62.670398684427965</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1">
+      <c r="A105" s="15">
+        <v>73.751809940192487</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1">
+      <c r="A106" s="15">
+        <v>61.800843709988818</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1">
+      <c r="A107" s="15">
+        <v>55.373944166260628</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1">
+      <c r="A108" s="15">
+        <v>63.068204514980742</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1">
+      <c r="A109" s="15">
+        <v>71.586076108806807</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1">
+      <c r="A110" s="15">
+        <v>56.24082895519804</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1">
+      <c r="A111" s="15">
+        <v>61.6753262137495</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1">
+      <c r="A112" s="15">
+        <v>56.93632611495407</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1">
+      <c r="A113" s="15">
+        <v>59.051523603020968</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1">
+      <c r="A114" s="15">
+        <v>57.32545087575437</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1">
+      <c r="A115" s="15">
+        <v>65.880727663462551</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1">
+      <c r="A116" s="15">
+        <v>60.397191824618311</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1">
+      <c r="A117" s="15">
+        <v>68.572389036669335</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1">
+      <c r="A118" s="15">
+        <v>62.414335418119315</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1">
+      <c r="A119" s="15">
+        <v>61.172005219132537</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1">
+      <c r="A120" s="15">
+        <v>66.934417907137245</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1">
+      <c r="A121" s="15">
+        <v>60.797748822549465</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1">
+      <c r="A122" s="15">
+        <v>64.808955302109922</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1">
+      <c r="A123" s="15">
+        <v>65.623525673374814</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1">
+      <c r="A124" s="15">
+        <v>58.469063244083806</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1">
+      <c r="A125" s="15">
+        <v>62.831208676459113</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1">
+      <c r="A126" s="15">
+        <v>66.159947542461353</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1">
+      <c r="A127" s="15">
+        <v>66.86970214005477</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1">
+      <c r="A128" s="15">
+        <v>58.811440190429188</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1">
+      <c r="A129" s="15">
+        <v>56.480164667592014</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1">
+      <c r="A130" s="15">
+        <v>67.270150214608236</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1">
+      <c r="A131" s="15">
+        <v>57.861621245659549</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1">
+      <c r="A132" s="15">
+        <v>66.782331525938133</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1">
+      <c r="A133" s="15">
+        <v>63.58405032228729</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1">
+      <c r="A134" s="15">
+        <v>67.54402046997609</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1">
+      <c r="A135" s="15">
+        <v>69.946875229688843</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1">
+      <c r="A136" s="15">
+        <v>59.248140321978966</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1">
+      <c r="A137" s="15">
+        <v>65.31387542060358</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1">
+      <c r="A138" s="15">
+        <v>53.913691619685814</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1">
+      <c r="A139" s="15">
+        <v>63.595214975168055</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1">
+      <c r="A140" s="15">
+        <v>59.620405974427783</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1">
+      <c r="A141" s="15">
+        <v>50.953337971226844</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1">
+      <c r="A142" s="15">
+        <v>56.665762779172603</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1">
+      <c r="A143" s="15">
+        <v>63.858801892323001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1">
+      <c r="A144" s="15">
+        <v>59.816653526960238</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1">
+      <c r="A145" s="15">
+        <v>58.720316519026355</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1">
+      <c r="A146" s="15">
+        <v>70.515316260734039</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1">
+      <c r="A147" s="15">
+        <v>62.859127955355163</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1">
+      <c r="A148" s="15">
+        <v>64.436237602234272</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1">
+      <c r="A149" s="15">
+        <v>63.493875274325575</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1">
+      <c r="A150" s="15">
+        <v>69.570450236903511</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1">
+      <c r="A151" s="15">
+        <v>53.580864727368095</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1">
+      <c r="A152" s="15">
+        <v>65.075354610557142</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1">
+      <c r="A153" s="15">
+        <v>64.57519291077827</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1">
+      <c r="A154" s="15">
+        <v>63.391643779972902</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1">
+      <c r="A155" s="15">
+        <v>65.896750387576475</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1">
+      <c r="A156" s="15">
+        <v>66.900185254800618</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1">
+      <c r="A157" s="15">
+        <v>63.349568195108922</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1">
+      <c r="A158" s="15">
+        <v>60.940862131249013</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1">
+      <c r="A159" s="15">
+        <v>56.076199787454847</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1">
+      <c r="A160" s="15">
+        <v>57.119036994174543</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1">
+      <c r="A161" s="15">
+        <v>64.833109285659546</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1">
+      <c r="A162" s="15">
+        <v>61.748600986346212</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1">
+      <c r="A163" s="15">
+        <v>65.680457529471013</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1">
+      <c r="A164" s="15">
+        <v>68.122561677959666</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1">
+      <c r="A165" s="15">
+        <v>61.885813200223282</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1">
+      <c r="A166" s="15">
+        <v>64.160723758977682</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1">
+      <c r="A167" s="15">
+        <v>69.259878100937883</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1">
+      <c r="A168" s="15">
+        <v>58.244589617257176</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1">
+      <c r="A169" s="15">
+        <v>66.861575274173916</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1">
+      <c r="A170" s="15">
+        <v>65.634588119505821</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1">
+      <c r="A171" s="15">
+        <v>66.389064963591878</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1">
+      <c r="A172" s="15">
+        <v>66.939233976508476</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1">
+      <c r="A173" s="15">
+        <v>68.867062466027477</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1">
+      <c r="A174" s="15">
+        <v>76.136767408424333</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1">
+      <c r="A175" s="15">
+        <v>59.32192764987942</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1">
+      <c r="A176" s="15">
+        <v>65.273688750755227</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1">
+      <c r="A177" s="15">
+        <v>68.37882869420261</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1">
+      <c r="A178" s="15">
+        <v>60.566493999237707</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1">
+      <c r="A179" s="15">
+        <v>66.691112642045866</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1">
+      <c r="A180" s="15">
+        <v>57.403228618526008</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1">
+      <c r="A181" s="15">
+        <v>66.731718204712351</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1">
+      <c r="A182" s="15">
+        <v>65.822301828076647</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1">
+      <c r="A183" s="15">
+        <v>57.209747289593075</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1">
+      <c r="A184" s="15">
+        <v>70.059378503963885</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1">
+      <c r="A185" s="15">
+        <v>71.896074907338686</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1">
+      <c r="A186" s="15">
+        <v>66.255976669970607</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1">
+      <c r="A187" s="15">
+        <v>71.94521231132407</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1">
+      <c r="A188" s="15">
+        <v>64.50975488507396</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1">
+      <c r="A189" s="15">
+        <v>69.850486097663676</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1">
+      <c r="A190" s="15">
+        <v>63.78498386336463</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1">
+      <c r="A191" s="15">
+        <v>59.773307887165849</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1">
+      <c r="A192" s="15">
+        <v>66.562126752602396</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1">
+      <c r="A193" s="15">
+        <v>66.878580665469173</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1">
+      <c r="A194" s="15">
+        <v>62.438097225255326</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1">
+      <c r="A195" s="15">
+        <v>70.347692171195717</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1">
+      <c r="A196" s="15">
+        <v>56.359576248860812</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1">
+      <c r="A197" s="15">
+        <v>64.947474346662119</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1">
+      <c r="A198" s="15">
+        <v>64.648923557647464</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1">
+      <c r="A199" s="15">
+        <v>63.686025498670119</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1">
+      <c r="A200" s="15">
+        <v>58.296193500596658</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1">
+      <c r="A201" s="15">
+        <v>62.217355862155749</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1266,20 +6558,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="44" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>32</v>
+      <c r="A1" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1292,29 +6584,29 @@
       <c r="N1" s="1"/>
     </row>
     <row r="2" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A2" s="8">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="10">
         <v>35</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="12">
         <f>(A2-0.5)/$H$2</f>
         <v>4.1666666666666664E-2</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <f>_xlfn.NORM.S.INV(C2)</f>
         <v>-1.7316643961222451</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="5">
         <f>$H$3+$H$4*D2</f>
         <v>34.423768669978713</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H2" s="10">
+        <v>90</v>
+      </c>
+      <c r="H2" s="11">
         <f>COUNT(B2:B13)</f>
         <v>12</v>
       </c>
@@ -1326,29 +6618,29 @@
       <c r="N2" s="1"/>
     </row>
     <row r="3" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="10">
         <v>39</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="12">
         <f t="shared" ref="C3:C13" si="0">(A3-0.5)/$H$2</f>
         <v>0.125</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="5">
         <f t="shared" ref="D3:D13" si="1">_xlfn.NORM.S.INV(C3)</f>
         <v>-1.1503493803760083</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="5">
         <f t="shared" ref="E3:E13" si="2">$H$3+$H$4*D3</f>
         <v>39.652667053034193</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="4">
+        <v>91</v>
+      </c>
+      <c r="H3" s="5">
         <f>AVERAGE(B2:B13)</f>
         <v>50</v>
       </c>
@@ -1360,29 +6652,29 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="10">
         <v>42</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="12">
         <f t="shared" si="0"/>
         <v>0.20833333333333334</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <f t="shared" si="1"/>
         <v>-0.81221780149991241</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="5">
         <f t="shared" si="2"/>
         <v>42.694143048240605</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="4">
+        <v>92</v>
+      </c>
+      <c r="H4" s="5">
         <f>_xlfn.STDEV.S(B2:B13)</f>
         <v>8.9949480770647536</v>
       </c>
@@ -1394,21 +6686,21 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>45</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="12">
         <f t="shared" si="0"/>
         <v>0.29166666666666669</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="5">
         <f t="shared" si="1"/>
         <v>-0.54852228269809788</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <f t="shared" si="2"/>
         <v>45.066070548017578</v>
       </c>
@@ -1423,21 +6715,21 @@
       <c r="N5" s="1"/>
     </row>
     <row r="6" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>47</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="12">
         <f t="shared" si="0"/>
         <v>0.375</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="5">
         <f t="shared" si="1"/>
         <v>-0.3186393639643752</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <f t="shared" si="2"/>
         <v>47.133855465831509</v>
       </c>
@@ -1452,21 +6744,21 @@
       <c r="N6" s="1"/>
     </row>
     <row r="7" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="10">
         <v>49</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="12">
         <f t="shared" si="0"/>
         <v>0.45833333333333331</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="5">
         <f t="shared" si="1"/>
         <v>-0.10463345561407539</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <f t="shared" si="2"/>
         <v>49.058827499627533</v>
       </c>
@@ -1481,21 +6773,21 @@
       <c r="N7" s="1"/>
     </row>
     <row r="8" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A8" s="8">
+      <c r="A8" s="9">
         <v>7</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <v>51</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <f t="shared" si="0"/>
         <v>0.54166666666666663</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="5">
         <f t="shared" si="1"/>
         <v>0.10463345561407525</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="5">
         <f t="shared" si="2"/>
         <v>50.941172500372467</v>
       </c>
@@ -1510,21 +6802,21 @@
       <c r="N8" s="1"/>
     </row>
     <row r="9" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <v>53</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="5">
         <f t="shared" si="1"/>
         <v>0.3186393639643752</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="5">
         <f t="shared" si="2"/>
         <v>52.866144534168491</v>
       </c>
@@ -1539,21 +6831,21 @@
       <c r="N9" s="1"/>
     </row>
     <row r="10" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A10" s="8">
+      <c r="A10" s="9">
         <v>9</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="10">
         <v>55</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="12">
         <f t="shared" si="0"/>
         <v>0.70833333333333337</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="5">
         <f t="shared" si="1"/>
         <v>0.54852228269809822</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="5">
         <f t="shared" si="2"/>
         <v>54.933929451982429</v>
       </c>
@@ -1568,21 +6860,21 @@
       <c r="N10" s="1"/>
     </row>
     <row r="11" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11" s="10">
         <v>58</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="12">
         <f t="shared" si="0"/>
         <v>0.79166666666666663</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <f t="shared" si="1"/>
         <v>0.81221780149991241</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <f t="shared" si="2"/>
         <v>57.305856951759395</v>
       </c>
@@ -1597,21 +6889,21 @@
       <c r="N11" s="1"/>
     </row>
     <row r="12" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A12" s="8">
+      <c r="A12" s="9">
         <v>11</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="10">
         <v>61</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <f t="shared" si="0"/>
         <v>0.875</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="5">
         <f t="shared" si="1"/>
         <v>1.1503493803760083</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="5">
         <f t="shared" si="2"/>
         <v>60.347332946965807</v>
       </c>
@@ -1626,21 +6918,21 @@
       <c r="N12" s="1"/>
     </row>
     <row r="13" spans="1:14" ht="23.95" customHeight="1">
-      <c r="A13" s="8">
+      <c r="A13" s="9">
         <v>12</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="10">
         <v>65</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <f t="shared" si="0"/>
         <v>0.95833333333333337</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="5">
         <f t="shared" si="1"/>
         <v>1.7316643961222455</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="5">
         <f t="shared" si="2"/>
         <v>65.576231330021287</v>
       </c>
@@ -1688,7 +6980,7 @@
     </row>
     <row r="16" spans="1:14" ht="23.95" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1722,7 +7014,7 @@
     </row>
     <row r="18" spans="1:14" ht="23.95" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1740,7 +7032,7 @@
     </row>
     <row r="19" spans="1:14" ht="23.95" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1774,7 +7066,7 @@
     </row>
     <row r="21" spans="1:14" ht="23.95" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1792,7 +7084,7 @@
     </row>
     <row r="22" spans="1:14" ht="23.95" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1858,7 +7150,473 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="57" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="4" width="22" customWidth="1"/>
+    <col min="6" max="6" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="13">
+        <v>60</v>
+      </c>
+      <c r="C2" s="13">
+        <v>50</v>
+      </c>
+      <c r="D2" s="13">
+        <v>10</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13">
+        <v>42</v>
+      </c>
+      <c r="C3" s="13">
+        <v>30</v>
+      </c>
+      <c r="D3" s="13">
+        <v>6</v>
+      </c>
+      <c r="F3" s="18"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="F4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="F5" s="18"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="F6" s="18"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="F7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="13">
+        <v>4</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="13">
+        <v>5</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="13">
+        <v>5</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="13">
+        <v>6</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="13">
+        <v>10</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="C7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="13">
+        <v>50</v>
+      </c>
+      <c r="C2" s="13">
+        <v>10</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="13">
+        <v>65</v>
+      </c>
+      <c r="C3" s="13">
+        <v>10</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" s="13">
+        <v>50</v>
+      </c>
+      <c r="C4" s="13">
+        <v>15</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="E7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0</v>
+      </c>
+      <c r="C2" s="13">
+        <v>1</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="B3" s="13">
+        <v>50</v>
+      </c>
+      <c r="C3" s="13">
+        <v>10</v>
+      </c>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="13">
+        <v>100</v>
+      </c>
+      <c r="C4" s="13">
+        <v>15</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="13">
+        <v>10</v>
+      </c>
+      <c r="C5" s="13">
+        <v>3</v>
+      </c>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="E7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="7" max="7" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25" customHeight="1">
+      <c r="A2" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" s="13">
+        <v>62</v>
+      </c>
+      <c r="C2" s="13">
+        <v>50</v>
+      </c>
+      <c r="D2" s="13">
+        <v>8</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.75</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25" customHeight="1">
+      <c r="A3" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="13">
+        <v>62</v>
+      </c>
+      <c r="C3" s="13">
+        <v>65</v>
+      </c>
+      <c r="D3" s="13">
+        <v>6</v>
+      </c>
+      <c r="E3" s="13"/>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="G4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="G6" s="18"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="G7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="G4:G7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="13.6"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1">
+      <c r="A2" s="13">
+        <v>2</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="C3" s="18"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1">
+      <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1">
+      <c r="A5" s="13">
+        <v>2</v>
+      </c>
+      <c r="C5" s="18"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1">
+      <c r="A6" s="13">
+        <v>12</v>
+      </c>
+      <c r="C6" s="18"/>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="C7" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC92E8C-033F-428D-9349-6A4E62F344DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0398793E-B21E-484A-AA3E-76164D6B6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{BD5A4487-83A7-457A-9D5B-249C1402CFA0}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{1438BA25-5DE2-4CE4-BAFD-4ED64237E948}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -13,21 +13,22 @@
     <sheet name="QQ" sheetId="3" r:id="rId3"/>
     <sheet name="Z_skory" sheetId="4" r:id="rId4"/>
     <sheet name="Standardizace" sheetId="5" r:id="rId5"/>
-    <sheet name="Modely" sheetId="6" r:id="rId6"/>
-    <sheet name="Skaly" sheetId="7" r:id="rId7"/>
-    <sheet name="U01_reference" sheetId="8" r:id="rId8"/>
-    <sheet name="U02_standardizace" sheetId="9" r:id="rId9"/>
-    <sheet name="U03_model" sheetId="10" r:id="rId10"/>
-    <sheet name="U04_plochy" sheetId="11" r:id="rId11"/>
-    <sheet name="U05_percentily" sheetId="12" r:id="rId12"/>
-    <sheet name="U06_zaokrouhleni" sheetId="13" r:id="rId13"/>
-    <sheet name="U07_prevody" sheetId="14" r:id="rId14"/>
-    <sheet name="U08_pasmo" sheetId="15" r:id="rId15"/>
-    <sheet name="QQ_data" sheetId="16" r:id="rId16"/>
-    <sheet name="Sim_normalni" sheetId="17" r:id="rId17"/>
-    <sheet name="Sim_sikme" sheetId="18" r:id="rId18"/>
-    <sheet name="Sim_chvosty" sheetId="19" r:id="rId19"/>
-    <sheet name="Sim_smes" sheetId="20" r:id="rId20"/>
+    <sheet name="Normalizace" sheetId="6" r:id="rId6"/>
+    <sheet name="Modely" sheetId="7" r:id="rId7"/>
+    <sheet name="Skaly" sheetId="8" r:id="rId8"/>
+    <sheet name="U01_reference" sheetId="9" r:id="rId9"/>
+    <sheet name="U02_standardizace" sheetId="10" r:id="rId10"/>
+    <sheet name="U03_model" sheetId="11" r:id="rId11"/>
+    <sheet name="U04_plochy" sheetId="12" r:id="rId12"/>
+    <sheet name="U05_percentily" sheetId="13" r:id="rId13"/>
+    <sheet name="U06_zaokrouhleni" sheetId="14" r:id="rId14"/>
+    <sheet name="U07_prevody" sheetId="15" r:id="rId15"/>
+    <sheet name="U08_pasmo" sheetId="16" r:id="rId16"/>
+    <sheet name="QQ_data" sheetId="17" r:id="rId17"/>
+    <sheet name="Sim_normalni" sheetId="18" r:id="rId18"/>
+    <sheet name="Sim_sikme" sheetId="19" r:id="rId19"/>
+    <sheet name="Sim_chvosty" sheetId="20" r:id="rId20"/>
+    <sheet name="Sim_smes" sheetId="21" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="133">
   <si>
     <t>Normální model</t>
   </si>
@@ -202,6 +203,15 @@
     <t>Výklad: standardizace pěti časů</t>
   </si>
   <si>
+    <t>Doba řešení (s)</t>
+  </si>
+  <si>
+    <t>Výklad: normalizace rozdělení přes pořadí</t>
+  </si>
+  <si>
+    <t>Patnáct seřazených dob; převod přes kompromisní percentilové pořadí a NORM.S.INV ukazuje tabulka ve výkladu.</t>
+  </si>
+  <si>
     <t>Model</t>
   </si>
   <si>
@@ -347,6 +357,12 @@
   </si>
   <si>
     <t>A2:A6</t>
+  </si>
+  <si>
+    <t>Normalizace</t>
+  </si>
+  <si>
+    <t>A2:A16</t>
   </si>
   <si>
     <t>Modely</t>
@@ -765,7 +781,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C564-4A0A-9090-90FF45979CB5}"/>
+              <c16:uniqueId val="{00000005-EAE0-4798-AD56-A1C7D1F98722}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -879,7 +895,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-C564-4A0A-9090-90FF45979CB5}"/>
+              <c16:uniqueId val="{00000006-EAE0-4798-AD56-A1C7D1F98722}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -891,11 +907,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1241508271"/>
-        <c:axId val="1097559152"/>
+        <c:axId val="745567471"/>
+        <c:axId val="745569871"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1241508271"/>
+        <c:axId val="745567471"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -925,13 +941,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1097559152"/>
+        <c:crossAx val="745569871"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1097559152"/>
+        <c:axId val="745569871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -959,7 +975,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1241508271"/>
+        <c:crossAx val="745567471"/>
         <c:crossesAt val="-2"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1021,7 +1037,7 @@
         <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6592307-7214-0ED3-B0A1-C63AABD91670}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37C1594E-9CC9-7DB9-19DB-3F578DE163B9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1358,8 +1374,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2A4FA30-1D4D-4A8D-B74B-4E397ABC102C}">
-  <dimension ref="A1:C29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E27B6E61-0262-4D90-BBD2-C7BA3F454103}">
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="25.625" customWidth="1"/>
@@ -1368,7 +1384,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1380,49 +1396,49 @@
     </row>
     <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>45</v>
@@ -1430,10 +1446,10 @@
     </row>
     <row r="9" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>48</v>
@@ -1441,32 +1457,32 @@
     </row>
     <row r="10" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>62</v>
@@ -1474,32 +1490,32 @@
     </row>
     <row r="13" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>70</v>
@@ -1507,18 +1523,18 @@
     </row>
     <row r="16" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>111</v>
@@ -1529,21 +1545,21 @@
     </row>
     <row r="18" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>80</v>
@@ -1551,21 +1567,21 @@
     </row>
     <row r="20" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>84</v>
@@ -1573,63 +1589,69 @@
     </row>
     <row r="22" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="A27" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -1640,6 +1662,11 @@
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1654,7 +1681,70 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09623729-FBA6-4CAD-9510-1E31F57F390D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9E61E6-00FC-419B-9B7A-E49DF6B8C37D}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
+        <v>2</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>2</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>2</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>2</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>12</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F306F-A11D-4964-A7B7-D3FD7BF2220D}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1665,7 +1755,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1682,7 +1772,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1696,7 +1786,7 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B4" s="14">
         <v>0.08</v>
@@ -1716,7 +1806,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B6" s="14">
         <v>25</v>
@@ -1735,8 +1825,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC763061-28AB-40A9-A360-C25D2116857A}">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D276C9B-2F55-4BE7-933F-3139D58A4CEB}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1747,7 +1837,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1764,7 +1854,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1798,7 +1888,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B6" s="14">
         <v>20</v>
@@ -1807,7 +1897,7 @@
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B7" s="14">
         <v>8</v>
@@ -1823,8 +1913,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE3F741-8CAF-46ED-88CF-29EEC485BCE4}">
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75310E57-8FBC-44BF-8A5B-9AC9B8D0C390}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1835,7 +1925,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1852,7 +1942,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1877,7 +1967,7 @@
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B5" s="14">
         <v>0.1</v>
@@ -1905,8 +1995,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A8B0056-0743-4BB9-80CA-CDAA8DE11395}">
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C639198E-DD95-4814-A3B5-4D9260DAEB0C}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1917,7 +2007,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -1934,7 +2024,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1948,7 +2038,7 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
@@ -1959,7 +2049,7 @@
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B5" s="14">
         <v>1</v>
@@ -1981,68 +2071,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10E3AA8C-BA13-4AB3-9CCF-08FB1C90FECB}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="3" max="3" width="60.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>38</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
-        <v>50</v>
-      </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
-        <v>60</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
-        <v>70</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287D5B69-B5A3-4E98-8B12-83A0CB0083E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B06EDD05-5EA0-41D6-824E-7FCC3534AEB6}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2060,7 +2090,7 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
-        <v>1.2</v>
+        <v>38</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>80</v>
@@ -2068,19 +2098,22 @@
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
-        <v>-0.6</v>
+        <v>50</v>
       </c>
       <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>70</v>
+      </c>
       <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,7 +2132,64 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91114212-D9F9-42B9-8338-0EA5C00605E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D11453-789F-44C0-BBBF-36866B411727}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>-0.6</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE71178-2FCE-4938-B597-766959C90267}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2120,7 +2210,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2134,7 +2224,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2183,1042 +2273,6 @@
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519B2961-9847-4F87-8D25-73D597EE6BB2}">
-  <dimension ref="A1:C201"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="3" max="3" width="60.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
-        <v>48.85602655957382</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18">
-        <v>46.839364304880455</v>
-      </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
-        <v>29.327651524791108</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18">
-        <v>52.872228445571935</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18">
-        <v>43.66797230215824</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="18">
-        <v>34.485641358295069</v>
-      </c>
-      <c r="C7" s="16"/>
-    </row>
-    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18">
-        <v>45.335951801294073</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="18">
-        <v>57.931231438988789</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18">
-        <v>73.645815079847083</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18">
-        <v>36.790659198448253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="18">
-        <v>60.633297746065026</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="18">
-        <v>49.953139935765826</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18">
-        <v>50.779485996595696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="18">
-        <v>65.530800942829472</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="18">
-        <v>60.164918633653301</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18">
-        <v>61.754371173718198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18">
-        <v>44.577442485984605</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18">
-        <v>49.551019429591818</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18">
-        <v>41.993588583607043</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="18">
-        <v>63.984391016308365</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18">
-        <v>48.310311875182087</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18">
-        <v>44.527688866082066</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18">
-        <v>59.414935702480037</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18">
-        <v>49.802831212210222</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18">
-        <v>33.994100406532567</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="18">
-        <v>40.032562575854747</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18">
-        <v>33.390443124033801</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="18">
-        <v>57.714430934046831</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="18">
-        <v>42.293809875655597</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="18">
-        <v>48.141142649359402</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="18">
-        <v>50.142776474036509</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="18">
-        <v>39.878822474858119</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="18">
-        <v>58.482898079282862</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="18">
-        <v>60.462869251118072</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="18">
-        <v>42.867747678169067</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="18">
-        <v>59.300964609143207</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="18">
-        <v>41.662759212547883</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="18">
-        <v>59.760074882925849</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="18">
-        <v>59.574101755909574</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="18">
-        <v>49.523339023247992</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="18">
-        <v>37.834035236208052</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18">
-        <v>46.41771648534035</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="18">
-        <v>36.983072480767042</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="18">
-        <v>54.280198905821017</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="18">
-        <v>37.035225004798946</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="18">
-        <v>52.737564164618441</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="18">
-        <v>46.950070180219853</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="18">
-        <v>69.081091085624621</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="18">
-        <v>46.412740836321923</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="18">
-        <v>49.393557819346448</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="18">
-        <v>55.395990431852944</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="18">
-        <v>53.654328011244573</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="18">
-        <v>46.816634564924215</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="18">
-        <v>43.709912914779309</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="18">
-        <v>43.000627703259845</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="18">
-        <v>38.539160700178265</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="18">
-        <v>51.752856677065076</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="18">
-        <v>54.508636923006378</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="18">
-        <v>40.192091375420389</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="18">
-        <v>39.485906461018509</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="18">
-        <v>56.937369572097801</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="18">
-        <v>49.233452734569866</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="18">
-        <v>37.369901795678075</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="18">
-        <v>37.215620558245739</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="18">
-        <v>56.194832296275479</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="18">
-        <v>45.930398057771058</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="18">
-        <v>34.804617767642014</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="18">
-        <v>46.152415724374336</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="18">
-        <v>46.591154083937894</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="18">
-        <v>61.859591041516673</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="18">
-        <v>61.246918279723097</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="18">
-        <v>43.323629776335913</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="18">
-        <v>59.744644956386963</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="18">
-        <v>65.23826650763894</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="18">
-        <v>34.604384632836016</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="18">
-        <v>40.947603679490442</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="18">
-        <v>45.304021468750101</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="18">
-        <v>53.843439944508297</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="18">
-        <v>52.740879757534955</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="18">
-        <v>28.105265642590773</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="18">
-        <v>45.571114810569938</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="18">
-        <v>53.203616542744832</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="18">
-        <v>60.593909023906214</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="18">
-        <v>57.60119104117085</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="18">
-        <v>44.13690372359622</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="18">
-        <v>36.788768113119197</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="18">
-        <v>61.783788225442834</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="18">
-        <v>39.29506336887534</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="18">
-        <v>45.66521280676416</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="18">
-        <v>45.957749168843776</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="18">
-        <v>45.699709604273082</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="18">
-        <v>43.497934881124671</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="18">
-        <v>53.332077289124832</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="18">
-        <v>67.28988187628606</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="18">
-        <v>45.456010305269949</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="18">
-        <v>49.534855487471489</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="18">
-        <v>52.059508780425801</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="18">
-        <v>48.068737172084461</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="18">
-        <v>64.725972215108769</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="18">
-        <v>61.560182292331547</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="18">
-        <v>50.229310447645041</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="18">
-        <v>25.430709780447991</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="18">
-        <v>63.388687440098877</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="18">
-        <v>46.780270853362268</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="18">
-        <v>36.534135800854969</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="18">
-        <v>42.238045619455782</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="18">
-        <v>49.413626080812918</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="18">
-        <v>48.771498146772707</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="18">
-        <v>51.397818335362309</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="18">
-        <v>60.361029134649513</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="18">
-        <v>60.316299946003681</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="18">
-        <v>53.128705788464941</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="18">
-        <v>64.946012690105391</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="18">
-        <v>65.570472734143124</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="18">
-        <v>60.988139986738474</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="18">
-        <v>65.386298755475039</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="18">
-        <v>51.986848954165737</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="18">
-        <v>49.0209671102984</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="18">
-        <v>60.864267940241319</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="18">
-        <v>40.421905271601595</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="18">
-        <v>32.302503424262298</v>
-      </c>
-    </row>
-    <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="18">
-        <v>31.264923499047999</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="18">
-        <v>74.569808674876398</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="18">
-        <v>37.007746347085309</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="18">
-        <v>48.342581739261632</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="18">
-        <v>36.704860301550589</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="18">
-        <v>64.005227930034394</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="18">
-        <v>51.115247787119728</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="18">
-        <v>66.977173845334235</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="18">
-        <v>59.204872664136033</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="18">
-        <v>45.847192248604749</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="18">
-        <v>39.206399006598417</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="18">
-        <v>38.80995021909321</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="18">
-        <v>45.361422367684931</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="18">
-        <v>42.219853681397353</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="18">
-        <v>51.354421515370717</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="18">
-        <v>57.526566372503332</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="18">
-        <v>39.570231804106143</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="18">
-        <v>56.324175281924994</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="18">
-        <v>74.243524608603622</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="18">
-        <v>51.118783278780072</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="18">
-        <v>44.592454438244189</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="18">
-        <v>50.68033529070587</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="18">
-        <v>40.548883654616702</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="18">
-        <v>57.476971275714739</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="18">
-        <v>59.646654826703212</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="18">
-        <v>39.385049402123293</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="18">
-        <v>40.266263696649418</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="18">
-        <v>34.153591938930738</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="18">
-        <v>42.960134885386921</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="18">
-        <v>49.190582206830669</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="18">
-        <v>44.393858749102854</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="18">
-        <v>40.822207618158913</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="18">
-        <v>58.387185978863286</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="18">
-        <v>43.940164537228007</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="18">
-        <v>45.13621953383872</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="18">
-        <v>44.160885732541971</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="18">
-        <v>60.338816362286423</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="18">
-        <v>38.336269962468833</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="18">
-        <v>44.699578744420954</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="18">
-        <v>60.750841970820169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="18">
-        <v>42.217990251135319</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="18">
-        <v>49.464529408381253</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="18">
-        <v>26.326737268137705</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="18">
-        <v>73.77697973777353</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="18">
-        <v>56.985227664501572</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="18">
-        <v>47.037125543672232</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="18">
-        <v>47.932432716228782</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="18">
-        <v>52.15744464937837</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="18">
-        <v>41.820146217412486</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="18">
-        <v>55.253686322740066</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="18">
-        <v>37.827325971507683</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="18">
-        <v>53.738822247743855</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="18">
-        <v>38.077037991019182</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="18">
-        <v>44.864807447460798</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="18">
-        <v>31.838565931149638</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="18">
-        <v>58.7185829174284</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="18">
-        <v>63.885943414368768</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="18">
-        <v>61.791327667336972</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="18">
-        <v>47.525722878995069</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="18">
-        <v>55.082461309605769</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="18">
-        <v>46.218250574281711</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="18">
-        <v>62.506367232129122</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="18">
-        <v>55.902376601600771</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="18">
-        <v>47.865588238340798</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="18">
-        <v>62.486024787688606</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="18">
-        <v>52.982428252352712</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="18">
-        <v>56.184283627515811</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="18">
-        <v>42.664715090276019</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="18">
-        <v>43.631634432761146</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="18">
-        <v>44.453961848924557</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="18">
-        <v>53.766982817623031</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="18">
-        <v>64.466716918938147</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="18">
-        <v>68.023243003280058</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="18">
-        <v>47.725956201885985</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="18">
-        <v>41.133352827241282</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="18">
-        <v>45.149796321819835</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="18">
-        <v>54.39814422263963</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="18">
-        <v>38.820045797836187</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="18">
-        <v>55.337898635839188</v>
       </c>
     </row>
   </sheetData>
@@ -3231,7 +2285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEFECDF8-68FC-4DDC-971E-C846B6760D37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54380A08-7C38-44BF-83B2-CB3D16410124}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3241,7 +2295,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>44</v>
@@ -3249,1012 +2303,1012 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18">
-        <v>66.073597304495223</v>
+        <v>48.85602655957382</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
-        <v>38.89004377881065</v>
+        <v>46.839364304880455</v>
       </c>
       <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
-        <v>80.020527650875579</v>
+        <v>29.327651524791108</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
-        <v>31.090159951709211</v>
+        <v>52.872228445571935</v>
       </c>
       <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
-        <v>47.040123384529949</v>
+        <v>43.66797230215824</v>
       </c>
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
-        <v>30.605094073243531</v>
+        <v>34.485641358295069</v>
       </c>
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
-        <v>32.889411058599826</v>
+        <v>45.335951801294073</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
-        <v>49.270290531519237</v>
+        <v>57.931231438988789</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
-        <v>60.680770826197033</v>
+        <v>73.645815079847083</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
-        <v>40.189021148253232</v>
+        <v>36.790659198448253</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
-        <v>53.771901529422323</v>
+        <v>60.633297746065026</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
-        <v>52.836964898001504</v>
+        <v>49.953139935765826</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
-        <v>59.209591447046762</v>
+        <v>50.779485996595696</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
-        <v>127.78312543566943</v>
+        <v>65.530800942829472</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
-        <v>34.183519198559225</v>
+        <v>60.164918633653301</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
-        <v>41.18274655595738</v>
+        <v>61.754371173718198</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
-        <v>37.030579636339098</v>
+        <v>44.577442485984605</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
-        <v>69.599282320561059</v>
+        <v>49.551019429591818</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
-        <v>40.128409448079765</v>
+        <v>41.993588583607043</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
-        <v>40.909797646406474</v>
+        <v>63.984391016308365</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
-        <v>41.117681948769274</v>
+        <v>48.310311875182087</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
-        <v>33.679715639445931</v>
+        <v>44.527688866082066</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
-        <v>34.593579797074199</v>
+        <v>59.414935702480037</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
-        <v>31.68787092436105</v>
+        <v>49.802831212210222</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
-        <v>32.181566556702968</v>
+        <v>33.994100406532567</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
-        <v>40.80281381453289</v>
+        <v>40.032562575854747</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
-        <v>110.54126476476218</v>
+        <v>33.390443124033801</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
-        <v>42.219834222986748</v>
+        <v>57.714430934046831</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
-        <v>49.51755097538549</v>
+        <v>42.293809875655597</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18">
-        <v>65.963283355365633</v>
+        <v>48.141142649359402</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
-        <v>50.119942095431867</v>
+        <v>50.142776474036509</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
-        <v>53.309910864240294</v>
+        <v>39.878822474858119</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
-        <v>34.308579972581441</v>
+        <v>58.482898079282862</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
-        <v>32.985101421363652</v>
+        <v>60.462869251118072</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18">
-        <v>64.227802537353881</v>
+        <v>42.867747678169067</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18">
-        <v>67.28401564803923</v>
+        <v>59.300964609143207</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18">
-        <v>56.376573777428632</v>
+        <v>41.662759212547883</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18">
-        <v>30.611158109861105</v>
+        <v>59.760074882925849</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
-        <v>49.650231808725181</v>
+        <v>59.574101755909574</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18">
-        <v>30.256860530935228</v>
+        <v>49.523339023247992</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18">
-        <v>47.465419680181327</v>
+        <v>37.834035236208052</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18">
-        <v>41.842515067522939</v>
+        <v>46.41771648534035</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18">
-        <v>40.54850793527028</v>
+        <v>36.983072480767042</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18">
-        <v>50.481946504976037</v>
+        <v>54.280198905821017</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="18">
-        <v>42.879178434911552</v>
+        <v>37.035225004798946</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18">
-        <v>31.99466759338975</v>
+        <v>52.737564164618441</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="18">
-        <v>41.608413615565183</v>
+        <v>46.950070180219853</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18">
-        <v>35.372470412403345</v>
+        <v>69.081091085624621</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="18">
-        <v>50.227781583116069</v>
+        <v>46.412740836321923</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18">
-        <v>33.258706101258475</v>
+        <v>49.393557819346448</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18">
-        <v>36.146681063355153</v>
+        <v>55.395990431852944</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18">
-        <v>41.541649535599532</v>
+        <v>53.654328011244573</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
-        <v>33.454991129692644</v>
+        <v>46.816634564924215</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
-        <v>33.187484617810696</v>
+        <v>43.709912914779309</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
-        <v>31.684710506815463</v>
+        <v>43.000627703259845</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18">
-        <v>54.368565714589117</v>
+        <v>38.539160700178265</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18">
-        <v>53.078939699238902</v>
+        <v>51.752856677065076</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18">
-        <v>57.385759221992259</v>
+        <v>54.508636923006378</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18">
-        <v>36.932783669326454</v>
+        <v>40.192091375420389</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18">
-        <v>44.711488661657455</v>
+        <v>39.485906461018509</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18">
-        <v>51.219978988002737</v>
+        <v>56.937369572097801</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18">
-        <v>34.738380846091424</v>
+        <v>49.233452734569866</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18">
-        <v>30.929745727242917</v>
+        <v>37.369901795678075</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18">
-        <v>30.328833469410338</v>
+        <v>37.215620558245739</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18">
-        <v>36.456756089111629</v>
+        <v>56.194832296275479</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18">
-        <v>37.117371812928468</v>
+        <v>45.930398057771058</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18">
-        <v>53.150044412859224</v>
+        <v>34.804617767642014</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18">
-        <v>32.838772782124579</v>
+        <v>46.152415724374336</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="18">
-        <v>33.988396197091788</v>
+        <v>46.591154083937894</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18">
-        <v>31.164749417428595</v>
+        <v>61.859591041516673</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="18">
-        <v>60.104070127612715</v>
+        <v>61.246918279723097</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18">
-        <v>54.271881431332069</v>
+        <v>43.323629776335913</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18">
-        <v>30.121303503401577</v>
+        <v>59.744644956386963</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18">
-        <v>66.225175337213187</v>
+        <v>65.23826650763894</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="18">
-        <v>40.822088484085434</v>
+        <v>34.604384632836016</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18">
-        <v>50.794695735580092</v>
+        <v>40.947603679490442</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="18">
-        <v>31.005436310078949</v>
+        <v>45.304021468750101</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18">
-        <v>39.967539429198951</v>
+        <v>53.843439944508297</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="18">
-        <v>52.430345461374877</v>
+        <v>52.740879757534955</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18">
-        <v>55.719065134084587</v>
+        <v>28.105265642590773</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="18">
-        <v>69.307078279527076</v>
+        <v>45.571114810569938</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="18">
-        <v>37.682667633052915</v>
+        <v>53.203616542744832</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="18">
-        <v>32.345481631346047</v>
+        <v>60.593909023906214</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="18">
-        <v>58.076325588530665</v>
+        <v>57.60119104117085</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="18">
-        <v>70.60914669782133</v>
+        <v>44.13690372359622</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="18">
-        <v>54.769155363223319</v>
+        <v>36.788768113119197</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="18">
-        <v>37.746288275811821</v>
+        <v>61.783788225442834</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18">
-        <v>64.19509685089065</v>
+        <v>39.29506336887534</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="18">
-        <v>67.746267547232719</v>
+        <v>45.66521280676416</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="18">
-        <v>35.118766218344049</v>
+        <v>45.957749168843776</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="18">
-        <v>43.427614587660315</v>
+        <v>45.699709604273082</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="18">
-        <v>43.050719894769969</v>
+        <v>43.497934881124671</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="18">
-        <v>34.890101321507245</v>
+        <v>53.332077289124832</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="18">
-        <v>37.646529239136726</v>
+        <v>67.28988187628606</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="18">
-        <v>36.512210180517286</v>
+        <v>45.456010305269949</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="18">
-        <v>44.99191072240788</v>
+        <v>49.534855487471489</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="18">
-        <v>40.478340214419546</v>
+        <v>52.059508780425801</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="18">
-        <v>52.912835216752057</v>
+        <v>48.068737172084461</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="18">
-        <v>32.852263803918561</v>
+        <v>64.725972215108769</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="18">
-        <v>42.150519377853158</v>
+        <v>61.560182292331547</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="18">
-        <v>34.615299509419771</v>
+        <v>50.229310447645041</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="18">
-        <v>36.867444069527146</v>
+        <v>25.430709780447991</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="18">
-        <v>57.641927952549224</v>
+        <v>63.388687440098877</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="18">
-        <v>49.332261517945113</v>
+        <v>46.780270853362268</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="18">
-        <v>38.767668509390205</v>
+        <v>36.534135800854969</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="18">
-        <v>34.39139593849702</v>
+        <v>42.238045619455782</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="18">
-        <v>38.342546371277422</v>
+        <v>49.413626080812918</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="18">
-        <v>37.086550329863663</v>
+        <v>48.771498146772707</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="18">
-        <v>61.755756277563222</v>
+        <v>51.397818335362309</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="18">
-        <v>33.55604701442644</v>
+        <v>60.361029134649513</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="18">
-        <v>49.528933362405184</v>
+        <v>60.316299946003681</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="18">
-        <v>53.53956713215149</v>
+        <v>53.128705788464941</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="18">
-        <v>54.111682287088399</v>
+        <v>64.946012690105391</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="18">
-        <v>45.94257321611363</v>
+        <v>65.570472734143124</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="18">
-        <v>65.763890061499723</v>
+        <v>60.988139986738474</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="18">
-        <v>40.325761288404465</v>
+        <v>65.386298755475039</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="18">
-        <v>31.281466302461919</v>
+        <v>51.986848954165737</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="18">
-        <v>38.169489009305835</v>
+        <v>49.0209671102984</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="18">
-        <v>37.51286887563765</v>
+        <v>60.864267940241319</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="18">
-        <v>52.210685516361863</v>
+        <v>40.421905271601595</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="18">
-        <v>32.152299138249312</v>
+        <v>32.302503424262298</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="18">
-        <v>33.794799861498177</v>
+        <v>31.264923499047999</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="18">
-        <v>32.705895078834146</v>
+        <v>74.569808674876398</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="18">
-        <v>40.015180462505668</v>
+        <v>37.007746347085309</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="18">
-        <v>31.645221028011292</v>
+        <v>48.342581739261632</v>
       </c>
     </row>
     <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="18">
-        <v>39.651232904288918</v>
+        <v>36.704860301550589</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="18">
-        <v>38.624180280603468</v>
+        <v>64.005227930034394</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="18">
-        <v>30.275298054726377</v>
+        <v>51.115247787119728</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="18">
-        <v>33.485360399354249</v>
+        <v>66.977173845334235</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="18">
-        <v>32.457574945874512</v>
+        <v>59.204872664136033</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="18">
-        <v>43.469868907496675</v>
+        <v>45.847192248604749</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="18">
-        <v>40.892417756210449</v>
+        <v>39.206399006598417</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="18">
-        <v>49.959278068806412</v>
+        <v>38.80995021909321</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18">
-        <v>33.819442035164684</v>
+        <v>45.361422367684931</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18">
-        <v>37.856629632879049</v>
+        <v>42.219853681397353</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="18">
-        <v>66.154856239566385</v>
+        <v>51.354421515370717</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="18">
-        <v>55.816313911518563</v>
+        <v>57.526566372503332</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="18">
-        <v>31.1981864226982</v>
+        <v>39.570231804106143</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="18">
-        <v>39.189103175885975</v>
+        <v>56.324175281924994</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="18">
-        <v>32.972748074680567</v>
+        <v>74.243524608603622</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="18">
-        <v>39.807592425495386</v>
+        <v>51.118783278780072</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="18">
-        <v>55.748269181038474</v>
+        <v>44.592454438244189</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="18">
-        <v>42.013864893767419</v>
+        <v>50.68033529070587</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="18">
-        <v>59.178414399406677</v>
+        <v>40.548883654616702</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="18">
-        <v>50.12521477353144</v>
+        <v>57.476971275714739</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="18">
-        <v>87.675613062339906</v>
+        <v>59.646654826703212</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="18">
-        <v>30.488174340651693</v>
+        <v>39.385049402123293</v>
       </c>
     </row>
     <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="18">
-        <v>31.602561503361489</v>
+        <v>40.266263696649418</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="18">
-        <v>55.443514394930453</v>
+        <v>34.153591938930738</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18">
-        <v>56.192054086035853</v>
+        <v>42.960134885386921</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="18">
-        <v>56.150123476433663</v>
+        <v>49.190582206830669</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="18">
-        <v>55.68656232081986</v>
+        <v>44.393858749102854</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="18">
-        <v>52.108126048601036</v>
+        <v>40.822207618158913</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="18">
-        <v>61.11078056380785</v>
+        <v>58.387185978863286</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="18">
-        <v>49.010764178189817</v>
+        <v>43.940164537228007</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="18">
-        <v>39.469132425729185</v>
+        <v>45.13621953383872</v>
       </c>
     </row>
     <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="18">
-        <v>34.490346286911517</v>
+        <v>44.160885732541971</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18">
-        <v>61.676710013272412</v>
+        <v>60.338816362286423</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="18">
-        <v>40.178170586004853</v>
+        <v>38.336269962468833</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="18">
-        <v>47.584741701673153</v>
+        <v>44.699578744420954</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="18">
-        <v>45.731316119888731</v>
+        <v>60.750841970820169</v>
       </c>
     </row>
     <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="18">
-        <v>55.215121841660505</v>
+        <v>42.217990251135319</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="18">
-        <v>32.609912313574071</v>
+        <v>49.464529408381253</v>
       </c>
     </row>
     <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="18">
-        <v>68.509276777478107</v>
+        <v>26.326737268137705</v>
       </c>
     </row>
     <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="18">
-        <v>41.674246587085797</v>
+        <v>73.77697973777353</v>
       </c>
     </row>
     <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="18">
-        <v>72.258166835091544</v>
+        <v>56.985227664501572</v>
       </c>
     </row>
     <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="18">
-        <v>33.935264372921168</v>
+        <v>47.037125543672232</v>
       </c>
     </row>
     <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="18">
-        <v>62.180283317410215</v>
+        <v>47.932432716228782</v>
       </c>
     </row>
     <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="18">
-        <v>45.977431022863271</v>
+        <v>52.15744464937837</v>
       </c>
     </row>
     <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="18">
-        <v>47.563953981104675</v>
+        <v>41.820146217412486</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="18">
-        <v>46.289589497561934</v>
+        <v>55.253686322740066</v>
       </c>
     </row>
     <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="18">
-        <v>35.568672852011275</v>
+        <v>37.827325971507683</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="18">
-        <v>52.65075185210145</v>
+        <v>53.738822247743855</v>
       </c>
     </row>
     <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="18">
-        <v>41.391437099616411</v>
+        <v>38.077037991019182</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="18">
-        <v>31.535752152121631</v>
+        <v>44.864807447460798</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="18">
-        <v>35.991911246117787</v>
+        <v>31.838565931149638</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="18">
-        <v>37.004774257075042</v>
+        <v>58.7185829174284</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="18">
-        <v>36.426826003007591</v>
+        <v>63.885943414368768</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="18">
-        <v>36.473699386697263</v>
+        <v>61.791327667336972</v>
       </c>
     </row>
     <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="18">
-        <v>47.995016471783998</v>
+        <v>47.525722878995069</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="18">
-        <v>38.942083126911427</v>
+        <v>55.082461309605769</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="18">
-        <v>38.489750877488405</v>
+        <v>46.218250574281711</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="18">
-        <v>37.104922577273101</v>
+        <v>62.506367232129122</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="18">
-        <v>66.423356354208835</v>
+        <v>55.902376601600771</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18">
-        <v>33.493768929038197</v>
+        <v>47.865588238340798</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18">
-        <v>35.440031850019146</v>
+        <v>62.486024787688606</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="18">
-        <v>45.77485809505302</v>
+        <v>52.982428252352712</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="18">
-        <v>32.561445453993244</v>
+        <v>56.184283627515811</v>
       </c>
     </row>
     <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18">
-        <v>58.733083101591831</v>
+        <v>42.664715090276019</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="18">
-        <v>54.14418962658084</v>
+        <v>43.631634432761146</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="18">
-        <v>30.812619506228231</v>
+        <v>44.453961848924557</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="18">
-        <v>92.30465666075888</v>
+        <v>53.766982817623031</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="18">
-        <v>39.329092456027865</v>
+        <v>64.466716918938147</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="18">
-        <v>50.524832247126291</v>
+        <v>68.023243003280058</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="18">
-        <v>31.928302756713844</v>
+        <v>47.725956201885985</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18">
-        <v>37.989236824214458</v>
+        <v>41.133352827241282</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18">
-        <v>46.942548611502531</v>
+        <v>45.149796321819835</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18">
-        <v>44.546492085161987</v>
+        <v>54.39814422263963</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18">
-        <v>34.785326840355992</v>
+        <v>38.820045797836187</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18">
-        <v>55.360773726037507</v>
+        <v>55.337898635839188</v>
       </c>
     </row>
   </sheetData>
@@ -4267,7 +3321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B82288-35C4-468B-8C02-1383E432019F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54225AB0-0774-4D9A-9F04-0F325C889366}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4277,7 +3331,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>44</v>
@@ -4285,1012 +3339,1012 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18">
-        <v>44.583323970004095</v>
+        <v>66.073597304495223</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
-        <v>51.334447207766225</v>
+        <v>38.89004377881065</v>
       </c>
       <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
-        <v>22.049299769270561</v>
+        <v>80.020527650875579</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
-        <v>67.12353898825269</v>
+        <v>31.090159951709211</v>
       </c>
       <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
-        <v>51.43348741741498</v>
+        <v>47.040123384529949</v>
       </c>
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
-        <v>51.851061941192299</v>
+        <v>30.605094073243531</v>
       </c>
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
-        <v>61.899850011110217</v>
+        <v>32.889411058599826</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
-        <v>45.089113454926675</v>
+        <v>49.270290531519237</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
-        <v>58.022351957847448</v>
+        <v>60.680770826197033</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
-        <v>27.918169643776512</v>
+        <v>40.189021148253232</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
-        <v>48.252400632490939</v>
+        <v>53.771901529422323</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
-        <v>50.504048652608617</v>
+        <v>52.836964898001504</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
-        <v>46.940464063830234</v>
+        <v>59.209591447046762</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
-        <v>32.477745204184998</v>
+        <v>127.78312543566943</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
-        <v>47.776046232762582</v>
+        <v>34.183519198559225</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
-        <v>52.364536146374576</v>
+        <v>41.18274655595738</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
-        <v>45.500856174103568</v>
+        <v>37.030579636339098</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
-        <v>55.052096044162909</v>
+        <v>69.599282320561059</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
-        <v>50.685613161086344</v>
+        <v>40.128409448079765</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
-        <v>49.66952996775624</v>
+        <v>40.909797646406474</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
-        <v>104.0837872400076</v>
+        <v>41.117681948769274</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
-        <v>48.138533562033437</v>
+        <v>33.679715639445931</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
-        <v>51.306818862784155</v>
+        <v>34.593579797074199</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
-        <v>50.20944889961028</v>
+        <v>31.68787092436105</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
-        <v>75.063939489551288</v>
+        <v>32.181566556702968</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
-        <v>45.850919890213376</v>
+        <v>40.80281381453289</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
-        <v>61.182874319803965</v>
+        <v>110.54126476476218</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
-        <v>53.242645886564432</v>
+        <v>42.219834222986748</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
-        <v>48.457622052033251</v>
+        <v>49.51755097538549</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18">
-        <v>50.141780231489143</v>
+        <v>65.963283355365633</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
-        <v>54.727203415741691</v>
+        <v>50.119942095431867</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
-        <v>41.170085502511725</v>
+        <v>53.309910864240294</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
-        <v>45.643499747389342</v>
+        <v>34.308579972581441</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
-        <v>49.679103878592088</v>
+        <v>32.985101421363652</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18">
-        <v>48.057261654852617</v>
+        <v>64.227802537353881</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18">
-        <v>69.936980427049335</v>
+        <v>67.28401564803923</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18">
-        <v>49.69352250939118</v>
+        <v>56.376573777428632</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18">
-        <v>68.62388039969656</v>
+        <v>30.611158109861105</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
-        <v>49.630861611768701</v>
+        <v>49.650231808725181</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18">
-        <v>46.252110620339266</v>
+        <v>30.256860530935228</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18">
-        <v>33.849920369473907</v>
+        <v>47.465419680181327</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18">
-        <v>61.040272273906567</v>
+        <v>41.842515067522939</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18">
-        <v>51.026349773822112</v>
+        <v>40.54850793527028</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18">
-        <v>25.437813575006871</v>
+        <v>50.481946504976037</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="18">
-        <v>42.412842605243902</v>
+        <v>42.879178434911552</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18">
-        <v>62.686303636400751</v>
+        <v>31.99466759338975</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="18">
-        <v>42.704975764121997</v>
+        <v>41.608413615565183</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18">
-        <v>49.587829692225341</v>
+        <v>35.372470412403345</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="18">
-        <v>40.78205054740252</v>
+        <v>50.227781583116069</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18">
-        <v>41.946539670316461</v>
+        <v>33.258706101258475</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18">
-        <v>45.353919743322727</v>
+        <v>36.146681063355153</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18">
-        <v>51.583911931211553</v>
+        <v>41.541649535599532</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
-        <v>43.714457679757274</v>
+        <v>33.454991129692644</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
-        <v>52.37259939470421</v>
+        <v>33.187484617810696</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
-        <v>36.057837306818563</v>
+        <v>31.684710506815463</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18">
-        <v>52.312866521311008</v>
+        <v>54.368565714589117</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18">
-        <v>50.898708249164237</v>
+        <v>53.078939699238902</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18">
-        <v>41.696665737883528</v>
+        <v>57.385759221992259</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18">
-        <v>44.350601057959913</v>
+        <v>36.932783669326454</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18">
-        <v>58.236466252153789</v>
+        <v>44.711488661657455</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18">
-        <v>19.574030505252157</v>
+        <v>51.219978988002737</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18">
-        <v>56.080188977948879</v>
+        <v>34.738380846091424</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18">
-        <v>30.68074555636943</v>
+        <v>30.929745727242917</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18">
-        <v>-12.204560354287352</v>
+        <v>30.328833469410338</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18">
-        <v>45.220203620598937</v>
+        <v>36.456756089111629</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18">
-        <v>17.633038518680848</v>
+        <v>37.117371812928468</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18">
-        <v>52.558418096840398</v>
+        <v>53.150044412859224</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18">
-        <v>53.918768547743881</v>
+        <v>32.838772782124579</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="18">
-        <v>56.972852118665365</v>
+        <v>33.988396197091788</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18">
-        <v>58.026408528720026</v>
+        <v>31.164749417428595</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="18">
-        <v>42.542720247102906</v>
+        <v>60.104070127612715</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18">
-        <v>48.323793455863751</v>
+        <v>54.271881431332069</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18">
-        <v>50.092658671687573</v>
+        <v>30.121303503401577</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18">
-        <v>45.229895119984732</v>
+        <v>66.225175337213187</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="18">
-        <v>52.728573385504006</v>
+        <v>40.822088484085434</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18">
-        <v>71.899363117058016</v>
+        <v>50.794695735580092</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="18">
-        <v>44.513348927234212</v>
+        <v>31.005436310078949</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18">
-        <v>63.77864435299476</v>
+        <v>39.967539429198951</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="18">
-        <v>46.436575656511899</v>
+        <v>52.430345461374877</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18">
-        <v>34.887998227138411</v>
+        <v>55.719065134084587</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="18">
-        <v>58.462021678261699</v>
+        <v>69.307078279527076</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="18">
-        <v>88.463061624052457</v>
+        <v>37.682667633052915</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="18">
-        <v>67.934703645557789</v>
+        <v>32.345481631346047</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="18">
-        <v>42.4628425000082</v>
+        <v>58.076325588530665</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="18">
-        <v>61.204939847809861</v>
+        <v>70.60914669782133</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="18">
-        <v>30.712805609794103</v>
+        <v>54.769155363223319</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="18">
-        <v>51.861494525023879</v>
+        <v>37.746288275811821</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18">
-        <v>54.918184385449301</v>
+        <v>64.19509685089065</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="18">
-        <v>32.623603626472288</v>
+        <v>67.746267547232719</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="18">
-        <v>45.728197050296096</v>
+        <v>35.118766218344049</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="18">
-        <v>43.597926883139415</v>
+        <v>43.427614587660315</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="18">
-        <v>23.030243265509871</v>
+        <v>43.050719894769969</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="18">
-        <v>56.656211338615392</v>
+        <v>34.890101321507245</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="18">
-        <v>58.795607188661208</v>
+        <v>37.646529239136726</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="18">
-        <v>45.169194495007787</v>
+        <v>36.512210180517286</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="18">
-        <v>58.697729354499721</v>
+        <v>44.99191072240788</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="18">
-        <v>36.002693637123954</v>
+        <v>40.478340214419546</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="18">
-        <v>48.499856032151719</v>
+        <v>52.912835216752057</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="18">
-        <v>55.574792339894898</v>
+        <v>32.852263803918561</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="18">
-        <v>46.620051006744809</v>
+        <v>42.150519377853158</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="18">
-        <v>35.192832980731971</v>
+        <v>34.615299509419771</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="18">
-        <v>45.186132660524521</v>
+        <v>36.867444069527146</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="18">
-        <v>41.440002205863252</v>
+        <v>57.641927952549224</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="18">
-        <v>56.867720158468678</v>
+        <v>49.332261517945113</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="18">
-        <v>53.295696930395053</v>
+        <v>38.767668509390205</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="18">
-        <v>64.889311035448912</v>
+        <v>34.39139593849702</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="18">
-        <v>54.26200612782938</v>
+        <v>38.342546371277422</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="18">
-        <v>52.544742047961151</v>
+        <v>37.086550329863663</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="18">
-        <v>40.523359873000345</v>
+        <v>61.755756277563222</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="18">
-        <v>46.446031997827333</v>
+        <v>33.55604701442644</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="18">
-        <v>51.779561027162579</v>
+        <v>49.528933362405184</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="18">
-        <v>49.014194362670722</v>
+        <v>53.53956713215149</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="18">
-        <v>61.819034752771493</v>
+        <v>54.111682287088399</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="18">
-        <v>29.985690829060811</v>
+        <v>45.94257321611363</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="18">
-        <v>53.876783794405526</v>
+        <v>65.763890061499723</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="18">
-        <v>61.539812338110224</v>
+        <v>40.325761288404465</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="18">
-        <v>43.974827192966821</v>
+        <v>31.281466302461919</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="18">
-        <v>45.551346114953439</v>
+        <v>38.169489009305835</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="18">
-        <v>50.084261318972246</v>
+        <v>37.51286887563765</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="18">
-        <v>62.01638668237868</v>
+        <v>52.210685516361863</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="18">
-        <v>56.175165413494142</v>
+        <v>32.152299138249312</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="18">
-        <v>47.456388751873405</v>
+        <v>33.794799861498177</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="18">
-        <v>23.038518892969723</v>
+        <v>32.705895078834146</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="18">
-        <v>51.998571819711955</v>
+        <v>40.015180462505668</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="18">
-        <v>44.601782349880828</v>
+        <v>31.645221028011292</v>
       </c>
     </row>
     <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="18">
-        <v>62.587679284555179</v>
+        <v>39.651232904288918</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="18">
-        <v>47.981402959431179</v>
+        <v>38.624180280603468</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="18">
-        <v>57.746497474145698</v>
+        <v>30.275298054726377</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="18">
-        <v>39.268318019440855</v>
+        <v>33.485360399354249</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="18">
-        <v>40.593793682408517</v>
+        <v>32.457574945874512</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="18">
-        <v>68.981146636466704</v>
+        <v>43.469868907496675</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="18">
-        <v>52.193130853285872</v>
+        <v>40.892417756210449</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="18">
-        <v>33.76091170487512</v>
+        <v>49.959278068806412</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18">
-        <v>50.171022483272182</v>
+        <v>33.819442035164684</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18">
-        <v>60.620977113570738</v>
+        <v>37.856629632879049</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="18">
-        <v>39.784466650531179</v>
+        <v>66.154856239566385</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="18">
-        <v>63.595008502574217</v>
+        <v>55.816313911518563</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="18">
-        <v>50.529974380471813</v>
+        <v>31.1981864226982</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="18">
-        <v>44.190483929113618</v>
+        <v>39.189103175885975</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="18">
-        <v>53.542574514794453</v>
+        <v>32.972748074680567</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="18">
-        <v>39.477142117733074</v>
+        <v>39.807592425495386</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="18">
-        <v>43.732251991134852</v>
+        <v>55.748269181038474</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="18">
-        <v>41.959239458331346</v>
+        <v>42.013864893767419</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="18">
-        <v>38.792495139376115</v>
+        <v>59.178414399406677</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="18">
-        <v>45.854655573468918</v>
+        <v>50.12521477353144</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="18">
-        <v>60.354771536885288</v>
+        <v>87.675613062339906</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="18">
-        <v>62.219049231687123</v>
+        <v>30.488174340651693</v>
       </c>
     </row>
     <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="18">
-        <v>45.52130275469495</v>
+        <v>31.602561503361489</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="18">
-        <v>49.924428774898615</v>
+        <v>55.443514394930453</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18">
-        <v>37.764960053846963</v>
+        <v>56.192054086035853</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="18">
-        <v>51.658304855015182</v>
+        <v>56.150123476433663</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="18">
-        <v>29.707599198619079</v>
+        <v>55.68656232081986</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="18">
-        <v>46.231772923103257</v>
+        <v>52.108126048601036</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="18">
-        <v>55.298751839191588</v>
+        <v>61.11078056380785</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="18">
-        <v>41.922572445910873</v>
+        <v>49.010764178189817</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="18">
-        <v>48.262933858575977</v>
+        <v>39.469132425729185</v>
       </c>
     </row>
     <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="18">
-        <v>44.476607929252594</v>
+        <v>34.490346286911517</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18">
-        <v>48.533536089568322</v>
+        <v>61.676710013272412</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="18">
-        <v>50.891699221834102</v>
+        <v>40.178170586004853</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="18">
-        <v>55.942113835665133</v>
+        <v>47.584741701673153</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="18">
-        <v>46.056943456482507</v>
+        <v>45.731316119888731</v>
       </c>
     </row>
     <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="18">
-        <v>58.216244888538114</v>
+        <v>55.215121841660505</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="18">
-        <v>52.217003100011731</v>
+        <v>32.609912313574071</v>
       </c>
     </row>
     <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="18">
-        <v>48.210090208151811</v>
+        <v>68.509276777478107</v>
       </c>
     </row>
     <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="18">
-        <v>62.0879827797365</v>
+        <v>41.674246587085797</v>
       </c>
     </row>
     <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="18">
-        <v>64.228945367396022</v>
+        <v>72.258166835091544</v>
       </c>
     </row>
     <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="18">
-        <v>20.131492243533419</v>
+        <v>33.935264372921168</v>
       </c>
     </row>
     <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="18">
-        <v>110.64886999472245</v>
+        <v>62.180283317410215</v>
       </c>
     </row>
     <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="18">
-        <v>32.941935085315933</v>
+        <v>45.977431022863271</v>
       </c>
     </row>
     <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="18">
-        <v>38.163113947951629</v>
+        <v>47.563953981104675</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="18">
-        <v>28.014152026886876</v>
+        <v>46.289589497561934</v>
       </c>
     </row>
     <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="18">
-        <v>37.31657769048735</v>
+        <v>35.568672852011275</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="18">
-        <v>62.196798206891565</v>
+        <v>52.65075185210145</v>
       </c>
     </row>
     <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="18">
-        <v>71.437812193563587</v>
+        <v>41.391437099616411</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="18">
-        <v>60.833312973349301</v>
+        <v>31.535752152121631</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="18">
-        <v>47.624045845330549</v>
+        <v>35.991911246117787</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="18">
-        <v>47.969146974682602</v>
+        <v>37.004774257075042</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="18">
-        <v>41.411513183912675</v>
+        <v>36.426826003007591</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="18">
-        <v>40.775685771027305</v>
+        <v>36.473699386697263</v>
       </c>
     </row>
     <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="18">
-        <v>37.87482306899652</v>
+        <v>47.995016471783998</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="18">
-        <v>36.109009913511997</v>
+        <v>38.942083126911427</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="18">
-        <v>58.135307145492682</v>
+        <v>38.489750877488405</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="18">
-        <v>66.807164265069304</v>
+        <v>37.104922577273101</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="18">
-        <v>53.720121887290681</v>
+        <v>66.423356354208835</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18">
-        <v>62.774840258291775</v>
+        <v>33.493768929038197</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18">
-        <v>47.137994499823385</v>
+        <v>35.440031850019146</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="18">
-        <v>42.151912174740652</v>
+        <v>45.77485809505302</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="18">
-        <v>51.059677931739131</v>
+        <v>32.561445453993244</v>
       </c>
     </row>
     <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18">
-        <v>28.741581848902054</v>
+        <v>58.733083101591831</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="18">
-        <v>41.54036883231511</v>
+        <v>54.14418962658084</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="18">
-        <v>40.373172130813913</v>
+        <v>30.812619506228231</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="18">
-        <v>55.702822738870395</v>
+        <v>92.30465666075888</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="18">
-        <v>11.42434803408441</v>
+        <v>39.329092456027865</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="18">
-        <v>49.053571153044992</v>
+        <v>50.524832247126291</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="18">
-        <v>45.577680998383187</v>
+        <v>31.928302756713844</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18">
-        <v>39.826789789901085</v>
+        <v>37.989236824214458</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18">
-        <v>38.979676161116856</v>
+        <v>46.942548611502531</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18">
-        <v>51.981276736960531</v>
+        <v>44.546492085161987</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18">
-        <v>20.98298801463104</v>
+        <v>34.785326840355992</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18">
-        <v>46.144000858098984</v>
+        <v>55.360773726037507</v>
       </c>
     </row>
   </sheetData>
@@ -5303,7 +4357,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1AB1787-7E2C-463B-98A7-8D63282CDE51}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5221BE-ABB9-4DA7-8EE9-96C1F5708535}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5655,7 +4709,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D22081-FD36-42B6-BF8C-2D7B79439F5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F78C825-D265-4744-BF95-2EA74E269665}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5665,7 +4719,1043 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>44.583323970004095</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>51.334447207766225</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>22.049299769270561</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>67.12353898825269</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>51.43348741741498</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>51.851061941192299</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>61.899850011110217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>45.089113454926675</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>58.022351957847448</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>27.918169643776512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>48.252400632490939</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>50.504048652608617</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>46.940464063830234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>32.477745204184998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>47.776046232762582</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>52.364536146374576</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>45.500856174103568</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>55.052096044162909</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>50.685613161086344</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
+        <v>49.66952996775624</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>104.0837872400076</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <v>48.138533562033437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>51.306818862784155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>50.20944889961028</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>75.063939489551288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>45.850919890213376</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <v>61.182874319803965</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>53.242645886564432</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18">
+        <v>48.457622052033251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>50.141780231489143</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18">
+        <v>54.727203415741691</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
+        <v>41.170085502511725</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18">
+        <v>45.643499747389342</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>49.679103878592088</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18">
+        <v>48.057261654852617</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
+        <v>69.936980427049335</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18">
+        <v>49.69352250939118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <v>68.62388039969656</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18">
+        <v>49.630861611768701</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
+        <v>46.252110620339266</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <v>33.849920369473907</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>61.040272273906567</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18">
+        <v>51.026349773822112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18">
+        <v>25.437813575006871</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>42.412842605243902</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18">
+        <v>62.686303636400751</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="18">
+        <v>42.704975764121997</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="18">
+        <v>49.587829692225341</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="18">
+        <v>40.78205054740252</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="18">
+        <v>41.946539670316461</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>45.353919743322727</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>51.583911931211553</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>43.714457679757274</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="18">
+        <v>52.37259939470421</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18">
+        <v>36.057837306818563</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="18">
+        <v>52.312866521311008</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="18">
+        <v>50.898708249164237</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="18">
+        <v>41.696665737883528</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18">
+        <v>44.350601057959913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="18">
+        <v>58.236466252153789</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="18">
+        <v>19.574030505252157</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="18">
+        <v>56.080188977948879</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="18">
+        <v>30.68074555636943</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="18">
+        <v>-12.204560354287352</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="18">
+        <v>45.220203620598937</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="18">
+        <v>17.633038518680848</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="18">
+        <v>52.558418096840398</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="18">
+        <v>53.918768547743881</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="18">
+        <v>56.972852118665365</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="18">
+        <v>58.026408528720026</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="18">
+        <v>42.542720247102906</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="18">
+        <v>48.323793455863751</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="18">
+        <v>50.092658671687573</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="18">
+        <v>45.229895119984732</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="18">
+        <v>52.728573385504006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="18">
+        <v>71.899363117058016</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="18">
+        <v>44.513348927234212</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="18">
+        <v>63.77864435299476</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="18">
+        <v>46.436575656511899</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="18">
+        <v>34.887998227138411</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="18">
+        <v>58.462021678261699</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="18">
+        <v>88.463061624052457</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>67.934703645557789</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="18">
+        <v>42.4628425000082</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="18">
+        <v>61.204939847809861</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="18">
+        <v>30.712805609794103</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="18">
+        <v>51.861494525023879</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="18">
+        <v>54.918184385449301</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="18">
+        <v>32.623603626472288</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="18">
+        <v>45.728197050296096</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="18">
+        <v>43.597926883139415</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="18">
+        <v>23.030243265509871</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="18">
+        <v>56.656211338615392</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="18">
+        <v>58.795607188661208</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="18">
+        <v>45.169194495007787</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="18">
+        <v>58.697729354499721</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="18">
+        <v>36.002693637123954</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="18">
+        <v>48.499856032151719</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="18">
+        <v>55.574792339894898</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="18">
+        <v>46.620051006744809</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="18">
+        <v>35.192832980731971</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="18">
+        <v>45.186132660524521</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="18">
+        <v>41.440002205863252</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="18">
+        <v>56.867720158468678</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="18">
+        <v>53.295696930395053</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="18">
+        <v>64.889311035448912</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="18">
+        <v>54.26200612782938</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="18">
+        <v>52.544742047961151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="18">
+        <v>40.523359873000345</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="18">
+        <v>46.446031997827333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="18">
+        <v>51.779561027162579</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="18">
+        <v>49.014194362670722</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="18">
+        <v>61.819034752771493</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="18">
+        <v>29.985690829060811</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="18">
+        <v>53.876783794405526</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="18">
+        <v>61.539812338110224</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="18">
+        <v>43.974827192966821</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="18">
+        <v>45.551346114953439</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="18">
+        <v>50.084261318972246</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="18">
+        <v>62.01638668237868</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="18">
+        <v>56.175165413494142</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="18">
+        <v>47.456388751873405</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="18">
+        <v>23.038518892969723</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="18">
+        <v>51.998571819711955</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="18">
+        <v>44.601782349880828</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="18">
+        <v>62.587679284555179</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="18">
+        <v>47.981402959431179</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="18">
+        <v>57.746497474145698</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="18">
+        <v>39.268318019440855</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="18">
+        <v>40.593793682408517</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="18">
+        <v>68.981146636466704</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="18">
+        <v>52.193130853285872</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="18">
+        <v>33.76091170487512</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="18">
+        <v>50.171022483272182</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="18">
+        <v>60.620977113570738</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="18">
+        <v>39.784466650531179</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="18">
+        <v>63.595008502574217</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="18">
+        <v>50.529974380471813</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="18">
+        <v>44.190483929113618</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="18">
+        <v>53.542574514794453</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="18">
+        <v>39.477142117733074</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="18">
+        <v>43.732251991134852</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="18">
+        <v>41.959239458331346</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="18">
+        <v>38.792495139376115</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="18">
+        <v>45.854655573468918</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="18">
+        <v>60.354771536885288</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="18">
+        <v>62.219049231687123</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="18">
+        <v>45.52130275469495</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="18">
+        <v>49.924428774898615</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="18">
+        <v>37.764960053846963</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="18">
+        <v>51.658304855015182</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="18">
+        <v>29.707599198619079</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="18">
+        <v>46.231772923103257</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="18">
+        <v>55.298751839191588</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="18">
+        <v>41.922572445910873</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="18">
+        <v>48.262933858575977</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="18">
+        <v>44.476607929252594</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="18">
+        <v>48.533536089568322</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="18">
+        <v>50.891699221834102</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="18">
+        <v>55.942113835665133</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="18">
+        <v>46.056943456482507</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="18">
+        <v>58.216244888538114</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="18">
+        <v>52.217003100011731</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="18">
+        <v>48.210090208151811</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="18">
+        <v>62.0879827797365</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="18">
+        <v>64.228945367396022</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="18">
+        <v>20.131492243533419</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="18">
+        <v>110.64886999472245</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="18">
+        <v>32.941935085315933</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="18">
+        <v>38.163113947951629</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="18">
+        <v>28.014152026886876</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="18">
+        <v>37.31657769048735</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="18">
+        <v>62.196798206891565</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="18">
+        <v>71.437812193563587</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="18">
+        <v>60.833312973349301</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="18">
+        <v>47.624045845330549</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="18">
+        <v>47.969146974682602</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="18">
+        <v>41.411513183912675</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="18">
+        <v>40.775685771027305</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="18">
+        <v>37.87482306899652</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="18">
+        <v>36.109009913511997</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="18">
+        <v>58.135307145492682</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="18">
+        <v>66.807164265069304</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="18">
+        <v>53.720121887290681</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="18">
+        <v>62.774840258291775</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="18">
+        <v>47.137994499823385</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="18">
+        <v>42.151912174740652</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="18">
+        <v>51.059677931739131</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="18">
+        <v>28.741581848902054</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="18">
+        <v>41.54036883231511</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="18">
+        <v>40.373172130813913</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="18">
+        <v>55.702822738870395</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="18">
+        <v>11.42434803408441</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="18">
+        <v>49.053571153044992</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="18">
+        <v>45.577680998383187</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="18">
+        <v>39.826789789901085</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="18">
+        <v>38.979676161116856</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="18">
+        <v>51.981276736960531</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="18">
+        <v>20.98298801463104</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="18">
+        <v>46.144000858098984</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F306312-682A-4B49-B219-A4B77B5CE0B4}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>44</v>
@@ -5676,7 +5766,7 @@
         <v>36.276933564652332</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5690,7 +5780,7 @@
         <v>35.639479476123725</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6691,7 +6781,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4B8F8E1-D3EA-4529-AA9C-37C09A026A94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C141E5-DFFE-42F8-A823-7E9A4AB58368}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7302,7 +7392,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C1057E-E043-443E-B9E6-93684BFA3AE2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD502498-124B-48ED-AB67-2E2294693E41}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7383,7 +7473,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC9B7CFF-DF81-44A4-8045-EDB354B45830}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ED0777-FE51-4C64-B1A6-AFDC393BEB0F}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7446,7 +7536,118 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FB71D2-195E-4CB6-AA06-02A71F065A49}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B883453-7822-4F94-B600-D08EE49C17FD}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
+        <v>11</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
+        <v>12</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>12</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
+        <v>13</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>14</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>14</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16096174-55E7-4D7D-8506-D791F994190E}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7456,7 +7657,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
@@ -7470,7 +7671,7 @@
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B2" s="14">
         <v>50</v>
@@ -7479,12 +7680,12 @@
         <v>10</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B3" s="14">
         <v>65</v>
@@ -7496,7 +7697,7 @@
     </row>
     <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
@@ -7509,96 +7710,6 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E5" s="16"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E6" s="16"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E7" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D24ED61-414C-4B80-9C0B-C3A684866A6A}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="22.625" customWidth="1"/>
-    <col min="5" max="5" width="60.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14">
-        <v>1</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B3" s="14">
-        <v>50</v>
-      </c>
-      <c r="C3" s="14">
-        <v>10</v>
-      </c>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="14">
-        <v>100</v>
-      </c>
-      <c r="C4" s="14">
-        <v>15</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="B5" s="14">
-        <v>10</v>
-      </c>
-      <c r="C5" s="14">
-        <v>3</v>
-      </c>
       <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -7617,7 +7728,97 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8B7772E-F367-43A0-97F3-85ECBA68A04C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A20569-32A7-49B9-8667-C19B13346CDC}">
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="3" width="22.625" customWidth="1"/>
+    <col min="5" max="5" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0</v>
+      </c>
+      <c r="C2" s="14">
+        <v>1</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="14">
+        <v>50</v>
+      </c>
+      <c r="C3" s="14">
+        <v>10</v>
+      </c>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="14">
+        <v>100</v>
+      </c>
+      <c r="C4" s="14">
+        <v>15</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="14">
+        <v>10</v>
+      </c>
+      <c r="C5" s="14">
+        <v>3</v>
+      </c>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116DA2AF-7763-4EBE-B2FA-E20D4F7859A4}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7627,7 +7828,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>29</v>
@@ -7639,7 +7840,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G1" s="15" t="s">
         <v>44</v>
@@ -7662,7 +7863,7 @@
         <v>-0.75</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7702,67 +7903,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74FE54B5-D87B-4DBB-97F2-E26BDE6BF044}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.625" customWidth="1"/>
-    <col min="3" max="3" width="60.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>2</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
-        <v>2</v>
-      </c>
-      <c r="C3" s="16"/>
-    </row>
-    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
-        <v>2</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
-        <v>2</v>
-      </c>
-      <c r="C5" s="16"/>
-    </row>
-    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
-        <v>12</v>
-      </c>
-      <c r="C6" s="16"/>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="16"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="C4:C7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0398793E-B21E-484A-AA3E-76164D6B6188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17B669C1-94DC-487F-A994-8DC06F67240F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{1438BA25-5DE2-4CE4-BAFD-4ED64237E948}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{4D7CAE42-A276-43C5-8ABA-098102ED0B2C}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="135">
   <si>
     <t>Normální model</t>
   </si>
@@ -164,6 +164,9 @@
     <t>Směrodatná odchylka</t>
   </si>
   <si>
+    <t>Modelový podíl (P–P)</t>
+  </si>
+  <si>
     <t>Autorská ilustrační data, již seřazená vzestupně.</t>
   </si>
   <si>
@@ -179,6 +182,9 @@
     <t>Graf a vzorce se přepočítají. Data nemají být prázdná.</t>
   </si>
   <si>
+    <t>Sloupec F a druhý graf: nepovinný P–P graf (podíl C proti F).</t>
+  </si>
+  <si>
     <t>Test</t>
   </si>
   <si>
@@ -449,10 +455,10 @@
     <t>QQ</t>
   </si>
   <si>
-    <t>A1:N24</t>
-  </si>
-  <si>
-    <t>Hotový Q–Q graf a mezivýpočty</t>
+    <t>A1:N44</t>
+  </si>
+  <si>
+    <t>Hotový Q–Q graf, nepovinný P–P graf a mezivýpočty</t>
   </si>
 </sst>
 </file>
@@ -781,7 +787,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-EAE0-4798-AD56-A1C7D1F98722}"/>
+              <c16:uniqueId val="{00000008-5923-4FD2-95A5-F36A1562BCA4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -895,7 +901,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000006-EAE0-4798-AD56-A1C7D1F98722}"/>
+              <c16:uniqueId val="{00000009-5923-4FD2-95A5-F36A1562BCA4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -907,11 +913,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="745567471"/>
-        <c:axId val="745569871"/>
+        <c:axId val="926123087"/>
+        <c:axId val="926139887"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="745567471"/>
+        <c:axId val="926123087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -941,13 +947,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="745569871"/>
+        <c:crossAx val="926139887"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="745569871"/>
+        <c:axId val="926139887"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -975,9 +981,405 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="745567471"/>
+        <c:crossAx val="926123087"/>
         <c:crossesAt val="-2"/>
         <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1100">
+          <a:latin typeface="Arial"/>
+          <a:ea typeface="Arial"/>
+          <a:cs typeface="Arial"/>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="cs-CZ"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="cs-CZ"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1500"/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="cs-CZ"/>
+              <a:t>P–P graf (nepovinné)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Pozorované skóry</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="245D78"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="245D78"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>QQ!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.1666666666666664E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29166666666666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45833333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.70833333333333337</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95833333333333337</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>QQ!$F$2:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.769730764606428E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11068209655016407</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18689726251601743</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.28915069200159116</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3693706912104468</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45573937647191709</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54426062352808291</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.63062930878955314</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.71084930799840884</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.81310273748398254</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.88931790344983597</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95230269235393572</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-C1AF-4EF5-B986-BA8CCCA5CCA6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Úhlopříčka</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="B54E24"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>QQ!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.1666666666666664E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29166666666666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45833333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.70833333333333337</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95833333333333337</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>QQ!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>4.1666666666666664E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.125</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.20833333333333334</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29166666666666669</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.45833333333333331</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.54166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.70833333333333337</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.79166666666666663</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.875</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95833333333333337</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-C1AF-4EF5-B986-BA8CCCA5CCA6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="926140847"/>
+        <c:axId val="926141807"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="926140847"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Empirický podíl (i − 0,5)/n</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="926141807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="926141807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="cs-CZ"/>
+                  <a:t>Modelový podíl</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="low"/>
+        <c:crossAx val="926140847"/>
+        <c:crossesAt val="0"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="0.2"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -1028,7 +1430,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -1037,7 +1439,7 @@
         <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{37C1594E-9CC9-7DB9-19DB-3F578DE163B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10960FCE-1690-9B43-17A9-A519702ED5E2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1050,6 +1452,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graf 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B22F1649-BBFC-B11B-F6D3-B55EB3646688}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1374,7 +1812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E27B6E61-0262-4D90-BBD2-C7BA3F454103}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7849B37D-BCF4-40D6-9787-0C4984086B4D}">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1384,7 +1822,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1396,261 +1834,261 @@
     </row>
     <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -1681,7 +2119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B9E61E6-00FC-419B-9B7A-E49DF6B8C37D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF47257B-D556-4CBF-8BE3-DCCDC9094036}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1691,10 +2129,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1702,7 +2140,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1716,7 +2154,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1744,7 +2182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{462F306F-A11D-4964-A7B7-D3FD7BF2220D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B361C5-71DB-4A17-A6CA-D70A333C62AF}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1755,13 +2193,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1772,7 +2210,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1786,13 +2224,13 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B4" s="14">
         <v>0.08</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1806,7 +2244,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B6" s="14">
         <v>25</v>
@@ -1826,7 +2264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D276C9B-2F55-4BE7-933F-3139D58A4CEB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB73AF7-F141-4EF2-8D8B-77FFCDA82420}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1837,13 +2275,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1854,7 +2292,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1874,7 +2312,7 @@
         <v>45</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1888,7 +2326,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B6" s="14">
         <v>20</v>
@@ -1897,7 +2335,7 @@
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="14">
         <v>8</v>
@@ -1914,7 +2352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75310E57-8FBC-44BF-8A5B-9AC9B8D0C390}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4CE6EF-58FE-4E1A-9480-CC492BFA52D1}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1925,13 +2363,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1942,7 +2380,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1962,12 +2400,12 @@
         <v>0.2</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B5" s="14">
         <v>0.1</v>
@@ -1996,7 +2434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C639198E-DD95-4814-A3B5-4D9260DAEB0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E4B569-A307-4C3F-B353-B0E60BD74045}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2007,13 +2445,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2024,7 +2462,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2038,18 +2476,18 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B5" s="14">
         <v>1</v>
@@ -2072,7 +2510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B06EDD05-5EA0-41D6-824E-7FCC3534AEB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CA0501-B3DD-484A-B669-19EB6AD1EE29}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2082,10 +2520,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2093,7 +2531,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2107,7 +2545,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2132,7 +2570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87D11453-789F-44C0-BBBF-36866B411727}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7EF3EB-0FAC-436F-90C6-DEE23E3E1CBC}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2142,10 +2580,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2153,7 +2591,7 @@
         <v>1.2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2167,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2189,7 +2627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE71178-2FCE-4938-B597-766959C90267}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9DAE74E-57D2-43A4-B6D8-7568045F64DB}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2202,7 +2640,7 @@
         <v>29</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2210,7 +2648,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2224,7 +2662,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2285,7 +2723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54380A08-7C38-44BF-83B2-CB3D16410124}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BAEAC4-3ACF-4266-A47F-536DC248CB8C}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2295,10 +2733,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2306,7 +2744,7 @@
         <v>48.85602655957382</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2320,7 +2758,7 @@
         <v>29.327651524791108</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3321,7 +3759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54225AB0-0774-4D9A-9F04-0F325C889366}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB78D65-9D37-474D-8F96-367C6AB89E87}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3331,10 +3769,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3342,7 +3780,7 @@
         <v>66.073597304495223</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3356,7 +3794,7 @@
         <v>80.020527650875579</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4357,7 +4795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5221BE-ABB9-4DA7-8EE9-96C1F5708535}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C92F48-9441-477F-908F-1D4ECAE41637}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4709,7 +5147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F78C825-D265-4744-BF95-2EA74E269665}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8BEEDE-1ABD-4344-9A3A-D5F30647120C}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4719,10 +5157,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4730,7 +5168,7 @@
         <v>44.583323970004095</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4744,7 +5182,7 @@
         <v>22.049299769270561</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5745,7 +6183,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F306312-682A-4B49-B219-A4B77B5CE0B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6565B5-5BFB-4253-9F1C-6FC18720DA8E}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5755,10 +6193,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5766,7 +6204,7 @@
         <v>36.276933564652332</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5780,7 +6218,7 @@
         <v>35.639479476123725</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6781,14 +7219,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56C141E5-DFFE-42F8-A823-7E9A4AB58368}">
-  <dimension ref="A1:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0BDCF0A-4AA9-4A26-A410-C5113EC45D33}">
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.625" customWidth="1"/>
     <col min="2" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="5" width="20.625" customWidth="1"/>
-    <col min="6" max="6" width="3.625" customWidth="1"/>
+    <col min="6" max="6" width="16.625" customWidth="1"/>
     <col min="7" max="7" width="26.625" customWidth="1"/>
     <col min="8" max="8" width="12.625" customWidth="1"/>
     <col min="9" max="14" width="15.625" customWidth="1"/>
@@ -6810,7 +7248,9 @@
       <c r="E1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="F1" s="4" t="s">
+        <v>36</v>
+      </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
@@ -6839,7 +7279,10 @@
         <f>$H$3+$H$4*D2</f>
         <v>34.423768669978713</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="13">
+        <f>_xlfn.NORM.S.DIST((B2-$H$3)/$H$4,TRUE)</f>
+        <v>4.769730764606428E-2</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>33</v>
       </c>
@@ -6873,7 +7316,10 @@
         <f t="shared" ref="E3:E13" si="2">$H$3+$H$4*D3</f>
         <v>39.652667053034193</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="13">
+        <f t="shared" ref="F3:F13" si="3">_xlfn.NORM.S.DIST((B3-$H$3)/$H$4,TRUE)</f>
+        <v>0.11068209655016407</v>
+      </c>
       <c r="G3" s="2" t="s">
         <v>34</v>
       </c>
@@ -6907,7 +7353,10 @@
         <f t="shared" si="2"/>
         <v>42.694143048240605</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="F4" s="13">
+        <f t="shared" si="3"/>
+        <v>0.18689726251601743</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>35</v>
       </c>
@@ -6941,7 +7390,10 @@
         <f t="shared" si="2"/>
         <v>45.066070548017578</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="F5" s="13">
+        <f t="shared" si="3"/>
+        <v>0.28915069200159116</v>
+      </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -6970,7 +7422,10 @@
         <f t="shared" si="2"/>
         <v>47.133855465831509</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="13">
+        <f t="shared" si="3"/>
+        <v>0.3693706912104468</v>
+      </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -6999,7 +7454,10 @@
         <f t="shared" si="2"/>
         <v>49.058827499627533</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="13">
+        <f t="shared" si="3"/>
+        <v>0.45573937647191709</v>
+      </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -7028,7 +7486,10 @@
         <f t="shared" si="2"/>
         <v>50.941172500372467</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="13">
+        <f t="shared" si="3"/>
+        <v>0.54426062352808291</v>
+      </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -7057,7 +7518,10 @@
         <f t="shared" si="2"/>
         <v>52.866144534168491</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="13">
+        <f t="shared" si="3"/>
+        <v>0.63062930878955314</v>
+      </c>
       <c r="G9" s="1"/>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -7086,7 +7550,10 @@
         <f t="shared" si="2"/>
         <v>54.933929451982429</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="13">
+        <f t="shared" si="3"/>
+        <v>0.71084930799840884</v>
+      </c>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -7115,7 +7582,10 @@
         <f t="shared" si="2"/>
         <v>57.305856951759395</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="13">
+        <f t="shared" si="3"/>
+        <v>0.81310273748398254</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -7144,7 +7614,10 @@
         <f t="shared" si="2"/>
         <v>60.347332946965807</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="13">
+        <f t="shared" si="3"/>
+        <v>0.88931790344983597</v>
+      </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -7173,7 +7646,10 @@
         <f t="shared" si="2"/>
         <v>65.576231330021287</v>
       </c>
-      <c r="F13" s="1"/>
+      <c r="F13" s="13">
+        <f t="shared" si="3"/>
+        <v>0.95230269235393572</v>
+      </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -7217,7 +7693,7 @@
     </row>
     <row r="16" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -7251,7 +7727,7 @@
     </row>
     <row r="18" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7269,7 +7745,7 @@
     </row>
     <row r="19" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -7303,7 +7779,7 @@
     </row>
     <row r="21" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7321,7 +7797,7 @@
     </row>
     <row r="22" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -7354,7 +7830,9 @@
       <c r="N23" s="1"/>
     </row>
     <row r="24" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
+      <c r="A24" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -7385,6 +7863,310 @@
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
     </row>
+    <row r="26" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+    </row>
+    <row r="31" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+    </row>
+    <row r="32" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+    </row>
+    <row r="34" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+    </row>
+    <row r="35" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+    </row>
+    <row r="36" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+    </row>
+    <row r="37" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+    </row>
+    <row r="38" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+    </row>
+    <row r="39" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+    </row>
+    <row r="40" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+    </row>
+    <row r="41" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+    </row>
+    <row r="42" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+    </row>
+    <row r="43" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+    </row>
+    <row r="44" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7392,7 +8174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD502498-124B-48ED-AB67-2E2294693E41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9D5632-074D-4C02-98A3-5FA4AFC2ECE9}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7402,7 +8184,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>29</v>
@@ -7414,12 +8196,12 @@
         <v>3</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="14">
         <v>60</v>
@@ -7431,12 +8213,12 @@
         <v>10</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="14">
         <v>42</v>
@@ -7451,7 +8233,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -7473,7 +8255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17ED0777-FE51-4C64-B1A6-AFDC393BEB0F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C933BD-B5A1-43E1-9161-CD10CD1EFBF2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7483,10 +8265,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7494,7 +8276,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7508,7 +8290,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7536,7 +8318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B883453-7822-4F94-B600-D08EE49C17FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20AFE5D-C6D9-4C19-B2DD-F8C6B369B004}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7546,10 +8328,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7557,7 +8339,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7571,7 +8353,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7647,7 +8429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16096174-55E7-4D7D-8506-D791F994190E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF8DF5-2501-42D5-B6F3-763F77815F1D}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7657,7 +8439,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
@@ -7666,12 +8448,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" s="14">
         <v>50</v>
@@ -7680,12 +8462,12 @@
         <v>10</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B3" s="14">
         <v>65</v>
@@ -7697,7 +8479,7 @@
     </row>
     <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
@@ -7706,7 +8488,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -7728,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A20569-32A7-49B9-8667-C19B13346CDC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE3403D-288D-41C2-88AA-458E0B879844}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7738,7 +8520,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>34</v>
@@ -7747,12 +8529,12 @@
         <v>35</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="14">
         <v>0</v>
@@ -7761,12 +8543,12 @@
         <v>1</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B3" s="14">
         <v>50</v>
@@ -7778,7 +8560,7 @@
     </row>
     <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B4" s="14">
         <v>100</v>
@@ -7787,12 +8569,12 @@
         <v>15</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="14">
         <v>10</v>
@@ -7818,7 +8600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116DA2AF-7763-4EBE-B2FA-E20D4F7859A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DED6BBD-49ED-46CA-A9EE-35F54E57D19C}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7828,7 +8610,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>29</v>
@@ -7840,15 +8622,15 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" s="14">
         <v>62</v>
@@ -7863,12 +8645,12 @@
         <v>-0.75</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" s="14">
         <v>62</v>
@@ -7884,7 +8666,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G4" s="17" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17B669C1-94DC-487F-A994-8DC06F67240F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B62199-8425-4B8B-890F-0EDC01EE7FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{4D7CAE42-A276-43C5-8ABA-098102ED0B2C}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{E165FF1A-5F0A-49E9-A088-3B78EC568C0A}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
     <t>Simulovaný skór (body)</t>
   </si>
   <si>
-    <t>Obrázky histogramů a Q–Q grafů</t>
+    <t>Obrázky histogramů a Q–Q grafů; šikmost a exces</t>
   </si>
   <si>
     <t>Simulovaná data z obrázků kapitoly, 200 hodnot. Nejde o skutečný test ani o nezadaná individuální data cvičení 10.</t>
@@ -787,7 +787,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-5923-4FD2-95A5-F36A1562BCA4}"/>
+              <c16:uniqueId val="{00000008-95A6-40DD-A3E5-F863981A32F3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -901,7 +901,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-5923-4FD2-95A5-F36A1562BCA4}"/>
+              <c16:uniqueId val="{00000009-95A6-40DD-A3E5-F863981A32F3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -913,11 +913,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="926123087"/>
-        <c:axId val="926139887"/>
+        <c:axId val="883778752"/>
+        <c:axId val="883780672"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="926123087"/>
+        <c:axId val="883778752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -947,13 +947,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="926139887"/>
+        <c:crossAx val="883780672"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="926139887"/>
+        <c:axId val="883780672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -981,7 +981,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="926123087"/>
+        <c:crossAx val="883778752"/>
         <c:crossesAt val="-2"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1180,7 +1180,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-C1AF-4EF5-B986-BA8CCCA5CCA6}"/>
+              <c16:uniqueId val="{00000008-5D1E-41BF-AB08-D3562C30A25F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1294,7 +1294,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-C1AF-4EF5-B986-BA8CCCA5CCA6}"/>
+              <c16:uniqueId val="{00000009-5D1E-41BF-AB08-D3562C30A25F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1306,11 +1306,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="926140847"/>
-        <c:axId val="926141807"/>
+        <c:axId val="1695869903"/>
+        <c:axId val="1695872783"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="926140847"/>
+        <c:axId val="1695869903"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1340,13 +1340,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="926141807"/>
+        <c:crossAx val="1695872783"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="926141807"/>
+        <c:axId val="1695872783"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1376,7 +1376,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="926140847"/>
+        <c:crossAx val="1695869903"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
@@ -1439,7 +1439,7 @@
         <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10960FCE-1690-9B43-17A9-A519702ED5E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{040D4174-3722-268F-56DF-4B97B205973C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1475,7 +1475,7 @@
         <xdr:cNvPr id="3" name="Graf 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B22F1649-BBFC-B11B-F6D3-B55EB3646688}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BB7C2C4-5A7E-C207-B493-230EBB0329A5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1812,7 +1812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7849B37D-BCF4-40D6-9787-0C4984086B4D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC759E7-29C3-4B04-A857-C3D0C6A96419}">
   <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2119,7 +2119,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF47257B-D556-4CBF-8BE3-DCCDC9094036}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C82B95-3B33-4010-8314-72191CB408AA}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2182,7 +2182,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2B361C5-71DB-4A17-A6CA-D70A333C62AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A58480-5BC6-4F86-AAA8-40A08A10A12C}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2264,7 +2264,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB73AF7-F141-4EF2-8D8B-77FFCDA82420}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6AB753-2C1C-4C8E-840D-9B25C76BB77D}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2352,7 +2352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4CE6EF-58FE-4E1A-9480-CC492BFA52D1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3936583F-D594-4C23-9660-AB8EC155A6DE}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2434,7 +2434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E4B569-A307-4C3F-B353-B0E60BD74045}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2626B2D-E3CA-43E0-8B6C-3963C1CC9F31}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2510,7 +2510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CA0501-B3DD-484A-B669-19EB6AD1EE29}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB95700-F352-4E62-B217-0B56CF2143E5}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2570,7 +2570,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7EF3EB-0FAC-436F-90C6-DEE23E3E1CBC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ACB1AE-ACBB-4347-AFF0-62E135F55DE1}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2627,7 +2627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9DAE74E-57D2-43A4-B6D8-7568045F64DB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95530D35-B61C-4308-B4F2-3742B7ACEB47}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2723,7 +2723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27BAEAC4-3ACF-4266-A47F-536DC248CB8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DE2AB6-FADC-4B0C-BC8E-1CEA3ED8EA67}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3759,7 +3759,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AB78D65-9D37-474D-8F96-367C6AB89E87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2261A7-86A8-49E7-8BCB-CEB28EA0B313}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4795,7 +4795,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C92F48-9441-477F-908F-1D4ECAE41637}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8580E3-BC35-4CE3-B51B-75E91D498FF4}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5147,7 +5147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8BEEDE-1ABD-4344-9A3A-D5F30647120C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33B4A1C-4578-44C5-BDC8-8F47C4E52632}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6183,7 +6183,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6565B5-5BFB-4253-9F1C-6FC18720DA8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D3D00-2798-491C-BDE7-C7C8787D5FA4}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7219,7 +7219,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0BDCF0A-4AA9-4A26-A410-C5113EC45D33}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C955F2F1-43C9-4F71-B669-1BE51AD809F7}">
   <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8174,7 +8174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9D5632-074D-4C02-98A3-5FA4AFC2ECE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B127E1C0-C15F-44EB-AF34-589FAF6EC930}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8255,7 +8255,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25C933BD-B5A1-43E1-9161-CD10CD1EFBF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E736E3B-C501-4318-B90E-1A395ED65A30}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8318,7 +8318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20AFE5D-C6D9-4C19-B2DD-F8C6B369B004}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C1634D-F83A-45C5-8EE7-D99343FB5988}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8429,7 +8429,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDF8DF5-2501-42D5-B6F3-763F77815F1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC518FD-1DE2-43D8-BFAF-75317D2A1417}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8510,7 +8510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CE3403D-288D-41C2-88AA-458E0B879844}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FACE664-974F-4E86-90E6-D73B6AB7E193}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8600,7 +8600,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DED6BBD-49ED-46CA-A9EE-35F54E57D19C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E104B4FA-42D2-468E-8CCA-A100AF1CEB7C}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>

--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33B62199-8425-4B8B-890F-0EDC01EE7FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C144945-8A9B-4502-831F-D27AD408A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{E165FF1A-5F0A-49E9-A088-3B78EC568C0A}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{4A0A6F10-B855-443F-A03E-A1F9BEA70190}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,8 @@
     <sheet name="Sim_sikme" sheetId="19" r:id="rId19"/>
     <sheet name="Sim_chvosty" sheetId="20" r:id="rId20"/>
     <sheet name="Sim_smes" sheetId="21" r:id="rId21"/>
+    <sheet name="Sim_sikme_vlevo" sheetId="22" r:id="rId22"/>
+    <sheet name="Sim_lehke" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="135">
   <si>
     <t>Normální model</t>
   </si>
@@ -83,13 +85,13 @@
     <t>Přímý převod na podíl</t>
   </si>
   <si>
-    <t>Dolní hranice (body)</t>
-  </si>
-  <si>
-    <t>Horní hranice (body)</t>
-  </si>
-  <si>
-    <t>Podíl mezi hranicemi</t>
+    <t>Dolní mez (body)</t>
+  </si>
+  <si>
+    <t>Horní mez (body)</t>
+  </si>
+  <si>
+    <t>Podíl mezi mezemi</t>
   </si>
   <si>
     <t>Podíl vlevo</t>
@@ -110,12 +112,6 @@
     <t>Podíl v jednom chvostu</t>
   </si>
   <si>
-    <t>Dolní mez (body)</t>
-  </si>
-  <si>
-    <t>Horní mez (body)</t>
-  </si>
-  <si>
     <t>Autorský ilustrační model skóru pozornosti.</t>
   </si>
   <si>
@@ -444,6 +440,12 @@
   </si>
   <si>
     <t>Sim_smes</t>
+  </si>
+  <si>
+    <t>Sim_sikme_vlevo</t>
+  </si>
+  <si>
+    <t>Sim_lehke</t>
   </si>
   <si>
     <t>A1:D25</t>
@@ -787,7 +789,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-95A6-40DD-A3E5-F863981A32F3}"/>
+              <c16:uniqueId val="{00000008-9256-44C1-94FC-FB2158D72C35}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -901,7 +903,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-95A6-40DD-A3E5-F863981A32F3}"/>
+              <c16:uniqueId val="{00000009-9256-44C1-94FC-FB2158D72C35}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -913,11 +915,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="883778752"/>
-        <c:axId val="883780672"/>
+        <c:axId val="1164856047"/>
+        <c:axId val="1164867567"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="883778752"/>
+        <c:axId val="1164856047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -947,13 +949,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="883780672"/>
+        <c:crossAx val="1164867567"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="883780672"/>
+        <c:axId val="1164867567"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -981,7 +983,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="883778752"/>
+        <c:crossAx val="1164856047"/>
         <c:crossesAt val="-2"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1180,7 +1182,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-5D1E-41BF-AB08-D3562C30A25F}"/>
+              <c16:uniqueId val="{00000008-8AE5-4A1E-AC68-9000AE458192}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1294,7 +1296,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-5D1E-41BF-AB08-D3562C30A25F}"/>
+              <c16:uniqueId val="{00000009-8AE5-4A1E-AC68-9000AE458192}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1306,11 +1308,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1695869903"/>
-        <c:axId val="1695872783"/>
+        <c:axId val="1164868047"/>
+        <c:axId val="1164864207"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1695869903"/>
+        <c:axId val="1164868047"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1340,13 +1342,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1695872783"/>
+        <c:crossAx val="1164864207"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1695872783"/>
+        <c:axId val="1164864207"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1376,7 +1378,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1695869903"/>
+        <c:crossAx val="1164868047"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
@@ -1439,7 +1441,7 @@
         <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{040D4174-3722-268F-56DF-4B97B205973C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2A79358-AF4E-7A75-A44F-6445F2BF10F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1475,7 +1477,7 @@
         <xdr:cNvPr id="3" name="Graf 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BB7C2C4-5A7E-C207-B493-230EBB0329A5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C7D836E-DF92-0645-F46E-14BB2019E792}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1812,8 +1814,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEC759E7-29C3-4B04-A857-C3D0C6A96419}">
-  <dimension ref="A1:C30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0D22CF-D47E-4A75-B463-15DA91FAD1B8}">
+  <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="25.625" customWidth="1"/>
@@ -1822,7 +1824,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1834,277 +1836,299 @@
     </row>
     <row r="3" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
     </row>
     <row r="5" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
     </row>
     <row r="7" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B29" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-    </row>
-    <row r="29" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
     </row>
     <row r="30" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" ht="30.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2119,7 +2143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C82B95-3B33-4010-8314-72191CB408AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B748F50A-6420-4E90-9FA9-A0D7CD1F0D94}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2129,10 +2153,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2140,7 +2164,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2154,7 +2178,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2182,7 +2206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A58480-5BC6-4F86-AAA8-40A08A10A12C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E910E5-A7EA-46E2-B9D9-C1736470A5C6}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2193,13 +2217,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2210,7 +2234,7 @@
         <v>80</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2224,13 +2248,13 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B4" s="14">
         <v>0.08</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2244,7 +2268,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B6" s="14">
         <v>25</v>
@@ -2264,7 +2288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F6AB753-2C1C-4C8E-840D-9B25C76BB77D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B69289-AA34-4DAC-9BEE-8F3B8A5803DD}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2275,13 +2299,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2292,7 +2316,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2306,18 +2330,18 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B4" s="14">
         <v>45</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B5" s="14">
         <v>65</v>
@@ -2326,7 +2350,7 @@
     </row>
     <row r="6" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B6" s="14">
         <v>20</v>
@@ -2335,7 +2359,7 @@
     </row>
     <row r="7" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" s="14">
         <v>8</v>
@@ -2352,7 +2376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3936583F-D594-4C23-9660-AB8EC155A6DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D8E3D3-546F-4A6C-AD33-66F8A2F80212}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2363,13 +2387,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2380,7 +2404,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2400,12 +2424,12 @@
         <v>0.2</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="14">
         <v>0.1</v>
@@ -2434,7 +2458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2626B2D-E3CA-43E0-8B6C-3963C1CC9F31}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79986BEA-76C8-4AD1-B44A-B6C7819420F2}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2445,13 +2469,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2462,7 +2486,7 @@
         <v>50</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2476,18 +2500,18 @@
     </row>
     <row r="4" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B5" s="14">
         <v>1</v>
@@ -2510,7 +2534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB95700-F352-4E62-B217-0B56CF2143E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDAE8B7-77C0-4C72-B2EA-90A234D545B7}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2520,10 +2544,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2531,7 +2555,7 @@
         <v>38</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2545,7 +2569,7 @@
         <v>60</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2570,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40ACB1AE-ACBB-4347-AFF0-62E135F55DE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A303A4A-A3B5-4525-A43F-660AC44E0F1F}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2580,10 +2604,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2591,7 +2615,7 @@
         <v>1.2</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2605,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2627,7 +2651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95530D35-B61C-4308-B4F2-3742B7ACEB47}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A2BDE6-7B4C-449C-AAAE-555802B61CF4}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2637,10 +2661,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2648,7 +2672,7 @@
         <v>35</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2662,7 +2686,7 @@
         <v>42</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2723,7 +2747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36DE2AB6-FADC-4B0C-BC8E-1CEA3ED8EA67}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E828F21-B68F-4E38-A94E-ECC0917A572A}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2733,10 +2757,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2744,7 +2768,7 @@
         <v>48.85602655957382</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2758,7 +2782,7 @@
         <v>29.327651524791108</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3759,7 +3783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2261A7-86A8-49E7-8BCB-CEB28EA0B313}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E76D6B6-F167-402B-8BDE-5F02A7D14F80}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3769,10 +3793,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3780,7 +3804,7 @@
         <v>66.073597304495223</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -3794,7 +3818,7 @@
         <v>80.020527650875579</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4795,7 +4819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C8580E3-BC35-4CE3-B51B-75E91D498FF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F894E161-84B4-4807-93E3-0CEA1F45BF2D}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4827,7 +4851,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -4841,7 +4865,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -4863,7 +4887,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -4891,7 +4915,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -4906,7 +4930,7 @@
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -4929,7 +4953,7 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
@@ -4943,7 +4967,7 @@
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -4978,7 +5002,7 @@
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -5085,7 +5109,7 @@
     </row>
     <row r="24" spans="1:6" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B24" s="9">
         <f>_xlfn.NORM.INV(B23,B2,B3)</f>
@@ -5098,7 +5122,7 @@
     </row>
     <row r="25" spans="1:6" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B25" s="9">
         <f>_xlfn.NORM.INV(1-B23,B2,B3)</f>
@@ -5147,7 +5171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33B4A1C-4578-44C5-BDC8-8F47C4E52632}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2E6DD1-5EE5-4142-AEE5-8E3011462CAA}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5157,10 +5181,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5168,7 +5192,7 @@
         <v>44.583323970004095</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5182,7 +5206,7 @@
         <v>22.049299769270561</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6183,7 +6207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B01D3D00-2798-491C-BDE7-C7C8787D5FA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130DFEC5-EC78-4A0A-846D-285700F57BB0}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6193,10 +6217,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6204,7 +6228,7 @@
         <v>36.276933564652332</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -6218,7 +6242,7 @@
         <v>35.639479476123725</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7207,6 +7231,2078 @@
     <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18">
         <v>62.217355862155749</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F3CFAA-E4F1-4676-97C7-96704803B99F}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>68.15406359732151</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>65.903256717137992</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>63.971926025114954</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>63.684091111645103</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>44.085506481447453</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>66.256279135122895</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>69.003366821229676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>30.66381408252645</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>64.901006795548994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>69.439091901294887</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>57.748960871669517</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>65.837693950161338</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>59.622667422938221</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>51.881279685443403</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>63.323133820667863</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>69.770360249094665</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>63.672768254764378</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>21.836418325739373</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>67.852026061154902</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
+        <v>69.40068556429209</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>68.862554035149515</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <v>61.330015398199969</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>59.749066923233741</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>67.303809864563547</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>37.665798516761775</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>61.422756836238385</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <v>66.229441935704969</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>65.365416743070568</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18">
+        <v>69.163908791731359</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>66.183201628737152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18">
+        <v>48.499367964782948</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
+        <v>69.989033644087613</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18">
+        <v>63.89130306430161</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>63.073906661011279</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18">
+        <v>61.292501417452378</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
+        <v>63.190186279825866</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18">
+        <v>65.417461488395929</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <v>64.997382666915655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18">
+        <v>69.372790437191725</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
+        <v>67.213252182118595</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <v>68.628837061114609</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>64.152404759079218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18">
+        <v>69.186743353493512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18">
+        <v>50.647774171924354</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>62.881567078131319</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18">
+        <v>64.536593542434275</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="18">
+        <v>66.237899428233504</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="18">
+        <v>69.82309999410063</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="18">
+        <v>66.381855397485197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="18">
+        <v>53.309334070330621</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>44.723450673141713</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>68.318493459373713</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>27.141006703215112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="18">
+        <v>59.166635116982334</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18">
+        <v>49.21822575936293</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="18">
+        <v>67.251667319796979</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="18">
+        <v>64.051090343855321</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="18">
+        <v>69.163206345401704</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18">
+        <v>60.187724819826961</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="18">
+        <v>67.126636286266148</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="18">
+        <v>68.19448544178158</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="18">
+        <v>61.934845401394249</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="18">
+        <v>67.325844308122299</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="18">
+        <v>48.592788783231015</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="18">
+        <v>68.80921034142375</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="18">
+        <v>53.927314915603162</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="18">
+        <v>67.184346038848162</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="18">
+        <v>64.984008702449501</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="18">
+        <v>68.681420953944325</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="18">
+        <v>57.162500620308393</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="18">
+        <v>28.56183136092065</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="18">
+        <v>64.845928973518312</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="18">
+        <v>33.860786308682705</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="18">
+        <v>64.824970536865294</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="18">
+        <v>69.035267727449536</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="18">
+        <v>69.860888523980975</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="18">
+        <v>60.814164150926352</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="18">
+        <v>62.222131687605568</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="18">
+        <v>54.138825876698739</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="18">
+        <v>51.774967835193635</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="18">
+        <v>60.725120949047685</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="18">
+        <v>60.442665107968331</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>43.09331620238089</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="18">
+        <v>61.08277672943759</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="18">
+        <v>68.599343481473625</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="18">
+        <v>69.957813219505113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="18">
+        <v>67.37631868892575</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="18">
+        <v>63.806246984750032</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="18">
+        <v>65.007871212437749</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="18">
+        <v>59.400562998327487</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="18">
+        <v>60.050475104200721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="18">
+        <v>61.36010745424295</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="18">
+        <v>63.697921088896692</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="18">
+        <v>61.835123121765385</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="18">
+        <v>66.162578742951155</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="18">
+        <v>63.177781314589083</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="18">
+        <v>67.223013770733857</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="18">
+        <v>26.952396220120814</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="18">
+        <v>61.409417828965069</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="18">
+        <v>63.939713072031736</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="18">
+        <v>69.711294073748903</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="18">
+        <v>50.358935502266647</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="18">
+        <v>63.675325699150562</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="18">
+        <v>65.740929935127497</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="18">
+        <v>60.318842409598709</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="18">
+        <v>63.164688120596111</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="18">
+        <v>69.720857515164695</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="18">
+        <v>68.172278606654459</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="18">
+        <v>55.127329473292583</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="18">
+        <v>66.689402391541037</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="18">
+        <v>59.711335748854154</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="18">
+        <v>69.785951757803559</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="18">
+        <v>68.368981926155584</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="18">
+        <v>57.907977281558388</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="18">
+        <v>69.502522514836613</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="18">
+        <v>67.168812085874379</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="18">
+        <v>65.109582911289735</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="18">
+        <v>60.784521822038627</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="18">
+        <v>63.621471753819804</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="18">
+        <v>44.529263657846691</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="18">
+        <v>61.603337453598513</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="18">
+        <v>62.634366974654675</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="18">
+        <v>65.707171722315252</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="18">
+        <v>59.883957868862026</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="18">
+        <v>47.089721250855106</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="18">
+        <v>64.135908745229244</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="18">
+        <v>64.498678483068943</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="18">
+        <v>64.617446279153228</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="18">
+        <v>64.589405474252999</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="18">
+        <v>64.495418764636554</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="18">
+        <v>65.157488510012627</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="18">
+        <v>39.731272088181491</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="18">
+        <v>55.10317601470755</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="18">
+        <v>69.921586601994932</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="18">
+        <v>65.377256562933326</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="18">
+        <v>52.137102764940025</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="18">
+        <v>66.093358634971082</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="18">
+        <v>65.959082841873169</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="18">
+        <v>49.534032569175714</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="18">
+        <v>68.630873506959176</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="18">
+        <v>64.701181864365935</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="18">
+        <v>66.375338637310961</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="18">
+        <v>37.786630244743343</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="18">
+        <v>63.989662388339639</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="18">
+        <v>51.505820603018762</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="18">
+        <v>66.653778995387256</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="18">
+        <v>69.501903397031128</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="18">
+        <v>54.403790757900232</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="18">
+        <v>54.168964737003797</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="18">
+        <v>54.282969572490209</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="18">
+        <v>67.931337301499255</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="18">
+        <v>62.979649250558928</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="18">
+        <v>66.799648582177852</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="18">
+        <v>59.304515130608635</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="18">
+        <v>67.52361168153584</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="18">
+        <v>59.393040184351683</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="18">
+        <v>63.56746275909245</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="18">
+        <v>55.512787704458688</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="18">
+        <v>67.87473007074253</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="18">
+        <v>66.220361185260117</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="18">
+        <v>38.301261739623058</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="18">
+        <v>37.205278949629779</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="18">
+        <v>63.673041500151157</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="18">
+        <v>53.906791336942867</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="18">
+        <v>67.224547651763274</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="18">
+        <v>58.577946769493693</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="18">
+        <v>66.639596014283597</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="18">
+        <v>10.622601284424263</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="18">
+        <v>53.714845344670209</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="18">
+        <v>64.480729224160314</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="18">
+        <v>69.245125320740044</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="18">
+        <v>67.549383253416266</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="18">
+        <v>69.457086031325161</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="18">
+        <v>61.83220518794942</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="18">
+        <v>55.901519344023789</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="18">
+        <v>68.253622539460679</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="18">
+        <v>57.730194107118123</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="18">
+        <v>60.565905193624573</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="18">
+        <v>36.330436544310565</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="18">
+        <v>54.371732604598755</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="18">
+        <v>68.076506294310093</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="18">
+        <v>66.814738283865154</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="18">
+        <v>64.854898252524436</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="18">
+        <v>52.315707635974647</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="18">
+        <v>54.665355068540329</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="18">
+        <v>53.966292260536029</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="18">
+        <v>67.771987211088117</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="18">
+        <v>19.593071681097499</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="18">
+        <v>43.101171237745518</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="18">
+        <v>64.850421641021967</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="18">
+        <v>68.547247480636074</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="18">
+        <v>61.988776791668542</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="18">
+        <v>66.080443824692964</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="18">
+        <v>54.670921345182563</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="18">
+        <v>69.752130196429789</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="18">
+        <v>66.856773183866252</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="18">
+        <v>67.858769148588181</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="18">
+        <v>63.998540183529258</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="18">
+        <v>52.715792879839704</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="18">
+        <v>47.550380483448464</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="C4:C7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6BEEB4-665F-447C-961F-1F125E5D68DF}">
+  <dimension ref="A1:C201"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="60.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>54.159601153805852</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>66.380661819130182</v>
+      </c>
+      <c r="C3" s="16"/>
+    </row>
+    <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>36.291775908321142</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>50.686198230832815</v>
+      </c>
+      <c r="C5" s="16"/>
+    </row>
+    <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>31.592826182022691</v>
+      </c>
+      <c r="C6" s="16"/>
+    </row>
+    <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>45.855253227055073</v>
+      </c>
+      <c r="C7" s="16"/>
+    </row>
+    <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>30.320517616346478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>52.302951691672206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>49.434026712551713</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>43.199387555941939</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>56.002839189022779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>63.57905781827867</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>32.869030348956585</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>58.837524456903338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>69.796532960608602</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>47.778660459443927</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>63.368809698149562</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>68.03225489333272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="18">
+        <v>43.620424745604403</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="18">
+        <v>59.179010717198253</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18">
+        <v>54.713209187611938</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18">
+        <v>39.906998192891479</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>54.700477113947272</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>65.905556287616491</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>48.372254511341453</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>69.898928459733725</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18">
+        <v>63.934656400233507</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>50.923178065568209</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="18">
+        <v>46.912962635979056</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="18">
+        <v>63.923185840249062</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="18">
+        <v>40.89056265540421</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="18">
+        <v>41.869257381185889</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="18">
+        <v>48.810077300295234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="18">
+        <v>55.641898140311241</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="18">
+        <v>35.514342486858368</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="18">
+        <v>33.811726784333587</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="18">
+        <v>47.603143313899629</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="18">
+        <v>48.058695737272501</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="18">
+        <v>46.699465122073889</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="18">
+        <v>55.661057541146874</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="18">
+        <v>65.828026421368122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="18">
+        <v>34.533796273171902</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="18">
+        <v>49.820895986631513</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="18">
+        <v>68.34688963368535</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="18">
+        <v>59.393338020890951</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="18">
+        <v>42.243235912173986</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="18">
+        <v>55.272279866039753</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="18">
+        <v>35.142013486474752</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="18">
+        <v>43.110614437609911</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="18">
+        <v>69.392444984987378</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="18">
+        <v>40.75867997482419</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="18">
+        <v>48.73500338755548</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="18">
+        <v>31.786803537979718</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="18">
+        <v>31.982082910835743</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="18">
+        <v>55.842280834913254</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="18">
+        <v>66.566613717004657</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="18">
+        <v>59.079321585595608</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="18">
+        <v>53.112175399437547</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="18">
+        <v>66.850007614120841</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="18">
+        <v>39.644232336431742</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="18">
+        <v>67.799554318189621</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="18">
+        <v>59.231163468211889</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="18">
+        <v>65.581199442967772</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="18">
+        <v>35.482415361329913</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="18">
+        <v>55.319436984136701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="18">
+        <v>33.917870698496699</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="18">
+        <v>67.946593435481191</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="18">
+        <v>46.660039061680429</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="18">
+        <v>62.638314943760633</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="18">
+        <v>55.942162619903677</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="18">
+        <v>67.160349432379007</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="18">
+        <v>69.526862446218729</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="18">
+        <v>53.961099330335855</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="18">
+        <v>52.42811388336122</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="18">
+        <v>50.728246290236712</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="18">
+        <v>41.554477345198393</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="18">
+        <v>48.927850946784019</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="18">
+        <v>37.299285233020782</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="18">
+        <v>62.793126543983817</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="18">
+        <v>61.664043515920639</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="18">
+        <v>40.086802085861571</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="18">
+        <v>37.580863414332271</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="18">
+        <v>39.40100310370326</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="18">
+        <v>64.929334465414286</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="18">
+        <v>38.812923701480031</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="18">
+        <v>56.085501546040177</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="18">
+        <v>49.970622388646007</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="18">
+        <v>39.551843293011189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="18">
+        <v>44.322796929627657</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="18">
+        <v>69.830646272748709</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="18">
+        <v>33.525597183033824</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="18">
+        <v>54.766030581668019</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="18">
+        <v>56.523997485637665</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="18">
+        <v>63.554204320535064</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="18">
+        <v>53.303320398554206</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="18">
+        <v>55.987999374046922</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="18">
+        <v>69.871886996552348</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="18">
+        <v>57.877961648628109</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="18">
+        <v>48.032662989571691</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="18">
+        <v>47.323811231181026</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="18">
+        <v>51.103584431111813</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="18">
+        <v>67.10775782354176</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="18">
+        <v>61.860852492973208</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="18">
+        <v>42.269951719790697</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="18">
+        <v>56.52883805334568</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="18">
+        <v>59.640783695504069</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="18">
+        <v>57.985356627032161</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="18">
+        <v>52.775864265859127</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="18">
+        <v>69.65032079257071</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="18">
+        <v>38.445673892274499</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="18">
+        <v>51.816422147676349</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="18">
+        <v>52.66826044768095</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="18">
+        <v>46.604007706046104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="18">
+        <v>51.137546300888062</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="18">
+        <v>38.558493498712778</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="18">
+        <v>49.867883129045367</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="18">
+        <v>49.223454156890512</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="18">
+        <v>34.964152798056602</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="18">
+        <v>56.913818707689643</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="18">
+        <v>46.752912066876888</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="18">
+        <v>59.240476069971919</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="18">
+        <v>52.775810984894633</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="18">
+        <v>68.899649083614349</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="18">
+        <v>52.95214562676847</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="18">
+        <v>59.829586436972022</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="18">
+        <v>45.553642669692643</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="18">
+        <v>56.208467623218894</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="18">
+        <v>69.552129628136754</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="18">
+        <v>48.518926370888948</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="18">
+        <v>38.388260584324598</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="18">
+        <v>48.723424477502704</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="18">
+        <v>48.934789504855871</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="18">
+        <v>47.384428307414055</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="18">
+        <v>50.525541407987475</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="18">
+        <v>46.097106197848909</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="18">
+        <v>53.338918257504702</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="18">
+        <v>40.904699936509132</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="18">
+        <v>68.991130376234651</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="18">
+        <v>39.466299256309867</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="18">
+        <v>65.018547754734755</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="18">
+        <v>37.706687552854419</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="18">
+        <v>68.892200365662575</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="18">
+        <v>33.690879996865988</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="18">
+        <v>44.44531537592411</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="18">
+        <v>52.778187086805701</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="18">
+        <v>35.68511039018631</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="18">
+        <v>34.605477172881365</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="18">
+        <v>62.452744031324983</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="18">
+        <v>39.397408347576857</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="18">
+        <v>53.602568507194519</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="18">
+        <v>41.857693074271083</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="18">
+        <v>42.494654655456543</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="18">
+        <v>63.70848510414362</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="18">
+        <v>66.304153650999069</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="18">
+        <v>33.204325661063194</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="18">
+        <v>52.994925091043115</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="18">
+        <v>35.711140288040042</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="18">
+        <v>62.1308125089854</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="18">
+        <v>67.610325580462813</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="18">
+        <v>49.242674261331558</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="18">
+        <v>44.160215891897678</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="18">
+        <v>30.822160728275776</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="18">
+        <v>50.132974106818438</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="18">
+        <v>68.218390541151166</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="18">
+        <v>47.14512700214982</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="18">
+        <v>60.579321729019277</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="18">
+        <v>45.781482821330428</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="18">
+        <v>55.657301694154739</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A170" s="18">
+        <v>35.594209851697087</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="18">
+        <v>41.1560018081218</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="18">
+        <v>35.156222796067595</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A173" s="18">
+        <v>64.276959728449583</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="18">
+        <v>36.610254775732749</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="18">
+        <v>61.994597408920527</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A176" s="18">
+        <v>46.422534650191665</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="18">
+        <v>64.49917258694768</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="18">
+        <v>64.428684301674366</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="18">
+        <v>69.050594232976437</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="18">
+        <v>33.706649420782924</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="18">
+        <v>44.193472033366561</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="18">
+        <v>31.614128211513162</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="18">
+        <v>44.478811724111438</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="18">
+        <v>32.498178854584694</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="18">
+        <v>35.630365908145905</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="18">
+        <v>41.808858495205641</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="18">
+        <v>57.326766448095441</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="18">
+        <v>36.020947201177478</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="18">
+        <v>47.873855493962765</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="18">
+        <v>56.80857784114778</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="18">
+        <v>55.882668988779187</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="18">
+        <v>54.589489782229066</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="18">
+        <v>69.549052882939577</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="18">
+        <v>52.304007112979889</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="18">
+        <v>43.794741509482265</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="18">
+        <v>46.870538676157594</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="18">
+        <v>36.246237857267261</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="18">
+        <v>60.91596039943397</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="18">
+        <v>37.118570785969496</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="18">
+        <v>41.947133084759123</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="18">
+        <v>48.764944039285183</v>
       </c>
     </row>
   </sheetData>
@@ -7219,7 +9315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C955F2F1-43C9-4F71-B669-1BE51AD809F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D389AD84-D528-4727-A4E4-AEB12F8E073E}">
   <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7234,22 +9330,22 @@
   <sheetData>
     <row r="1" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -7284,7 +9380,7 @@
         <v>4.769730764606428E-2</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H2" s="12">
         <f>COUNT(B2:B13)</f>
@@ -7321,7 +9417,7 @@
         <v>0.11068209655016407</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H3" s="6">
         <f>AVERAGE(B2:B13)</f>
@@ -7358,7 +9454,7 @@
         <v>0.18689726251601743</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H4" s="6">
         <f>_xlfn.STDEV.S(B2:B13)</f>
@@ -7693,7 +9789,7 @@
     </row>
     <row r="16" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -7727,7 +9823,7 @@
     </row>
     <row r="18" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7745,7 +9841,7 @@
     </row>
     <row r="19" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -7779,7 +9875,7 @@
     </row>
     <row r="21" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -7797,7 +9893,7 @@
     </row>
     <row r="22" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -7831,7 +9927,7 @@
     </row>
     <row r="24" spans="1:14" ht="23.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -8174,7 +10270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B127E1C0-C15F-44EB-AF34-589FAF6EC930}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8459E6-98D4-4C0A-80A7-110A95963DFA}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8184,10 +10280,10 @@
   <sheetData>
     <row r="1" spans="1:6" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
@@ -8196,12 +10292,12 @@
         <v>3</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="14">
         <v>60</v>
@@ -8213,12 +10309,12 @@
         <v>10</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="14">
         <v>42</v>
@@ -8233,7 +10329,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -8255,7 +10351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E736E3B-C501-4318-B90E-1A395ED65A30}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ACB657-8380-46F3-B107-5CCBEAE85396}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8265,10 +10361,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8276,7 +10372,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8290,7 +10386,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8318,7 +10414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C1634D-F83A-45C5-8EE7-D99343FB5988}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D876A9B-38B5-4E28-B3A6-873A143D0C9D}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8328,10 +10424,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8339,7 +10435,7 @@
         <v>11</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8353,7 +10449,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -8429,7 +10525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BC518FD-1DE2-43D8-BFAF-75317D2A1417}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8048A5D2-78A7-4CE2-82C6-4041A76EC6C4}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8439,7 +10535,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>2</v>
@@ -8448,12 +10544,12 @@
         <v>3</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B2" s="14">
         <v>50</v>
@@ -8462,12 +10558,12 @@
         <v>10</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B3" s="14">
         <v>65</v>
@@ -8479,7 +10575,7 @@
     </row>
     <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B4" s="14">
         <v>50</v>
@@ -8488,7 +10584,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -8510,7 +10606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FACE664-974F-4E86-90E6-D73B6AB7E193}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A962CF91-33A4-48CB-AF77-2D81DB22305B}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8520,21 +10616,21 @@
   <sheetData>
     <row r="1" spans="1:5" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" s="14">
         <v>0</v>
@@ -8543,12 +10639,12 @@
         <v>1</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" s="14">
         <v>50</v>
@@ -8560,7 +10656,7 @@
     </row>
     <row r="4" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" s="14">
         <v>100</v>
@@ -8569,12 +10665,12 @@
         <v>15</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B5" s="14">
         <v>10</v>
@@ -8600,7 +10696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E104B4FA-42D2-468E-8CCA-A100AF1CEB7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB6F9EE-22CD-46F6-93A0-BD6076AF6F2C}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8610,10 +10706,10 @@
   <sheetData>
     <row r="1" spans="1:7" ht="46.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
@@ -8622,15 +10718,15 @@
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="14">
         <v>62</v>
@@ -8645,12 +10741,12 @@
         <v>-0.75</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" s="14">
         <v>62</v>
@@ -8666,7 +10762,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="G4" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/kapitola_04.xlsx
+++ b/data/kapitola_04.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C144945-8A9B-4502-831F-D27AD408A4B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E73D967A-EDA1-4BF7-975B-53CCA69D6358}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{4A0A6F10-B855-443F-A03E-A1F9BEA70190}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="34995" windowHeight="19060" xr2:uid="{B6B0A2F2-3418-4F22-89B5-CB9A06F1899A}"/>
   </bookViews>
   <sheets>
     <sheet name="Prehled" sheetId="1" r:id="rId1"/>
@@ -789,7 +789,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-9256-44C1-94FC-FB2158D72C35}"/>
+              <c16:uniqueId val="{00000008-73EC-4EB7-A9D0-6C792A6A4238}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -903,7 +903,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-9256-44C1-94FC-FB2158D72C35}"/>
+              <c16:uniqueId val="{00000009-73EC-4EB7-A9D0-6C792A6A4238}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -915,11 +915,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1164856047"/>
-        <c:axId val="1164867567"/>
+        <c:axId val="606791583"/>
+        <c:axId val="606794463"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1164856047"/>
+        <c:axId val="606791583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="2"/>
@@ -949,13 +949,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1164867567"/>
+        <c:crossAx val="606794463"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1164867567"/>
+        <c:axId val="606794463"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -983,7 +983,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1164856047"/>
+        <c:crossAx val="606791583"/>
         <c:crossesAt val="-2"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1182,7 +1182,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-8AE5-4A1E-AC68-9000AE458192}"/>
+              <c16:uniqueId val="{00000008-0901-4282-AF84-53BD840002AE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1296,7 +1296,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-8AE5-4A1E-AC68-9000AE458192}"/>
+              <c16:uniqueId val="{00000009-0901-4282-AF84-53BD840002AE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1308,11 +1308,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1164868047"/>
-        <c:axId val="1164864207"/>
+        <c:axId val="606793503"/>
+        <c:axId val="606793983"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1164868047"/>
+        <c:axId val="606793503"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1342,13 +1342,13 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1164864207"/>
+        <c:crossAx val="606793983"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1164864207"/>
+        <c:axId val="606793983"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -1378,7 +1378,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="low"/>
-        <c:crossAx val="1164868047"/>
+        <c:crossAx val="606793503"/>
         <c:crossesAt val="0"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
@@ -1441,7 +1441,7 @@
         <xdr:cNvPr id="2" name="Graf 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2A79358-AF4E-7A75-A44F-6445F2BF10F6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E2FDD63-8578-7C7F-1EB9-641ED2D5A4D2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1477,7 +1477,7 @@
         <xdr:cNvPr id="3" name="Graf 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C7D836E-DF92-0645-F46E-14BB2019E792}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D5E2609-07D4-C8B0-8A48-56B7C91DFD4F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1814,7 +1814,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC0D22CF-D47E-4A75-B463-15DA91FAD1B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25DDAA9D-FB87-484A-88E5-6AC619A7A1D8}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2143,7 +2143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B748F50A-6420-4E90-9FA9-A0D7CD1F0D94}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B131DD71-16B5-4390-8B5C-318B0ADDBC07}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2206,7 +2206,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53E910E5-A7EA-46E2-B9D9-C1736470A5C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0237FC15-1280-4C86-BD23-1A262506D3E6}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2288,7 +2288,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B69289-AA34-4DAC-9BEE-8F3B8A5803DD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A237558D-8A06-4817-99FD-2DDEC5E069EB}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2376,7 +2376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78D8E3D3-546F-4A6C-AD33-66F8A2F80212}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1EEAC6-4518-45F1-8093-6C7A613F995E}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2458,7 +2458,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79986BEA-76C8-4AD1-B44A-B6C7819420F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE83EE95-E4D4-4092-9724-138565C8A087}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2534,7 +2534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FDAE8B7-77C0-4C72-B2EA-90A234D545B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4532CD1B-F72D-4279-868D-8C3E85345C36}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2594,7 +2594,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A303A4A-A3B5-4525-A43F-660AC44E0F1F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB40D5EE-21B1-4D56-975B-804127A88850}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2651,7 +2651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92A2BDE6-7B4C-449C-AAAE-555802B61CF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03B14A65-0707-4542-BD9B-842C3CFC3BA8}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2747,7 +2747,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E828F21-B68F-4E38-A94E-ECC0917A572A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38EFCC64-6DEB-45C5-8E66-8FB88E67B0E0}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3783,7 +3783,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E76D6B6-F167-402B-8BDE-5F02A7D14F80}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B233DD26-5920-45CC-B28A-7625C6DA842A}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4819,7 +4819,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F894E161-84B4-4807-93E3-0CEA1F45BF2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AA6035D-42F3-4081-B8C8-9BB9412D17E7}">
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5171,7 +5171,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2E6DD1-5EE5-4142-AEE5-8E3011462CAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56FC6CA6-78EE-4020-83E6-90E14D4471C6}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5189,7 +5189,7 @@
     </row>
     <row r="2" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18">
-        <v>44.583323970004095</v>
+        <v>39.724727431511013</v>
       </c>
       <c r="C2" s="17" t="s">
         <v>87</v>
@@ -5197,13 +5197,13 @@
     </row>
     <row r="3" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="18">
-        <v>51.334447207766225</v>
+        <v>58.118776458561115</v>
       </c>
       <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18">
-        <v>22.049299769270561</v>
+        <v>51.549693565343112</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>88</v>
@@ -5211,990 +5211,990 @@
     </row>
     <row r="5" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18">
-        <v>67.12353898825269</v>
+        <v>54.168762503873189</v>
       </c>
       <c r="C5" s="16"/>
     </row>
     <row r="6" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18">
-        <v>51.43348741741498</v>
+        <v>0.26450928128574702</v>
       </c>
       <c r="C6" s="16"/>
     </row>
     <row r="7" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18">
-        <v>51.851061941192299</v>
+        <v>59.156280870021689</v>
       </c>
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18">
-        <v>61.899850011110217</v>
+        <v>51.00607829577649</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
-        <v>45.089113454926675</v>
+        <v>58.368700636682519</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
-        <v>58.022351957847448</v>
+        <v>53.672015724455157</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
-        <v>27.918169643776512</v>
+        <v>50.891779514678191</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
-        <v>48.252400632490939</v>
+        <v>60.928077357477186</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
-        <v>50.504048652608617</v>
+        <v>47.042420653698166</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
-        <v>46.940464063830234</v>
+        <v>60.370250101681357</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
-        <v>32.477745204184998</v>
+        <v>54.789008326850976</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
-        <v>47.776046232762582</v>
+        <v>53.75865911948803</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
-        <v>52.364536146374576</v>
+        <v>59.222732716971443</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
-        <v>45.500856174103568</v>
+        <v>39.402243702258858</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
-        <v>55.052096044162909</v>
+        <v>57.430363110897098</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
-        <v>50.685613161086344</v>
+        <v>65.891015846816899</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
-        <v>49.66952996775624</v>
+        <v>54.895824931083922</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
-        <v>104.0837872400076</v>
+        <v>54.1735664256802</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
-        <v>48.138533562033437</v>
+        <v>42.715099022893277</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
-        <v>51.306818862784155</v>
+        <v>38.971480257404153</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
-        <v>50.20944889961028</v>
+        <v>44.268552042379582</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
-        <v>75.063939489551288</v>
+        <v>70.731069508894421</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
-        <v>45.850919890213376</v>
+        <v>46.243143093170325</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
-        <v>61.182874319803965</v>
+        <v>50.741456252539415</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
-        <v>53.242645886564432</v>
+        <v>49.405084948705856</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
-        <v>48.457622052033251</v>
+        <v>56.774428583154823</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="18">
-        <v>50.141780231489143</v>
+        <v>62.201435154424708</v>
       </c>
     </row>
     <row r="32" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
-        <v>54.727203415741691</v>
+        <v>44.070829161996144</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
-        <v>41.170085502511725</v>
+        <v>35.606389537296621</v>
       </c>
     </row>
     <row r="34" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="18">
-        <v>45.643499747389342</v>
+        <v>51.0817992094141</v>
       </c>
     </row>
     <row r="35" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="18">
-        <v>49.679103878592088</v>
+        <v>49.382484349741766</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="18">
-        <v>48.057261654852617</v>
+        <v>42.857879046631588</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="18">
-        <v>69.936980427049335</v>
+        <v>21.690969435868485</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="18">
-        <v>49.69352250939118</v>
+        <v>45.798966644404146</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="18">
-        <v>68.62388039969656</v>
+        <v>48.934234645944727</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
-        <v>49.630861611768701</v>
+        <v>42.29757252431574</v>
       </c>
     </row>
     <row r="41" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="18">
-        <v>46.252110620339266</v>
+        <v>42.888432410652641</v>
       </c>
     </row>
     <row r="42" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="18">
-        <v>33.849920369473907</v>
+        <v>46.867880265574279</v>
       </c>
     </row>
     <row r="43" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="18">
-        <v>61.040272273906567</v>
+        <v>66.981012888387795</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="18">
-        <v>51.026349773822112</v>
+        <v>47.341479881702519</v>
       </c>
     </row>
     <row r="45" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="18">
-        <v>25.437813575006871</v>
+        <v>44.112392451074463</v>
       </c>
     </row>
     <row r="46" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="18">
-        <v>42.412842605243902</v>
+        <v>52.258088138642179</v>
       </c>
     </row>
     <row r="47" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18">
-        <v>62.686303636400751</v>
+        <v>48.126382538297968</v>
       </c>
     </row>
     <row r="48" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="18">
-        <v>42.704975764121997</v>
+        <v>60.326213967587165</v>
       </c>
     </row>
     <row r="49" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18">
-        <v>49.587829692225341</v>
+        <v>48.317790891858081</v>
       </c>
     </row>
     <row r="50" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="18">
-        <v>40.78205054740252</v>
+        <v>48.098361102434595</v>
       </c>
     </row>
     <row r="51" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18">
-        <v>41.946539670316461</v>
+        <v>56.532791274604683</v>
       </c>
     </row>
     <row r="52" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18">
-        <v>45.353919743322727</v>
+        <v>56.205372818910021</v>
       </c>
     </row>
     <row r="53" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="18">
-        <v>51.583911931211553</v>
+        <v>59.278661814366671</v>
       </c>
     </row>
     <row r="54" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
-        <v>43.714457679757274</v>
+        <v>31.975622365288288</v>
       </c>
     </row>
     <row r="55" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
-        <v>52.37259939470421</v>
+        <v>49.965090683132843</v>
       </c>
     </row>
     <row r="56" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
-        <v>36.057837306818563</v>
+        <v>41.850920470666857</v>
       </c>
     </row>
     <row r="57" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18">
-        <v>52.312866521311008</v>
+        <v>55.843622327535812</v>
       </c>
     </row>
     <row r="58" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="18">
-        <v>50.898708249164237</v>
+        <v>62.144257254596909</v>
       </c>
     </row>
     <row r="59" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="18">
-        <v>41.696665737883528</v>
+        <v>67.919104259787233</v>
       </c>
     </row>
     <row r="60" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18">
-        <v>44.350601057959913</v>
+        <v>56.328545186684565</v>
       </c>
     </row>
     <row r="61" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="18">
-        <v>58.236466252153789</v>
+        <v>57.86354034888604</v>
       </c>
     </row>
     <row r="62" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="18">
-        <v>19.574030505252157</v>
+        <v>30.82231053339391</v>
       </c>
     </row>
     <row r="63" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="18">
-        <v>56.080188977948879</v>
+        <v>51.565234809090015</v>
       </c>
     </row>
     <row r="64" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="18">
-        <v>30.68074555636943</v>
+        <v>44.487758520778883</v>
       </c>
     </row>
     <row r="65" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="18">
-        <v>-12.204560354287352</v>
+        <v>52.097375011673627</v>
       </c>
     </row>
     <row r="66" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="18">
-        <v>45.220203620598937</v>
+        <v>43.094426157035976</v>
       </c>
     </row>
     <row r="67" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="18">
-        <v>17.633038518680848</v>
+        <v>42.403509176801457</v>
       </c>
     </row>
     <row r="68" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="18">
-        <v>52.558418096840398</v>
+        <v>50.78434181264182</v>
       </c>
     </row>
     <row r="69" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="18">
-        <v>53.918768547743881</v>
+        <v>58.422128835990357</v>
       </c>
     </row>
     <row r="70" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="18">
-        <v>56.972852118665365</v>
+        <v>51.846581487407626</v>
       </c>
     </row>
     <row r="71" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="18">
-        <v>58.026408528720026</v>
+        <v>51.001032356714063</v>
       </c>
     </row>
     <row r="72" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="18">
-        <v>42.542720247102906</v>
+        <v>98.625584203476706</v>
       </c>
     </row>
     <row r="73" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="18">
-        <v>48.323793455863751</v>
+        <v>50.223893813690545</v>
       </c>
     </row>
     <row r="74" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18">
-        <v>50.092658671687573</v>
+        <v>27.181022851138508</v>
       </c>
     </row>
     <row r="75" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18">
-        <v>45.229895119984732</v>
+        <v>61.374386747861536</v>
       </c>
     </row>
     <row r="76" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="18">
-        <v>52.728573385504006</v>
+        <v>55.046851001158039</v>
       </c>
     </row>
     <row r="77" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18">
-        <v>71.899363117058016</v>
+        <v>53.319267573452812</v>
       </c>
     </row>
     <row r="78" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="18">
-        <v>44.513348927234212</v>
+        <v>64.121480066010079</v>
       </c>
     </row>
     <row r="79" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18">
-        <v>63.77864435299476</v>
+        <v>47.990705362420563</v>
       </c>
     </row>
     <row r="80" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="18">
-        <v>46.436575656511899</v>
+        <v>60.40581371236064</v>
       </c>
     </row>
     <row r="81" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18">
-        <v>34.887998227138411</v>
+        <v>62.495748118710729</v>
       </c>
     </row>
     <row r="82" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="18">
-        <v>58.462021678261699</v>
+        <v>53.351244138838112</v>
       </c>
     </row>
     <row r="83" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="18">
-        <v>88.463061624052457</v>
+        <v>82.14232343527209</v>
       </c>
     </row>
     <row r="84" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="18">
-        <v>67.934703645557789</v>
+        <v>50.582145829769068</v>
       </c>
     </row>
     <row r="85" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="18">
-        <v>42.4628425000082</v>
+        <v>42.392442026821755</v>
       </c>
     </row>
     <row r="86" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="18">
-        <v>61.204939847809861</v>
+        <v>52.232240301001326</v>
       </c>
     </row>
     <row r="87" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="18">
-        <v>30.712805609794103</v>
+        <v>45.09197018517721</v>
       </c>
     </row>
     <row r="88" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="18">
-        <v>51.861494525023879</v>
+        <v>54.948427753635393</v>
       </c>
     </row>
     <row r="89" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18">
-        <v>54.918184385449301</v>
+        <v>32.246457508143337</v>
       </c>
     </row>
     <row r="90" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="18">
-        <v>32.623603626472288</v>
+        <v>55.981956745346146</v>
       </c>
     </row>
     <row r="91" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="18">
-        <v>45.728197050296096</v>
+        <v>42.737246373952154</v>
       </c>
     </row>
     <row r="92" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="18">
-        <v>43.597926883139415</v>
+        <v>38.93412277284262</v>
       </c>
     </row>
     <row r="93" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="18">
-        <v>23.030243265509871</v>
+        <v>46.595969605800896</v>
       </c>
     </row>
     <row r="94" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="18">
-        <v>56.656211338615392</v>
+        <v>35.488426913050532</v>
       </c>
     </row>
     <row r="95" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="18">
-        <v>58.795607188661208</v>
+        <v>50.584418788767863</v>
       </c>
     </row>
     <row r="96" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="18">
-        <v>45.169194495007787</v>
+        <v>60.34497695853851</v>
       </c>
     </row>
     <row r="97" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="18">
-        <v>58.697729354499721</v>
+        <v>57.396151120543223</v>
       </c>
     </row>
     <row r="98" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="18">
-        <v>36.002693637123954</v>
+        <v>70.475388241866398</v>
       </c>
     </row>
     <row r="99" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="18">
-        <v>48.499856032151719</v>
+        <v>53.91521312271513</v>
       </c>
     </row>
     <row r="100" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="18">
-        <v>55.574792339894898</v>
+        <v>48.174698978153863</v>
       </c>
     </row>
     <row r="101" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="18">
-        <v>46.620051006744809</v>
+        <v>38.949618607218184</v>
       </c>
     </row>
     <row r="102" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="18">
-        <v>35.192832980731971</v>
+        <v>46.389970981785247</v>
       </c>
     </row>
     <row r="103" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="18">
-        <v>45.186132660524521</v>
+        <v>54.290097759645406</v>
       </c>
     </row>
     <row r="104" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="18">
-        <v>41.440002205863252</v>
+        <v>52.471151283741023</v>
       </c>
     </row>
     <row r="105" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="18">
-        <v>56.867720158468678</v>
+        <v>45.442168206456557</v>
       </c>
     </row>
     <row r="106" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="18">
-        <v>53.295696930395053</v>
+        <v>35.499611058454988</v>
       </c>
     </row>
     <row r="107" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="18">
-        <v>64.889311035448912</v>
+        <v>46.495934367505633</v>
       </c>
     </row>
     <row r="108" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="18">
-        <v>54.26200612782938</v>
+        <v>52.704200478698787</v>
       </c>
     </row>
     <row r="109" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="18">
-        <v>52.544742047961151</v>
+        <v>44.419121975138992</v>
       </c>
     </row>
     <row r="110" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="18">
-        <v>40.523359873000345</v>
+        <v>61.149565185138883</v>
       </c>
     </row>
     <row r="111" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="18">
-        <v>46.446031997827333</v>
+        <v>51.046601593847974</v>
       </c>
     </row>
     <row r="112" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="18">
-        <v>51.779561027162579</v>
+        <v>48.492554319077684</v>
       </c>
     </row>
     <row r="113" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="18">
-        <v>49.014194362670722</v>
+        <v>51.421176174767488</v>
       </c>
     </row>
     <row r="114" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="18">
-        <v>61.819034752771493</v>
+        <v>63.835830736229738</v>
       </c>
     </row>
     <row r="115" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="18">
-        <v>29.985690829060811</v>
+        <v>49.125957357671297</v>
       </c>
     </row>
     <row r="116" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="18">
-        <v>53.876783794405526</v>
+        <v>39.766572080096871</v>
       </c>
     </row>
     <row r="117" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="18">
-        <v>61.539812338110224</v>
+        <v>36.18100292771112</v>
       </c>
     </row>
     <row r="118" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="18">
-        <v>43.974827192966821</v>
+        <v>46.340085968608527</v>
       </c>
     </row>
     <row r="119" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="18">
-        <v>45.551346114953439</v>
+        <v>58.571023212204665</v>
       </c>
     </row>
     <row r="120" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="18">
-        <v>50.084261318972246</v>
+        <v>56.158306536071883</v>
       </c>
     </row>
     <row r="121" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="18">
-        <v>62.01638668237868</v>
+        <v>32.705329596195241</v>
       </c>
     </row>
     <row r="122" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="18">
-        <v>56.175165413494142</v>
+        <v>46.330914380935489</v>
       </c>
     </row>
     <row r="123" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="18">
-        <v>47.456388751873405</v>
+        <v>55.358282433825607</v>
       </c>
     </row>
     <row r="124" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="18">
-        <v>23.038518892969723</v>
+        <v>35.030361414130681</v>
       </c>
     </row>
     <row r="125" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="18">
-        <v>51.998571819711955</v>
+        <v>50.289757718576865</v>
       </c>
     </row>
     <row r="126" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="18">
-        <v>44.601782349880828</v>
+        <v>59.053231030160973</v>
       </c>
     </row>
     <row r="127" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="18">
-        <v>62.587679284555179</v>
+        <v>43.621179876209631</v>
       </c>
     </row>
     <row r="128" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="18">
-        <v>47.981402959431179</v>
+        <v>55.381254103458886</v>
       </c>
     </row>
     <row r="129" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="18">
-        <v>57.746497474145698</v>
+        <v>54.273169688545877</v>
       </c>
     </row>
     <row r="130" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="18">
-        <v>39.268318019440855</v>
+        <v>54.434743771249067</v>
       </c>
     </row>
     <row r="131" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="18">
-        <v>40.593793682408517</v>
+        <v>42.422121465148308</v>
       </c>
     </row>
     <row r="132" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="18">
-        <v>68.981146636466704</v>
+        <v>56.2579563366982</v>
       </c>
     </row>
     <row r="133" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="18">
-        <v>52.193130853285872</v>
+        <v>52.736555807487591</v>
       </c>
     </row>
     <row r="134" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="18">
-        <v>33.76091170487512</v>
+        <v>57.402843295453799</v>
       </c>
     </row>
     <row r="135" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="18">
-        <v>50.171022483272182</v>
+        <v>47.395345262911022</v>
       </c>
     </row>
     <row r="136" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="18">
-        <v>60.620977113570738</v>
+        <v>55.028160532842065</v>
       </c>
     </row>
     <row r="137" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="18">
-        <v>39.784466650531179</v>
+        <v>51.172716178356914</v>
       </c>
     </row>
     <row r="138" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="18">
-        <v>63.595008502574217</v>
+        <v>48.374305284300064</v>
       </c>
     </row>
     <row r="139" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="18">
-        <v>50.529974380471813</v>
+        <v>15.108578494940213</v>
       </c>
     </row>
     <row r="140" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="18">
-        <v>44.190483929113618</v>
+        <v>71.120551635300288</v>
       </c>
     </row>
     <row r="141" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="18">
-        <v>53.542574514794453</v>
+        <v>69.910912378502431</v>
       </c>
     </row>
     <row r="142" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="18">
-        <v>39.477142117733074</v>
+        <v>50.143477787399455</v>
       </c>
     </row>
     <row r="143" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="18">
-        <v>43.732251991134852</v>
+        <v>57.087882553740172</v>
       </c>
     </row>
     <row r="144" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="18">
-        <v>41.959239458331346</v>
+        <v>30.37035360126303</v>
       </c>
     </row>
     <row r="145" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="18">
-        <v>38.792495139376115</v>
+        <v>43.287788272562587</v>
       </c>
     </row>
     <row r="146" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="18">
-        <v>45.854655573468918</v>
+        <v>43.714821159148705</v>
       </c>
     </row>
     <row r="147" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="18">
-        <v>60.354771536885288</v>
+        <v>55.22878609637408</v>
       </c>
     </row>
     <row r="148" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="18">
-        <v>62.219049231687123</v>
+        <v>16.744147548002623</v>
       </c>
     </row>
     <row r="149" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="18">
-        <v>45.52130275469495</v>
+        <v>45.623284594797433</v>
       </c>
     </row>
     <row r="150" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="18">
-        <v>49.924428774898615</v>
+        <v>44.418434899096489</v>
       </c>
     </row>
     <row r="151" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="18">
-        <v>37.764960053846963</v>
+        <v>80.906599676794229</v>
       </c>
     </row>
     <row r="152" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="18">
-        <v>51.658304855015182</v>
+        <v>48.851658693260283</v>
       </c>
     </row>
     <row r="153" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="18">
-        <v>29.707599198619079</v>
+        <v>50.255395651187406</v>
       </c>
     </row>
     <row r="154" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="18">
-        <v>46.231772923103257</v>
+        <v>48.366714535745814</v>
       </c>
     </row>
     <row r="155" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="18">
-        <v>55.298751839191588</v>
+        <v>38.138813119198225</v>
       </c>
     </row>
     <row r="156" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="18">
-        <v>41.922572445910873</v>
+        <v>62.114514106185744</v>
       </c>
     </row>
     <row r="157" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="18">
-        <v>48.262933858575977</v>
+        <v>89.044123304201307</v>
       </c>
     </row>
     <row r="158" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="18">
-        <v>44.476607929252594</v>
+        <v>46.230586871601425</v>
       </c>
     </row>
     <row r="159" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="18">
-        <v>48.533536089568322</v>
+        <v>50.297842099809216</v>
       </c>
     </row>
     <row r="160" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="18">
-        <v>50.891699221834102</v>
+        <v>54.532855937459317</v>
       </c>
     </row>
     <row r="161" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="18">
-        <v>55.942113835665133</v>
+        <v>87.757894474667111</v>
       </c>
     </row>
     <row r="162" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="18">
-        <v>46.056943456482507</v>
+        <v>54.466946468348141</v>
       </c>
     </row>
     <row r="163" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="18">
-        <v>58.216244888538114</v>
+        <v>50.471710169218099</v>
       </c>
     </row>
     <row r="164" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="18">
-        <v>52.217003100011731</v>
+        <v>62.42450312593202</v>
       </c>
     </row>
     <row r="165" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="18">
-        <v>48.210090208151811</v>
+        <v>47.861203939628588</v>
       </c>
     </row>
     <row r="166" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="18">
-        <v>62.0879827797365</v>
+        <v>51.513529406448818</v>
       </c>
     </row>
     <row r="167" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="18">
-        <v>64.228945367396022</v>
+        <v>76.547904892048948</v>
       </c>
     </row>
     <row r="168" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="18">
-        <v>20.131492243533419</v>
+        <v>53.242337114454543</v>
       </c>
     </row>
     <row r="169" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="18">
-        <v>110.64886999472245</v>
+        <v>48.247108662185646</v>
       </c>
     </row>
     <row r="170" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="18">
-        <v>32.941935085315933</v>
+        <v>57.160241955209123</v>
       </c>
     </row>
     <row r="171" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="18">
-        <v>38.163113947951629</v>
+        <v>67.311397552087669</v>
       </c>
     </row>
     <row r="172" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="18">
-        <v>28.014152026886876</v>
+        <v>45.750161515257368</v>
       </c>
     </row>
     <row r="173" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="18">
-        <v>37.31657769048735</v>
+        <v>25.695928137197193</v>
       </c>
     </row>
     <row r="174" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="18">
-        <v>62.196798206891565</v>
+        <v>34.168154301390146</v>
       </c>
     </row>
     <row r="175" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="18">
-        <v>71.437812193563587</v>
+        <v>50.758333896554582</v>
       </c>
     </row>
     <row r="176" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="18">
-        <v>60.833312973349301</v>
+        <v>36.42948761760335</v>
       </c>
     </row>
     <row r="177" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="18">
-        <v>47.624045845330549</v>
+        <v>34.495583143570343</v>
       </c>
     </row>
     <row r="178" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="18">
-        <v>47.969146974682602</v>
+        <v>46.070327372243071</v>
       </c>
     </row>
     <row r="179" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="18">
-        <v>41.411513183912675</v>
+        <v>47.321982102905089</v>
       </c>
     </row>
     <row r="180" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="18">
-        <v>40.775685771027305</v>
+        <v>65.168113679426</v>
       </c>
     </row>
     <row r="181" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="18">
-        <v>37.87482306899652</v>
+        <v>51.802903328288394</v>
       </c>
     </row>
     <row r="182" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="18">
-        <v>36.109009913511997</v>
+        <v>56.361311949642122</v>
       </c>
     </row>
     <row r="183" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="18">
-        <v>58.135307145492682</v>
+        <v>53.754812274581838</v>
       </c>
     </row>
     <row r="184" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="18">
-        <v>66.807164265069304</v>
+        <v>59.744493536762221</v>
       </c>
     </row>
     <row r="185" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="18">
-        <v>53.720121887290681</v>
+        <v>36.109468986345533</v>
       </c>
     </row>
     <row r="186" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="18">
-        <v>62.774840258291775</v>
+        <v>56.362964271399221</v>
       </c>
     </row>
     <row r="187" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="18">
-        <v>47.137994499823385</v>
+        <v>86.332687137693071</v>
       </c>
     </row>
     <row r="188" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="18">
-        <v>42.151912174740652</v>
+        <v>12.534328646608904</v>
       </c>
     </row>
     <row r="189" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="18">
-        <v>51.059677931739131</v>
+        <v>74.933317492812549</v>
       </c>
     </row>
     <row r="190" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="18">
-        <v>28.741581848902054</v>
+        <v>51.501287057655638</v>
       </c>
     </row>
     <row r="191" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="18">
-        <v>41.54036883231511</v>
+        <v>49.65016464913402</v>
       </c>
     </row>
     <row r="192" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="18">
-        <v>40.373172130813913</v>
+        <v>46.959105184612248</v>
       </c>
     </row>
     <row r="193" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="18">
-        <v>55.702822738870395</v>
+        <v>46.440390595706795</v>
       </c>
     </row>
     <row r="194" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="18">
-        <v>11.42434803408441</v>
+        <v>43.157416314777265</v>
       </c>
     </row>
     <row r="195" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="18">
-        <v>49.053571153044992</v>
+        <v>48.391180980109894</v>
       </c>
     </row>
     <row r="196" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="18">
-        <v>45.577680998383187</v>
+        <v>60.513406900320845</v>
       </c>
     </row>
     <row r="197" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="18">
-        <v>39.826789789901085</v>
+        <v>50.661008835384578</v>
       </c>
     </row>
     <row r="198" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="18">
-        <v>38.979676161116856</v>
+        <v>58.638692831012222</v>
       </c>
     </row>
     <row r="199" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="18">
-        <v>51.981276736960531</v>
+        <v>49.336674268847567</v>
       </c>
     </row>
     <row r="200" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="18">
-        <v>20.98298801463104</v>
+        <v>59.870246431122155</v>
       </c>
     </row>
     <row r="201" spans="1:1" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="18">
-        <v>46.144000858098984</v>
+        <v>43.729801569967776</v>
       </c>
     </row>
   </sheetData>
@@ -6207,7 +6207,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{130DFEC5-EC78-4A0A-846D-285700F57BB0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56AA11DB-10CC-431D-AF32-89C62AABE066}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7243,7 +7243,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9F3CFAA-E4F1-4676-97C7-96704803B99F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0FA0375-7537-41FB-BB68-5CF00F11F2D9}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8279,7 +8279,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F6BEEB4-665F-447C-961F-1F125E5D68DF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{744FAFBB-E54B-49A5-9796-E58532FA182E}">
   <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9315,7 +9315,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D389AD84-D528-4727-A4E4-AEB12F8E073E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{855D364F-ECB0-4D99-BA0E-60C3CE1D0027}">
   <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10270,7 +10270,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8459E6-98D4-4C0A-80A7-110A95963DFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38288AB1-2B93-4D6A-97DB-856F390FA7B1}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10351,7 +10351,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2ACB657-8380-46F3-B107-5CCBEAE85396}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94D52721-F7B2-42F4-9737-2CCE66C8880C}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10414,7 +10414,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D876A9B-38B5-4E28-B3A6-873A143D0C9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DAB06F5-8CA7-483A-B872-4714FF557BEA}">
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10525,7 +10525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8048A5D2-78A7-4CE2-82C6-4041A76EC6C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F50F684-24C8-4D82-BCC6-55373D5B3B2D}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10606,7 +10606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A962CF91-33A4-48CB-AF77-2D81DB22305B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC99F7B8-73EC-4D44-9E0F-7FBF4670DFF8}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
@@ -10696,7 +10696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB6F9EE-22CD-46F6-93A0-BD6076AF6F2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1159BFD8-C8B7-46EE-A92D-F304D6761ABA}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
